--- a/_resultados/_resultados.xlsx
+++ b/_resultados/_resultados.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ravar\Documents\GitHub\recsys-fair-federation-flower\_resultados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B7E5C13-01FE-484E-9DEA-1AF1073863C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25D1090B-01FA-47E8-B12C-FE77CD50F7D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="7B-Backup" sheetId="1" r:id="rId1"/>
     <sheet name="7B" sheetId="2" r:id="rId2"/>
+    <sheet name="7M" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="7">
   <si>
     <t>Estratégia</t>
   </si>
@@ -114,6 +115,9 @@
       <t>)</t>
     </r>
   </si>
+  <si>
+    <t>7M</t>
+  </si>
 </sst>
 </file>
 
@@ -156,7 +160,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -172,6 +176,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -203,23 +213,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -316,6 +327,64 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1FB55215-8576-4BEB-860C-A575D7C49D21}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId2"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5669282" y="11723"/>
+          <a:ext cx="180000" cy="180000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>685802</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>11723</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>865802</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>191723</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Gráfico 1" descr="Contorno de rosto rindo com preenchimento sólido">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B28B2AC1-C8AF-4709-875B-ACACC927C7D4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -624,34 +693,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="3"/>
+      <c r="F1" s="2"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="6">
         <v>0.2</v>
       </c>
-      <c r="C2" s="2">
-        <v>1</v>
-      </c>
-      <c r="D2" s="4">
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3">
         <v>6.0960731897987297E-4</v>
       </c>
       <c r="E2" s="5">
@@ -663,38 +732,38 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="2">
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="1">
         <v>2</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="4">
         <v>1.2366666655837901E-3</v>
       </c>
-      <c r="E3" s="1"/>
+      <c r="E3" s="6"/>
       <c r="F3" s="7"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="2">
-        <v>3</v>
-      </c>
-      <c r="D4" s="4">
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="1">
+        <v>3</v>
+      </c>
+      <c r="D4" s="3">
         <v>1.16827424905807E-4</v>
       </c>
-      <c r="E4" s="1"/>
+      <c r="E4" s="6"/>
       <c r="F4" s="7"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1">
+      <c r="A5" s="6"/>
+      <c r="B5" s="6">
         <v>0.4</v>
       </c>
-      <c r="C5" s="2">
-        <v>1</v>
-      </c>
-      <c r="D5" s="6">
+      <c r="C5" s="1">
+        <v>1</v>
+      </c>
+      <c r="D5" s="4">
         <v>1.05738310578603E-3</v>
       </c>
       <c r="E5" s="5">
@@ -706,38 +775,38 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="2">
+      <c r="A6" s="6"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="1">
         <v>2</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="3">
         <v>7.1366126257072198E-4</v>
       </c>
-      <c r="E6" s="1"/>
+      <c r="E6" s="6"/>
       <c r="F6" s="7"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="2">
-        <v>3</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="A7" s="6"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="1">
+        <v>3</v>
+      </c>
+      <c r="D7" s="4">
         <v>1.03197048005576E-3</v>
       </c>
-      <c r="E7" s="1"/>
+      <c r="E7" s="6"/>
       <c r="F7" s="7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1">
+      <c r="A8" s="6"/>
+      <c r="B8" s="6">
         <v>0.6</v>
       </c>
-      <c r="C8" s="2">
-        <v>1</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="1">
+        <v>1</v>
+      </c>
+      <c r="D8" s="4">
         <v>8.5958764850758399E-4</v>
       </c>
       <c r="E8" s="5">
@@ -749,38 +818,38 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="2">
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="1">
         <v>2</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="3">
         <v>1.9315911817009E-5</v>
       </c>
-      <c r="E9" s="1"/>
+      <c r="E9" s="6"/>
       <c r="F9" s="7"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="2">
-        <v>3</v>
-      </c>
-      <c r="D10" s="4">
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="1">
+        <v>3</v>
+      </c>
+      <c r="D10" s="3">
         <v>1.7717362327830701E-4</v>
       </c>
-      <c r="E10" s="1"/>
+      <c r="E10" s="6"/>
       <c r="F10" s="7"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1">
+      <c r="A11" s="6"/>
+      <c r="B11" s="6">
         <v>0.8</v>
       </c>
-      <c r="C11" s="2">
-        <v>1</v>
-      </c>
-      <c r="D11" s="4">
+      <c r="C11" s="1">
+        <v>1</v>
+      </c>
+      <c r="D11" s="3">
         <v>1.1074035510559501E-3</v>
       </c>
       <c r="E11" s="5">
@@ -792,31 +861,36 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="2">
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="1">
         <v>2</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="3">
         <v>3.1072735918849998E-6</v>
       </c>
-      <c r="E12" s="1"/>
+      <c r="E12" s="6"/>
       <c r="F12" s="7"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="2">
-        <v>3</v>
-      </c>
-      <c r="D13" s="4">
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="1">
+        <v>3</v>
+      </c>
+      <c r="D13" s="3">
         <v>7.2416775178600003E-6</v>
       </c>
-      <c r="E13" s="1"/>
+      <c r="E13" s="6"/>
       <c r="F13" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A2:A13"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="B11:B13"/>
     <mergeCell ref="E2:E4"/>
     <mergeCell ref="E5:E7"/>
     <mergeCell ref="E8:E10"/>
@@ -825,11 +899,6 @@
     <mergeCell ref="F5:F7"/>
     <mergeCell ref="F8:F10"/>
     <mergeCell ref="F11:F13"/>
-    <mergeCell ref="A2:A13"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="B11:B13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -847,34 +916,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.6" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="3"/>
+      <c r="F1" s="2"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="6">
         <v>0.2</v>
       </c>
-      <c r="C2" s="2">
-        <v>1</v>
-      </c>
-      <c r="D2" s="4">
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3">
         <v>6.0960731897987297E-4</v>
       </c>
       <c r="E2" s="5">
@@ -886,38 +955,38 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="2">
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="1">
         <v>2</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="4">
         <v>1.2366666655837901E-3</v>
       </c>
-      <c r="E3" s="1"/>
+      <c r="E3" s="6"/>
       <c r="F3" s="7"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="2">
-        <v>3</v>
-      </c>
-      <c r="D4" s="4">
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="1">
+        <v>3</v>
+      </c>
+      <c r="D4" s="3">
         <v>1.16827424905807E-4</v>
       </c>
-      <c r="E4" s="1"/>
+      <c r="E4" s="6"/>
       <c r="F4" s="7"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1">
+      <c r="A5" s="6"/>
+      <c r="B5" s="6">
         <v>0.4</v>
       </c>
-      <c r="C5" s="2">
-        <v>1</v>
-      </c>
-      <c r="D5" s="6">
+      <c r="C5" s="1">
+        <v>1</v>
+      </c>
+      <c r="D5" s="4">
         <v>1.05738310578603E-3</v>
       </c>
       <c r="E5" s="5">
@@ -929,38 +998,38 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="2">
+      <c r="A6" s="6"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="1">
         <v>2</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="4">
         <v>9.1605188150462502E-4</v>
       </c>
-      <c r="E6" s="1"/>
+      <c r="E6" s="6"/>
       <c r="F6" s="7"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="2">
-        <v>3</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="A7" s="6"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="1">
+        <v>3</v>
+      </c>
+      <c r="D7" s="4">
         <v>1.03197048005576E-3</v>
       </c>
-      <c r="E7" s="1"/>
+      <c r="E7" s="6"/>
       <c r="F7" s="7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1">
+      <c r="A8" s="6"/>
+      <c r="B8" s="6">
         <v>0.6</v>
       </c>
-      <c r="C8" s="2">
-        <v>1</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="1">
+        <v>1</v>
+      </c>
+      <c r="D8" s="4">
         <v>8.5958764850758399E-4</v>
       </c>
       <c r="E8" s="5">
@@ -972,38 +1041,38 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="2">
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="1">
         <v>2</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="3">
         <v>1.9315911817009E-5</v>
       </c>
-      <c r="E9" s="1"/>
+      <c r="E9" s="6"/>
       <c r="F9" s="7"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="2">
-        <v>3</v>
-      </c>
-      <c r="D10" s="4">
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="1">
+        <v>3</v>
+      </c>
+      <c r="D10" s="3">
         <v>1.7717362327830701E-4</v>
       </c>
-      <c r="E10" s="1"/>
+      <c r="E10" s="6"/>
       <c r="F10" s="7"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1">
+      <c r="A11" s="6"/>
+      <c r="B11" s="6">
         <v>0.8</v>
       </c>
-      <c r="C11" s="2">
-        <v>1</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="1">
+        <v>1</v>
+      </c>
+      <c r="D11" s="4">
         <v>2.59495713031E-7</v>
       </c>
       <c r="E11" s="5">
@@ -1015,27 +1084,234 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="2">
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="1">
         <v>2</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="4">
         <v>3.1072735918849998E-6</v>
       </c>
-      <c r="E12" s="1"/>
+      <c r="E12" s="6"/>
       <c r="F12" s="7"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="2">
-        <v>3</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="1">
+        <v>3</v>
+      </c>
+      <c r="D13" s="4">
         <v>7.2416775178600003E-6</v>
       </c>
-      <c r="E13" s="1"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="7"/>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="E11:E13"/>
+    <mergeCell ref="F11:F13"/>
+    <mergeCell ref="A2:A13"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="F2:F4"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="E5:E7"/>
+    <mergeCell ref="F5:F7"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="E8:E10"/>
+    <mergeCell ref="F8:F10"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E0F3467-3308-40E3-97FC-BEFD81780136}">
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="22.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="2"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="8">
+        <v>1.10536709177707E-3</v>
+      </c>
+      <c r="E2" s="5">
+        <f>AVERAGE(D2:D4)</f>
+        <v>1.10536709177707E-3</v>
+      </c>
+      <c r="F2" s="7">
+        <v>1.1000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="1">
+        <v>2</v>
+      </c>
+      <c r="D3" s="8"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="7"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="1">
+        <v>3</v>
+      </c>
+      <c r="D4" s="8"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="7"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="6"/>
+      <c r="B5" s="6">
+        <v>0.4</v>
+      </c>
+      <c r="C5" s="1">
+        <v>1</v>
+      </c>
+      <c r="D5" s="8">
+        <v>8.6130823085382702E-4</v>
+      </c>
+      <c r="E5" s="5">
+        <f>AVERAGE(D5:D7)</f>
+        <v>8.6130823085382702E-4</v>
+      </c>
+      <c r="F5" s="7">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="6"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="1">
+        <v>2</v>
+      </c>
+      <c r="D6" s="8"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="7"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="6"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="1">
+        <v>3</v>
+      </c>
+      <c r="D7" s="8"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="7"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="6"/>
+      <c r="B8" s="6">
+        <v>0.6</v>
+      </c>
+      <c r="C8" s="1">
+        <v>1</v>
+      </c>
+      <c r="D8" s="8">
+        <v>9.1338658759890896E-4</v>
+      </c>
+      <c r="E8" s="5">
+        <f>AVERAGE(D8:D10)</f>
+        <v>9.1338658759890896E-4</v>
+      </c>
+      <c r="F8" s="7">
+        <v>8.0000000000000004E-4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="1">
+        <v>2</v>
+      </c>
+      <c r="D9" s="8"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="7"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="1">
+        <v>3</v>
+      </c>
+      <c r="D10" s="8"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="7"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="6"/>
+      <c r="B11" s="6">
+        <v>0.8</v>
+      </c>
+      <c r="C11" s="1">
+        <v>1</v>
+      </c>
+      <c r="D11" s="8">
+        <v>7.3798692719643404E-4</v>
+      </c>
+      <c r="E11" s="5">
+        <f>AVERAGE(D11:D13)</f>
+        <v>7.3798692719643404E-4</v>
+      </c>
+      <c r="F11" s="7">
+        <v>6.9999999999999999E-4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="1">
+        <v>2</v>
+      </c>
+      <c r="D12" s="8"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="7"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="1">
+        <v>3</v>
+      </c>
+      <c r="D13" s="8"/>
+      <c r="E13" s="6"/>
       <c r="F13" s="7"/>
     </row>
   </sheetData>

--- a/_resultados/_resultados.xlsx
+++ b/_resultados/_resultados.xlsx
@@ -8,14 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ravar\Documents\GitHub\recsys-fair-federation-flower\_resultados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25D1090B-01FA-47E8-B12C-FE77CD50F7D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B598F4C9-D16E-496C-AA78-92467A1865EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="7B-Backup" sheetId="1" r:id="rId1"/>
     <sheet name="7B" sheetId="2" r:id="rId2"/>
-    <sheet name="7M" sheetId="3" r:id="rId3"/>
+    <sheet name="7F" sheetId="6" r:id="rId3"/>
+    <sheet name="7M" sheetId="3" r:id="rId4"/>
+    <sheet name="7N" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="12">
   <si>
     <t>Estratégia</t>
   </si>
@@ -118,6 +120,57 @@
   <si>
     <t>7M</t>
   </si>
+  <si>
+    <t>7N</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">fairness_penalty = </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>loss</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> * (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>lambda_fairness</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> + normalized_variance)</t>
+    </r>
+  </si>
+  <si>
+    <t>fairness_penalty = diff_loss_global_mean * (lambda_fairness + normalized_variance)</t>
+  </si>
+  <si>
+    <t>7B</t>
+  </si>
+  <si>
+    <t>fairness_penalty = (group_mean_loss) * (lambda_fairness + normalized_variance)</t>
+  </si>
 </sst>
 </file>
 
@@ -127,7 +180,7 @@
     <numFmt numFmtId="164" formatCode="0.000000000000000000"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -159,8 +212,19 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -182,6 +246,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -213,7 +289,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -221,16 +297,23 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -384,7 +467,123 @@
         <xdr:cNvPr id="2" name="Gráfico 1" descr="Contorno de rosto rindo com preenchimento sólido">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{405FEE2D-D816-4B54-A4AC-D153B027F7FA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId2"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5669282" y="11723"/>
+          <a:ext cx="180000" cy="180000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>685802</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>11723</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>865802</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>191723</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Gráfico 1" descr="Contorno de rosto rindo com preenchimento sólido">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B28B2AC1-C8AF-4709-875B-ACACC927C7D4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId2"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5669282" y="11723"/>
+          <a:ext cx="180000" cy="180000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>685802</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>11723</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>865802</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>191723</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Gráfico 1" descr="Contorno de rosto rindo com preenchimento sólido">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D074DB1-D78D-4B46-B6DB-428F04FAFBA8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -723,11 +922,11 @@
       <c r="D2" s="3">
         <v>6.0960731897987297E-4</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="7">
         <f>AVERAGE(D2:D4)</f>
         <v>6.5436713648982334E-4</v>
       </c>
-      <c r="F2" s="7">
+      <c r="F2" s="8">
         <v>1.1999999999999999E-3</v>
       </c>
     </row>
@@ -741,7 +940,7 @@
         <v>1.2366666655837901E-3</v>
       </c>
       <c r="E3" s="6"/>
-      <c r="F3" s="7"/>
+      <c r="F3" s="8"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="6"/>
@@ -753,7 +952,7 @@
         <v>1.16827424905807E-4</v>
       </c>
       <c r="E4" s="6"/>
-      <c r="F4" s="7"/>
+      <c r="F4" s="8"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="6"/>
@@ -766,11 +965,11 @@
       <c r="D5" s="4">
         <v>1.05738310578603E-3</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="7">
         <f>AVERAGE(D5:D7)</f>
         <v>9.3433828280417065E-4</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="8">
         <v>1E-3</v>
       </c>
     </row>
@@ -784,7 +983,7 @@
         <v>7.1366126257072198E-4</v>
       </c>
       <c r="E6" s="6"/>
-      <c r="F6" s="7"/>
+      <c r="F6" s="8"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="6"/>
@@ -796,7 +995,7 @@
         <v>1.03197048005576E-3</v>
       </c>
       <c r="E7" s="6"/>
-      <c r="F7" s="7"/>
+      <c r="F7" s="8"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="6"/>
@@ -809,11 +1008,11 @@
       <c r="D8" s="4">
         <v>8.5958764850758399E-4</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="7">
         <f>AVERAGE(D8:D10)</f>
         <v>3.5202572786763336E-4</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="8">
         <v>8.0000000000000004E-4</v>
       </c>
     </row>
@@ -827,7 +1026,7 @@
         <v>1.9315911817009E-5</v>
       </c>
       <c r="E9" s="6"/>
-      <c r="F9" s="7"/>
+      <c r="F9" s="8"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="6"/>
@@ -839,7 +1038,7 @@
         <v>1.7717362327830701E-4</v>
       </c>
       <c r="E10" s="6"/>
-      <c r="F10" s="7"/>
+      <c r="F10" s="8"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="6"/>
@@ -852,11 +1051,11 @@
       <c r="D11" s="3">
         <v>1.1074035510559501E-3</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="7">
         <f>AVERAGE(D11:D13)</f>
         <v>3.7258416738856505E-4</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="8">
         <v>4.0000000000000002E-4</v>
       </c>
     </row>
@@ -870,7 +1069,7 @@
         <v>3.1072735918849998E-6</v>
       </c>
       <c r="E12" s="6"/>
-      <c r="F12" s="7"/>
+      <c r="F12" s="8"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="6"/>
@@ -882,15 +1081,10 @@
         <v>7.2416775178600003E-6</v>
       </c>
       <c r="E13" s="6"/>
-      <c r="F13" s="7"/>
+      <c r="F13" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A2:A13"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="B11:B13"/>
     <mergeCell ref="E2:E4"/>
     <mergeCell ref="E5:E7"/>
     <mergeCell ref="E8:E10"/>
@@ -899,6 +1093,11 @@
     <mergeCell ref="F5:F7"/>
     <mergeCell ref="F8:F10"/>
     <mergeCell ref="F11:F13"/>
+    <mergeCell ref="A2:A13"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="B11:B13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -908,7 +1107,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2024553D-A159-4997-B349-D1047B0C901E}">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
@@ -946,11 +1145,11 @@
       <c r="D2" s="3">
         <v>6.0960731897987297E-4</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="7">
         <f>AVERAGE(D2:D4)</f>
         <v>6.5436713648982334E-4</v>
       </c>
-      <c r="F2" s="7">
+      <c r="F2" s="8">
         <v>1.1999999999999999E-3</v>
       </c>
     </row>
@@ -964,7 +1163,7 @@
         <v>1.2366666655837901E-3</v>
       </c>
       <c r="E3" s="6"/>
-      <c r="F3" s="7"/>
+      <c r="F3" s="8"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="6"/>
@@ -976,7 +1175,7 @@
         <v>1.16827424905807E-4</v>
       </c>
       <c r="E4" s="6"/>
-      <c r="F4" s="7"/>
+      <c r="F4" s="8"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="6"/>
@@ -989,11 +1188,11 @@
       <c r="D5" s="4">
         <v>1.05738310578603E-3</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="7">
         <f>AVERAGE(D5:D7)</f>
         <v>1.0018018224488051E-3</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="8">
         <v>1E-3</v>
       </c>
     </row>
@@ -1007,7 +1206,7 @@
         <v>9.1605188150462502E-4</v>
       </c>
       <c r="E6" s="6"/>
-      <c r="F6" s="7"/>
+      <c r="F6" s="8"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="6"/>
@@ -1019,7 +1218,7 @@
         <v>1.03197048005576E-3</v>
       </c>
       <c r="E7" s="6"/>
-      <c r="F7" s="7"/>
+      <c r="F7" s="8"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="6"/>
@@ -1032,11 +1231,11 @@
       <c r="D8" s="4">
         <v>8.5958764850758399E-4</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="7">
         <f>AVERAGE(D8:D10)</f>
         <v>3.5202572786763336E-4</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="8">
         <v>8.0000000000000004E-4</v>
       </c>
     </row>
@@ -1050,7 +1249,7 @@
         <v>1.9315911817009E-5</v>
       </c>
       <c r="E9" s="6"/>
-      <c r="F9" s="7"/>
+      <c r="F9" s="8"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="6"/>
@@ -1062,7 +1261,7 @@
         <v>1.7717362327830701E-4</v>
       </c>
       <c r="E10" s="6"/>
-      <c r="F10" s="7"/>
+      <c r="F10" s="8"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="6"/>
@@ -1075,11 +1274,11 @@
       <c r="D11" s="4">
         <v>2.59495713031E-7</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="7">
         <f>AVERAGE(D11:D13)</f>
         <v>3.5361489409253331E-6</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="8">
         <v>4.0000000000000002E-4</v>
       </c>
     </row>
@@ -1093,7 +1292,7 @@
         <v>3.1072735918849998E-6</v>
       </c>
       <c r="E12" s="6"/>
-      <c r="F12" s="7"/>
+      <c r="F12" s="8"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="6"/>
@@ -1105,10 +1304,21 @@
         <v>7.2416775178600003E-6</v>
       </c>
       <c r="E13" s="6"/>
-      <c r="F13" s="7"/>
+      <c r="F13" s="8"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="14">
+    <mergeCell ref="A15:F15"/>
     <mergeCell ref="B11:B13"/>
     <mergeCell ref="E11:E13"/>
     <mergeCell ref="F11:F13"/>
@@ -1130,8 +1340,8 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E0F3467-3308-40E3-97FC-BEFD81780136}">
-  <dimension ref="A1:F13"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEE152AD-4AE1-4932-A3B5-ECD57917F8C6}">
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
@@ -1158,7 +1368,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B2" s="6">
         <v>0.2</v>
@@ -1166,15 +1376,13 @@
       <c r="C2" s="1">
         <v>1</v>
       </c>
-      <c r="D2" s="8">
-        <v>1.10536709177707E-3</v>
-      </c>
-      <c r="E2" s="5">
+      <c r="D2" s="5"/>
+      <c r="E2" s="7" t="e">
         <f>AVERAGE(D2:D4)</f>
-        <v>1.10536709177707E-3</v>
-      </c>
-      <c r="F2" s="7">
-        <v>1.1000000000000001E-3</v>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F2" s="8">
+        <v>1.1999999999999999E-3</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -1183,9 +1391,9 @@
       <c r="C3" s="1">
         <v>2</v>
       </c>
-      <c r="D3" s="8"/>
+      <c r="D3" s="5"/>
       <c r="E3" s="6"/>
-      <c r="F3" s="7"/>
+      <c r="F3" s="8"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="6"/>
@@ -1193,9 +1401,9 @@
       <c r="C4" s="1">
         <v>3</v>
       </c>
-      <c r="D4" s="8"/>
+      <c r="D4" s="5"/>
       <c r="E4" s="6"/>
-      <c r="F4" s="7"/>
+      <c r="F4" s="8"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="6"/>
@@ -1205,14 +1413,12 @@
       <c r="C5" s="1">
         <v>1</v>
       </c>
-      <c r="D5" s="8">
-        <v>8.6130823085382702E-4</v>
-      </c>
-      <c r="E5" s="5">
+      <c r="D5" s="5"/>
+      <c r="E5" s="7" t="e">
         <f>AVERAGE(D5:D7)</f>
-        <v>8.6130823085382702E-4</v>
-      </c>
-      <c r="F5" s="7">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F5" s="8">
         <v>1E-3</v>
       </c>
     </row>
@@ -1222,9 +1428,9 @@
       <c r="C6" s="1">
         <v>2</v>
       </c>
-      <c r="D6" s="8"/>
+      <c r="D6" s="5"/>
       <c r="E6" s="6"/>
-      <c r="F6" s="7"/>
+      <c r="F6" s="8"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="6"/>
@@ -1232,9 +1438,9 @@
       <c r="C7" s="1">
         <v>3</v>
       </c>
-      <c r="D7" s="8"/>
+      <c r="D7" s="5"/>
       <c r="E7" s="6"/>
-      <c r="F7" s="7"/>
+      <c r="F7" s="8"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="6"/>
@@ -1244,14 +1450,12 @@
       <c r="C8" s="1">
         <v>1</v>
       </c>
-      <c r="D8" s="8">
-        <v>9.1338658759890896E-4</v>
-      </c>
-      <c r="E8" s="5">
+      <c r="D8" s="5"/>
+      <c r="E8" s="7" t="e">
         <f>AVERAGE(D8:D10)</f>
-        <v>9.1338658759890896E-4</v>
-      </c>
-      <c r="F8" s="7">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F8" s="8">
         <v>8.0000000000000004E-4</v>
       </c>
     </row>
@@ -1261,9 +1465,9 @@
       <c r="C9" s="1">
         <v>2</v>
       </c>
-      <c r="D9" s="8"/>
+      <c r="D9" s="5"/>
       <c r="E9" s="6"/>
-      <c r="F9" s="7"/>
+      <c r="F9" s="8"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="6"/>
@@ -1271,9 +1475,9 @@
       <c r="C10" s="1">
         <v>3</v>
       </c>
-      <c r="D10" s="8"/>
+      <c r="D10" s="5"/>
       <c r="E10" s="6"/>
-      <c r="F10" s="7"/>
+      <c r="F10" s="8"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="6"/>
@@ -1283,15 +1487,13 @@
       <c r="C11" s="1">
         <v>1</v>
       </c>
-      <c r="D11" s="8">
-        <v>7.3798692719643404E-4</v>
-      </c>
-      <c r="E11" s="5">
+      <c r="D11" s="5"/>
+      <c r="E11" s="7" t="e">
         <f>AVERAGE(D11:D13)</f>
-        <v>7.3798692719643404E-4</v>
-      </c>
-      <c r="F11" s="7">
-        <v>6.9999999999999999E-4</v>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F11" s="8">
+        <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -1300,9 +1502,9 @@
       <c r="C12" s="1">
         <v>2</v>
       </c>
-      <c r="D12" s="8"/>
+      <c r="D12" s="5"/>
       <c r="E12" s="6"/>
-      <c r="F12" s="7"/>
+      <c r="F12" s="8"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="6"/>
@@ -1310,12 +1512,255 @@
       <c r="C13" s="1">
         <v>3</v>
       </c>
-      <c r="D13" s="8"/>
+      <c r="D13" s="5"/>
       <c r="E13" s="6"/>
-      <c r="F13" s="7"/>
+      <c r="F13" s="8"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="14">
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="E11:E13"/>
+    <mergeCell ref="F11:F13"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A2:A13"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="F2:F4"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="E5:E7"/>
+    <mergeCell ref="F5:F7"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="E8:E10"/>
+    <mergeCell ref="F8:F10"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E0F3467-3308-40E3-97FC-BEFD81780136}">
+  <dimension ref="A1:H15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="22.77734375" customWidth="1"/>
+    <col min="8" max="8" width="27" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="2"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="5">
+        <v>1.10536709177707E-3</v>
+      </c>
+      <c r="E2" s="7">
+        <f>AVERAGE(D2:D4)</f>
+        <v>1.1309055570820001E-3</v>
+      </c>
+      <c r="F2" s="8">
+        <v>1.1000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="11"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="1">
+        <v>2</v>
+      </c>
+      <c r="D3" s="5">
+        <v>1.1564440223869299E-3</v>
+      </c>
+      <c r="E3" s="6"/>
+      <c r="F3" s="8"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="11"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="1">
+        <v>3</v>
+      </c>
+      <c r="D4" s="5"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="8"/>
+      <c r="H4" s="5">
+        <v>1.0454979313277799E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="11"/>
+      <c r="B5" s="6">
+        <v>0.4</v>
+      </c>
+      <c r="C5" s="1">
+        <v>1</v>
+      </c>
+      <c r="D5" s="5">
+        <v>8.6130823085382702E-4</v>
+      </c>
+      <c r="E5" s="7">
+        <f>AVERAGE(D5:D7)</f>
+        <v>9.6691710734251137E-4</v>
+      </c>
+      <c r="F5" s="8">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="11"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="1">
+        <v>2</v>
+      </c>
+      <c r="D6" s="5">
+        <v>1.14094976896151E-3</v>
+      </c>
+      <c r="E6" s="6"/>
+      <c r="F6" s="8"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="11"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="1">
+        <v>3</v>
+      </c>
+      <c r="D7" s="5">
+        <v>8.9849332221219702E-4</v>
+      </c>
+      <c r="E7" s="6"/>
+      <c r="F7" s="8"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="11"/>
+      <c r="B8" s="6">
+        <v>0.6</v>
+      </c>
+      <c r="C8" s="1">
+        <v>1</v>
+      </c>
+      <c r="D8" s="5">
+        <v>9.1338658759890896E-4</v>
+      </c>
+      <c r="E8" s="7">
+        <f>AVERAGE(D8:D10)</f>
+        <v>8.8801660113643126E-4</v>
+      </c>
+      <c r="F8" s="8">
+        <v>8.0000000000000004E-4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="11"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="1">
+        <v>2</v>
+      </c>
+      <c r="D9" s="9">
+        <v>9.8614258166756607E-4</v>
+      </c>
+      <c r="E9" s="6"/>
+      <c r="F9" s="8"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="11"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="1">
+        <v>3</v>
+      </c>
+      <c r="D10" s="5">
+        <v>7.6452063414281896E-4</v>
+      </c>
+      <c r="E10" s="6"/>
+      <c r="F10" s="8"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="11"/>
+      <c r="B11" s="6">
+        <v>0.8</v>
+      </c>
+      <c r="C11" s="1">
+        <v>1</v>
+      </c>
+      <c r="D11" s="5">
+        <v>7.3798692719643404E-4</v>
+      </c>
+      <c r="E11" s="7">
+        <f>AVERAGE(D11:D13)</f>
+        <v>7.3798692719643404E-4</v>
+      </c>
+      <c r="F11" s="8">
+        <v>6.9999999999999999E-4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="11"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="1">
+        <v>2</v>
+      </c>
+      <c r="D12" s="5"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="8"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" s="11"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="1">
+        <v>3</v>
+      </c>
+      <c r="D13" s="5"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="8"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A15:F15"/>
     <mergeCell ref="B11:B13"/>
     <mergeCell ref="E11:E13"/>
     <mergeCell ref="F11:F13"/>
@@ -1334,4 +1779,280 @@
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06AE1873-B58F-471C-B0A2-50D443D1B6D1}">
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="22.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="2"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="5">
+        <v>1.0456008086864E-3</v>
+      </c>
+      <c r="E2" s="7">
+        <f>AVERAGE(D2:D5)</f>
+        <v>1.062493548102375E-3</v>
+      </c>
+      <c r="F2" s="8">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="1">
+        <v>2</v>
+      </c>
+      <c r="D3" s="5">
+        <v>1.09467266122671E-3</v>
+      </c>
+      <c r="E3" s="6"/>
+      <c r="F3" s="8"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="1">
+        <v>3</v>
+      </c>
+      <c r="D4" s="5">
+        <v>1.0701604268465201E-3</v>
+      </c>
+      <c r="E4" s="6"/>
+      <c r="F4" s="8"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="6"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="1">
+        <v>4</v>
+      </c>
+      <c r="D5" s="5">
+        <v>1.0395402956498701E-3</v>
+      </c>
+      <c r="E5" s="6"/>
+      <c r="F5" s="8"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="6"/>
+      <c r="B6" s="6">
+        <v>0.4</v>
+      </c>
+      <c r="C6" s="1">
+        <v>1</v>
+      </c>
+      <c r="D6" s="5">
+        <v>1.3060672401840299E-3</v>
+      </c>
+      <c r="E6" s="7">
+        <f>AVERAGE(D6:D9)</f>
+        <v>1.0119003627781611E-3</v>
+      </c>
+      <c r="F6" s="8"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="6"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="1">
+        <v>2</v>
+      </c>
+      <c r="D7" s="5">
+        <v>9.3494025407098202E-4</v>
+      </c>
+      <c r="E7" s="6"/>
+      <c r="F7" s="8"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="1">
+        <v>3</v>
+      </c>
+      <c r="D8" s="5">
+        <v>1.11627799419256E-3</v>
+      </c>
+      <c r="E8" s="6"/>
+      <c r="F8" s="8"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="1">
+        <v>4</v>
+      </c>
+      <c r="D9" s="5">
+        <v>6.9031596266507205E-4</v>
+      </c>
+      <c r="E9" s="6"/>
+      <c r="F9" s="8"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="6"/>
+      <c r="B10" s="6">
+        <v>0.6</v>
+      </c>
+      <c r="C10" s="1">
+        <v>1</v>
+      </c>
+      <c r="D10" s="5">
+        <v>1.1258039438553501E-3</v>
+      </c>
+      <c r="E10" s="7">
+        <f>AVERAGE(D10:D13)</f>
+        <v>1.0913926731899966E-3</v>
+      </c>
+      <c r="F10" s="8"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="6"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="1">
+        <v>2</v>
+      </c>
+      <c r="D11" s="5">
+        <v>9.6767982546831603E-4</v>
+      </c>
+      <c r="E11" s="6"/>
+      <c r="F11" s="8"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="1">
+        <v>3</v>
+      </c>
+      <c r="D12" s="5">
+        <v>1.0759200072066801E-3</v>
+      </c>
+      <c r="E12" s="6"/>
+      <c r="F12" s="8"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="1">
+        <v>4</v>
+      </c>
+      <c r="D13" s="5">
+        <v>1.1961669162296399E-3</v>
+      </c>
+      <c r="E13" s="6"/>
+      <c r="F13" s="8"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="6"/>
+      <c r="B14" s="6">
+        <v>0.8</v>
+      </c>
+      <c r="C14" s="1">
+        <v>1</v>
+      </c>
+      <c r="D14" s="5">
+        <v>8.5667911779765201E-4</v>
+      </c>
+      <c r="E14" s="7">
+        <f>AVERAGE(D14:D17)</f>
+        <v>8.7466814763753067E-4</v>
+      </c>
+      <c r="F14" s="8"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="1">
+        <v>2</v>
+      </c>
+      <c r="D15" s="5">
+        <v>6.7159374136605899E-4</v>
+      </c>
+      <c r="E15" s="7"/>
+      <c r="F15" s="8"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="1">
+        <v>3</v>
+      </c>
+      <c r="D16" s="5">
+        <v>9.2119835353706196E-4</v>
+      </c>
+      <c r="E16" s="6"/>
+      <c r="F16" s="8"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="1">
+        <v>4</v>
+      </c>
+      <c r="D17" s="5">
+        <v>1.0492013778493499E-3</v>
+      </c>
+      <c r="E17" s="6"/>
+      <c r="F17" s="8"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="10"/>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="E14:E17"/>
+    <mergeCell ref="F14:F17"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A2:A17"/>
+    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="E2:E5"/>
+    <mergeCell ref="F2:F5"/>
+    <mergeCell ref="B6:B9"/>
+    <mergeCell ref="E6:E9"/>
+    <mergeCell ref="F6:F9"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="E10:E13"/>
+    <mergeCell ref="F10:F13"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>
--- a/_resultados/_resultados.xlsx
+++ b/_resultados/_resultados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ravar\Documents\GitHub\recsys-fair-federation-flower\_resultados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B598F4C9-D16E-496C-AA78-92467A1865EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF6B6769-DF5A-4443-9886-6F54385641BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="7B-Backup" sheetId="1" r:id="rId1"/>
@@ -298,16 +298,16 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -910,10 +910,10 @@
       <c r="F1" s="2"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="6">
+      <c r="A2" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="8">
         <v>0.2</v>
       </c>
       <c r="C2" s="1">
@@ -926,37 +926,37 @@
         <f>AVERAGE(D2:D4)</f>
         <v>6.5436713648982334E-4</v>
       </c>
-      <c r="F2" s="8">
+      <c r="F2" s="9">
         <v>1.1999999999999999E-3</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6"/>
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
       <c r="D3" s="4">
         <v>1.2366666655837901E-3</v>
       </c>
-      <c r="E3" s="6"/>
-      <c r="F3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="9"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
       <c r="D4" s="3">
         <v>1.16827424905807E-4</v>
       </c>
-      <c r="E4" s="6"/>
-      <c r="F4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="9"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6">
+      <c r="A5" s="8"/>
+      <c r="B5" s="8">
         <v>0.4</v>
       </c>
       <c r="C5" s="1">
@@ -969,37 +969,37 @@
         <f>AVERAGE(D5:D7)</f>
         <v>9.3433828280417065E-4</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="9">
         <v>1E-3</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6"/>
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
       <c r="C6" s="1">
         <v>2</v>
       </c>
       <c r="D6" s="3">
         <v>7.1366126257072198E-4</v>
       </c>
-      <c r="E6" s="6"/>
-      <c r="F6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="9"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6"/>
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
       <c r="C7" s="1">
         <v>3</v>
       </c>
       <c r="D7" s="4">
         <v>1.03197048005576E-3</v>
       </c>
-      <c r="E7" s="6"/>
-      <c r="F7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="9"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6">
+      <c r="A8" s="8"/>
+      <c r="B8" s="8">
         <v>0.6</v>
       </c>
       <c r="C8" s="1">
@@ -1012,37 +1012,37 @@
         <f>AVERAGE(D8:D10)</f>
         <v>3.5202572786763336E-4</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="9">
         <v>8.0000000000000004E-4</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
       <c r="C9" s="1">
         <v>2</v>
       </c>
       <c r="D9" s="3">
         <v>1.9315911817009E-5</v>
       </c>
-      <c r="E9" s="6"/>
-      <c r="F9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
       <c r="C10" s="1">
         <v>3</v>
       </c>
       <c r="D10" s="3">
         <v>1.7717362327830701E-4</v>
       </c>
-      <c r="E10" s="6"/>
-      <c r="F10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="9"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8">
         <v>0.8</v>
       </c>
       <c r="C11" s="1">
@@ -1055,36 +1055,41 @@
         <f>AVERAGE(D11:D13)</f>
         <v>3.7258416738856505E-4</v>
       </c>
-      <c r="F11" s="8">
+      <c r="F11" s="9">
         <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
       <c r="C12" s="1">
         <v>2</v>
       </c>
       <c r="D12" s="3">
         <v>3.1072735918849998E-6</v>
       </c>
-      <c r="E12" s="6"/>
-      <c r="F12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="9"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
       <c r="C13" s="1">
         <v>3</v>
       </c>
       <c r="D13" s="3">
         <v>7.2416775178600003E-6</v>
       </c>
-      <c r="E13" s="6"/>
-      <c r="F13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A2:A13"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="B11:B13"/>
     <mergeCell ref="E2:E4"/>
     <mergeCell ref="E5:E7"/>
     <mergeCell ref="E8:E10"/>
@@ -1093,11 +1098,6 @@
     <mergeCell ref="F5:F7"/>
     <mergeCell ref="F8:F10"/>
     <mergeCell ref="F11:F13"/>
-    <mergeCell ref="A2:A13"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="B11:B13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1133,10 +1133,10 @@
       <c r="F1" s="2"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="6">
+      <c r="A2" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="8">
         <v>0.2</v>
       </c>
       <c r="C2" s="1">
@@ -1149,37 +1149,37 @@
         <f>AVERAGE(D2:D4)</f>
         <v>6.5436713648982334E-4</v>
       </c>
-      <c r="F2" s="8">
+      <c r="F2" s="9">
         <v>1.1999999999999999E-3</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6"/>
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
       <c r="D3" s="4">
         <v>1.2366666655837901E-3</v>
       </c>
-      <c r="E3" s="6"/>
-      <c r="F3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="9"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
       <c r="D4" s="3">
         <v>1.16827424905807E-4</v>
       </c>
-      <c r="E4" s="6"/>
-      <c r="F4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="9"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6">
+      <c r="A5" s="8"/>
+      <c r="B5" s="8">
         <v>0.4</v>
       </c>
       <c r="C5" s="1">
@@ -1192,37 +1192,37 @@
         <f>AVERAGE(D5:D7)</f>
         <v>1.0018018224488051E-3</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="9">
         <v>1E-3</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6"/>
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
       <c r="C6" s="1">
         <v>2</v>
       </c>
       <c r="D6" s="4">
         <v>9.1605188150462502E-4</v>
       </c>
-      <c r="E6" s="6"/>
-      <c r="F6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="9"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6"/>
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
       <c r="C7" s="1">
         <v>3</v>
       </c>
       <c r="D7" s="4">
         <v>1.03197048005576E-3</v>
       </c>
-      <c r="E7" s="6"/>
-      <c r="F7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="9"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6">
+      <c r="A8" s="8"/>
+      <c r="B8" s="8">
         <v>0.6</v>
       </c>
       <c r="C8" s="1">
@@ -1235,37 +1235,37 @@
         <f>AVERAGE(D8:D10)</f>
         <v>3.5202572786763336E-4</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="9">
         <v>8.0000000000000004E-4</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
       <c r="C9" s="1">
         <v>2</v>
       </c>
       <c r="D9" s="3">
         <v>1.9315911817009E-5</v>
       </c>
-      <c r="E9" s="6"/>
-      <c r="F9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
       <c r="C10" s="1">
         <v>3</v>
       </c>
       <c r="D10" s="3">
         <v>1.7717362327830701E-4</v>
       </c>
-      <c r="E10" s="6"/>
-      <c r="F10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="9"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8">
         <v>0.8</v>
       </c>
       <c r="C11" s="1">
@@ -1278,33 +1278,33 @@
         <f>AVERAGE(D11:D13)</f>
         <v>3.5361489409253331E-6</v>
       </c>
-      <c r="F11" s="8">
+      <c r="F11" s="9">
         <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
       <c r="C12" s="1">
         <v>2</v>
       </c>
       <c r="D12" s="4">
         <v>3.1072735918849998E-6</v>
       </c>
-      <c r="E12" s="6"/>
-      <c r="F12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="9"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
       <c r="C13" s="1">
         <v>3</v>
       </c>
       <c r="D13" s="4">
         <v>7.2416775178600003E-6</v>
       </c>
-      <c r="E13" s="6"/>
-      <c r="F13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="9"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="10" t="s">
@@ -1367,10 +1367,10 @@
       <c r="F1" s="2"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="8">
         <v>0.2</v>
       </c>
       <c r="C2" s="1">
@@ -1381,33 +1381,33 @@
         <f>AVERAGE(D2:D4)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F2" s="8">
+      <c r="F2" s="9">
         <v>1.1999999999999999E-3</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6"/>
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
       <c r="D3" s="5"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="9"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
       <c r="D4" s="5"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="9"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6">
+      <c r="A5" s="8"/>
+      <c r="B5" s="8">
         <v>0.4</v>
       </c>
       <c r="C5" s="1">
@@ -1418,33 +1418,33 @@
         <f>AVERAGE(D5:D7)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="9">
         <v>1E-3</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6"/>
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
       <c r="C6" s="1">
         <v>2</v>
       </c>
       <c r="D6" s="5"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="9"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6"/>
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
       <c r="C7" s="1">
         <v>3</v>
       </c>
       <c r="D7" s="5"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="9"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6">
+      <c r="A8" s="8"/>
+      <c r="B8" s="8">
         <v>0.6</v>
       </c>
       <c r="C8" s="1">
@@ -1455,33 +1455,33 @@
         <f>AVERAGE(D8:D10)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="9">
         <v>8.0000000000000004E-4</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
       <c r="C9" s="1">
         <v>2</v>
       </c>
       <c r="D9" s="5"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
       <c r="C10" s="1">
         <v>3</v>
       </c>
       <c r="D10" s="5"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="9"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8">
         <v>0.8</v>
       </c>
       <c r="C11" s="1">
@@ -1492,29 +1492,29 @@
         <f>AVERAGE(D11:D13)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F11" s="8">
+      <c r="F11" s="9">
         <v>4.0000000000000002E-4</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
       <c r="C12" s="1">
         <v>2</v>
       </c>
       <c r="D12" s="5"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="9"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
       <c r="C13" s="1">
         <v>3</v>
       </c>
       <c r="D13" s="5"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="9"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="10" t="s">
@@ -1581,7 +1581,7 @@
       <c r="A2" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="8">
         <v>0.2</v>
       </c>
       <c r="C2" s="1">
@@ -1594,38 +1594,38 @@
         <f>AVERAGE(D2:D4)</f>
         <v>1.1309055570820001E-3</v>
       </c>
-      <c r="F2" s="8">
+      <c r="F2" s="9">
         <v>1.1000000000000001E-3</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="11"/>
-      <c r="B3" s="6"/>
+      <c r="B3" s="8"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
       <c r="D3" s="5">
         <v>1.1564440223869299E-3</v>
       </c>
-      <c r="E3" s="6"/>
-      <c r="F3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="9"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="11"/>
-      <c r="B4" s="6"/>
+      <c r="B4" s="8"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
       <c r="D4" s="5"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="9"/>
       <c r="H4" s="5">
         <v>1.0454979313277799E-3</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="11"/>
-      <c r="B5" s="6">
+      <c r="B5" s="8">
         <v>0.4</v>
       </c>
       <c r="C5" s="1">
@@ -1638,37 +1638,37 @@
         <f>AVERAGE(D5:D7)</f>
         <v>9.6691710734251137E-4</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="9">
         <v>1E-3</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="11"/>
-      <c r="B6" s="6"/>
+      <c r="B6" s="8"/>
       <c r="C6" s="1">
         <v>2</v>
       </c>
       <c r="D6" s="5">
         <v>1.14094976896151E-3</v>
       </c>
-      <c r="E6" s="6"/>
-      <c r="F6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="9"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="11"/>
-      <c r="B7" s="6"/>
+      <c r="B7" s="8"/>
       <c r="C7" s="1">
         <v>3</v>
       </c>
       <c r="D7" s="5">
         <v>8.9849332221219702E-4</v>
       </c>
-      <c r="E7" s="6"/>
-      <c r="F7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="9"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="11"/>
-      <c r="B8" s="6">
+      <c r="B8" s="8">
         <v>0.6</v>
       </c>
       <c r="C8" s="1">
@@ -1681,37 +1681,37 @@
         <f>AVERAGE(D8:D10)</f>
         <v>8.8801660113643126E-4</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="9">
         <v>8.0000000000000004E-4</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="11"/>
-      <c r="B9" s="6"/>
+      <c r="B9" s="8"/>
       <c r="C9" s="1">
         <v>2</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="6">
         <v>9.8614258166756607E-4</v>
       </c>
-      <c r="E9" s="6"/>
-      <c r="F9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="9"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="11"/>
-      <c r="B10" s="6"/>
+      <c r="B10" s="8"/>
       <c r="C10" s="1">
         <v>3</v>
       </c>
       <c r="D10" s="5">
         <v>7.6452063414281896E-4</v>
       </c>
-      <c r="E10" s="6"/>
-      <c r="F10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="9"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="11"/>
-      <c r="B11" s="6">
+      <c r="B11" s="8">
         <v>0.8</v>
       </c>
       <c r="C11" s="1">
@@ -1724,29 +1724,29 @@
         <f>AVERAGE(D11:D13)</f>
         <v>7.3798692719643404E-4</v>
       </c>
-      <c r="F11" s="8">
+      <c r="F11" s="9">
         <v>6.9999999999999999E-4</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="11"/>
-      <c r="B12" s="6"/>
+      <c r="B12" s="8"/>
       <c r="C12" s="1">
         <v>2</v>
       </c>
       <c r="D12" s="5"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="9"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="11"/>
-      <c r="B13" s="6"/>
+      <c r="B13" s="8"/>
       <c r="C13" s="1">
         <v>3</v>
       </c>
       <c r="D13" s="5"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="9"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="10" t="s">
@@ -1809,10 +1809,10 @@
       <c r="F1" s="2"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="8">
         <v>0.2</v>
       </c>
       <c r="C2" s="1">
@@ -1825,49 +1825,49 @@
         <f>AVERAGE(D2:D5)</f>
         <v>1.062493548102375E-3</v>
       </c>
-      <c r="F2" s="8">
-        <v>1E-3</v>
+      <c r="F2" s="9">
+        <v>1.08E-3</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6"/>
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="4">
         <v>1.09467266122671E-3</v>
       </c>
-      <c r="E3" s="6"/>
-      <c r="F3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="9"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="4">
         <v>1.0701604268465201E-3</v>
       </c>
-      <c r="E4" s="6"/>
-      <c r="F4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="9"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6"/>
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
       <c r="C5" s="1">
         <v>4</v>
       </c>
       <c r="D5" s="5">
         <v>1.0395402956498701E-3</v>
       </c>
-      <c r="E5" s="6"/>
-      <c r="F5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="9"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6">
+      <c r="A6" s="8"/>
+      <c r="B6" s="8">
         <v>0.4</v>
       </c>
       <c r="C6" s="1">
@@ -1880,47 +1880,49 @@
         <f>AVERAGE(D6:D9)</f>
         <v>1.0119003627781611E-3</v>
       </c>
-      <c r="F6" s="8"/>
+      <c r="F6" s="9">
+        <v>1E-3</v>
+      </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6"/>
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
       <c r="C7" s="1">
         <v>2</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="4">
         <v>9.3494025407098202E-4</v>
       </c>
-      <c r="E7" s="6"/>
-      <c r="F7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="9"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
       <c r="C8" s="1">
         <v>3</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="4">
         <v>1.11627799419256E-3</v>
       </c>
-      <c r="E8" s="6"/>
-      <c r="F8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="9"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
       <c r="C9" s="1">
         <v>4</v>
       </c>
       <c r="D9" s="5">
         <v>6.9031596266507205E-4</v>
       </c>
-      <c r="E9" s="6"/>
-      <c r="F9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6">
+      <c r="A10" s="8"/>
+      <c r="B10" s="8">
         <v>0.6</v>
       </c>
       <c r="C10" s="1">
@@ -1933,96 +1935,100 @@
         <f>AVERAGE(D10:D13)</f>
         <v>1.0913926731899966E-3</v>
       </c>
-      <c r="F10" s="8"/>
+      <c r="F10" s="9">
+        <v>8.9999999999999998E-4</v>
+      </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
       <c r="C11" s="1">
         <v>2</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11" s="4">
         <v>9.6767982546831603E-4</v>
       </c>
-      <c r="E11" s="6"/>
-      <c r="F11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="9"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
       <c r="C12" s="1">
         <v>3</v>
       </c>
       <c r="D12" s="5">
         <v>1.0759200072066801E-3</v>
       </c>
-      <c r="E12" s="6"/>
-      <c r="F12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="9"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
       <c r="C13" s="1">
         <v>4</v>
       </c>
       <c r="D13" s="5">
         <v>1.1961669162296399E-3</v>
       </c>
-      <c r="E13" s="6"/>
-      <c r="F13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="9"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6">
+      <c r="A14" s="8"/>
+      <c r="B14" s="8">
         <v>0.8</v>
       </c>
       <c r="C14" s="1">
         <v>1</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D14" s="4">
         <v>8.5667911779765201E-4</v>
       </c>
       <c r="E14" s="7">
         <f>AVERAGE(D14:D17)</f>
         <v>8.7466814763753067E-4</v>
       </c>
-      <c r="F14" s="8"/>
+      <c r="F14" s="9">
+        <v>6.9999999999999999E-4</v>
+      </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
       <c r="C15" s="1">
         <v>2</v>
       </c>
-      <c r="D15" s="5">
+      <c r="D15" s="4">
         <v>6.7159374136605899E-4</v>
       </c>
       <c r="E15" s="7"/>
-      <c r="F15" s="8"/>
+      <c r="F15" s="9"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
       <c r="C16" s="1">
         <v>3</v>
       </c>
       <c r="D16" s="5">
         <v>9.2119835353706196E-4</v>
       </c>
-      <c r="E16" s="6"/>
-      <c r="F16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="9"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
       <c r="C17" s="1">
         <v>4</v>
       </c>
       <c r="D17" s="5">
         <v>1.0492013778493499E-3</v>
       </c>
-      <c r="E17" s="6"/>
-      <c r="F17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="9"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">

--- a/_resultados/_resultados.xlsx
+++ b/_resultados/_resultados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ravar\Documents\GitHub\recsys-fair-federation-flower\_resultados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF6B6769-DF5A-4443-9886-6F54385641BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6611E20E-C382-47DB-BB7A-8B353C0B1D32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="7B-Backup" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="7F" sheetId="6" r:id="rId3"/>
     <sheet name="7M" sheetId="3" r:id="rId4"/>
     <sheet name="7N" sheetId="4" r:id="rId5"/>
+    <sheet name="7O" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="12">
   <si>
     <t>Estratégia</t>
   </si>
@@ -299,10 +300,10 @@
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -621,6 +622,64 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>685802</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>11723</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>865802</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>191723</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Gráfico 1" descr="Contorno de rosto rindo com preenchimento sólido">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8E6BCFDA-907F-4C6E-A798-6D6A235890B9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId2"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5669282" y="11723"/>
+          <a:ext cx="180000" cy="180000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -910,10 +969,10 @@
       <c r="F1" s="2"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="8">
+      <c r="A2" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="7">
         <v>0.2</v>
       </c>
       <c r="C2" s="1">
@@ -922,7 +981,7 @@
       <c r="D2" s="3">
         <v>6.0960731897987297E-4</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="8">
         <f>AVERAGE(D2:D4)</f>
         <v>6.5436713648982334E-4</v>
       </c>
@@ -931,32 +990,32 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
       <c r="D3" s="4">
         <v>1.2366666655837901E-3</v>
       </c>
-      <c r="E3" s="8"/>
+      <c r="E3" s="7"/>
       <c r="F3" s="9"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
       <c r="D4" s="3">
         <v>1.16827424905807E-4</v>
       </c>
-      <c r="E4" s="8"/>
+      <c r="E4" s="7"/>
       <c r="F4" s="9"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7">
         <v>0.4</v>
       </c>
       <c r="C5" s="1">
@@ -965,7 +1024,7 @@
       <c r="D5" s="4">
         <v>1.05738310578603E-3</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="8">
         <f>AVERAGE(D5:D7)</f>
         <v>9.3433828280417065E-4</v>
       </c>
@@ -974,32 +1033,32 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
       <c r="C6" s="1">
         <v>2</v>
       </c>
       <c r="D6" s="3">
         <v>7.1366126257072198E-4</v>
       </c>
-      <c r="E6" s="8"/>
+      <c r="E6" s="7"/>
       <c r="F6" s="9"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
       <c r="C7" s="1">
         <v>3</v>
       </c>
       <c r="D7" s="4">
         <v>1.03197048005576E-3</v>
       </c>
-      <c r="E7" s="8"/>
+      <c r="E7" s="7"/>
       <c r="F7" s="9"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8">
+      <c r="A8" s="7"/>
+      <c r="B8" s="7">
         <v>0.6</v>
       </c>
       <c r="C8" s="1">
@@ -1008,7 +1067,7 @@
       <c r="D8" s="4">
         <v>8.5958764850758399E-4</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="8">
         <f>AVERAGE(D8:D10)</f>
         <v>3.5202572786763336E-4</v>
       </c>
@@ -1017,32 +1076,32 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
       <c r="C9" s="1">
         <v>2</v>
       </c>
       <c r="D9" s="3">
         <v>1.9315911817009E-5</v>
       </c>
-      <c r="E9" s="8"/>
+      <c r="E9" s="7"/>
       <c r="F9" s="9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
       <c r="C10" s="1">
         <v>3</v>
       </c>
       <c r="D10" s="3">
         <v>1.7717362327830701E-4</v>
       </c>
-      <c r="E10" s="8"/>
+      <c r="E10" s="7"/>
       <c r="F10" s="9"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7">
         <v>0.8</v>
       </c>
       <c r="C11" s="1">
@@ -1051,7 +1110,7 @@
       <c r="D11" s="3">
         <v>1.1074035510559501E-3</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="8">
         <f>AVERAGE(D11:D13)</f>
         <v>3.7258416738856505E-4</v>
       </c>
@@ -1060,36 +1119,31 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
       <c r="C12" s="1">
         <v>2</v>
       </c>
       <c r="D12" s="3">
         <v>3.1072735918849998E-6</v>
       </c>
-      <c r="E12" s="8"/>
+      <c r="E12" s="7"/>
       <c r="F12" s="9"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
       <c r="C13" s="1">
         <v>3</v>
       </c>
       <c r="D13" s="3">
         <v>7.2416775178600003E-6</v>
       </c>
-      <c r="E13" s="8"/>
+      <c r="E13" s="7"/>
       <c r="F13" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A2:A13"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="B11:B13"/>
     <mergeCell ref="E2:E4"/>
     <mergeCell ref="E5:E7"/>
     <mergeCell ref="E8:E10"/>
@@ -1098,6 +1152,11 @@
     <mergeCell ref="F5:F7"/>
     <mergeCell ref="F8:F10"/>
     <mergeCell ref="F11:F13"/>
+    <mergeCell ref="A2:A13"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="B11:B13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1133,10 +1192,10 @@
       <c r="F1" s="2"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="8">
+      <c r="A2" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="7">
         <v>0.2</v>
       </c>
       <c r="C2" s="1">
@@ -1145,7 +1204,7 @@
       <c r="D2" s="3">
         <v>6.0960731897987297E-4</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="8">
         <f>AVERAGE(D2:D4)</f>
         <v>6.5436713648982334E-4</v>
       </c>
@@ -1154,32 +1213,32 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
       <c r="D3" s="4">
         <v>1.2366666655837901E-3</v>
       </c>
-      <c r="E3" s="8"/>
+      <c r="E3" s="7"/>
       <c r="F3" s="9"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
       <c r="D4" s="3">
         <v>1.16827424905807E-4</v>
       </c>
-      <c r="E4" s="8"/>
+      <c r="E4" s="7"/>
       <c r="F4" s="9"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7">
         <v>0.4</v>
       </c>
       <c r="C5" s="1">
@@ -1188,7 +1247,7 @@
       <c r="D5" s="4">
         <v>1.05738310578603E-3</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="8">
         <f>AVERAGE(D5:D7)</f>
         <v>1.0018018224488051E-3</v>
       </c>
@@ -1197,32 +1256,32 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
       <c r="C6" s="1">
         <v>2</v>
       </c>
       <c r="D6" s="4">
         <v>9.1605188150462502E-4</v>
       </c>
-      <c r="E6" s="8"/>
+      <c r="E6" s="7"/>
       <c r="F6" s="9"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
       <c r="C7" s="1">
         <v>3</v>
       </c>
       <c r="D7" s="4">
         <v>1.03197048005576E-3</v>
       </c>
-      <c r="E7" s="8"/>
+      <c r="E7" s="7"/>
       <c r="F7" s="9"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8">
+      <c r="A8" s="7"/>
+      <c r="B8" s="7">
         <v>0.6</v>
       </c>
       <c r="C8" s="1">
@@ -1231,7 +1290,7 @@
       <c r="D8" s="4">
         <v>8.5958764850758399E-4</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="8">
         <f>AVERAGE(D8:D10)</f>
         <v>3.5202572786763336E-4</v>
       </c>
@@ -1240,32 +1299,32 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
       <c r="C9" s="1">
         <v>2</v>
       </c>
       <c r="D9" s="3">
         <v>1.9315911817009E-5</v>
       </c>
-      <c r="E9" s="8"/>
+      <c r="E9" s="7"/>
       <c r="F9" s="9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
       <c r="C10" s="1">
         <v>3</v>
       </c>
       <c r="D10" s="3">
         <v>1.7717362327830701E-4</v>
       </c>
-      <c r="E10" s="8"/>
+      <c r="E10" s="7"/>
       <c r="F10" s="9"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7">
         <v>0.8</v>
       </c>
       <c r="C11" s="1">
@@ -1274,7 +1333,7 @@
       <c r="D11" s="4">
         <v>2.59495713031E-7</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="8">
         <f>AVERAGE(D11:D13)</f>
         <v>3.5361489409253331E-6</v>
       </c>
@@ -1283,27 +1342,27 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
       <c r="C12" s="1">
         <v>2</v>
       </c>
       <c r="D12" s="4">
         <v>3.1072735918849998E-6</v>
       </c>
-      <c r="E12" s="8"/>
+      <c r="E12" s="7"/>
       <c r="F12" s="9"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
       <c r="C13" s="1">
         <v>3</v>
       </c>
       <c r="D13" s="4">
         <v>7.2416775178600003E-6</v>
       </c>
-      <c r="E13" s="8"/>
+      <c r="E13" s="7"/>
       <c r="F13" s="9"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -1367,17 +1426,17 @@
       <c r="F1" s="2"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="8">
+      <c r="B2" s="7">
         <v>0.2</v>
       </c>
       <c r="C2" s="1">
         <v>1</v>
       </c>
       <c r="D2" s="5"/>
-      <c r="E2" s="7" t="e">
+      <c r="E2" s="8" t="e">
         <f>AVERAGE(D2:D4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -1386,35 +1445,35 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
       <c r="D3" s="5"/>
-      <c r="E3" s="8"/>
+      <c r="E3" s="7"/>
       <c r="F3" s="9"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
       <c r="D4" s="5"/>
-      <c r="E4" s="8"/>
+      <c r="E4" s="7"/>
       <c r="F4" s="9"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7">
         <v>0.4</v>
       </c>
       <c r="C5" s="1">
         <v>1</v>
       </c>
       <c r="D5" s="5"/>
-      <c r="E5" s="7" t="e">
+      <c r="E5" s="8" t="e">
         <f>AVERAGE(D5:D7)</f>
         <v>#DIV/0!</v>
       </c>
@@ -1423,35 +1482,35 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
       <c r="C6" s="1">
         <v>2</v>
       </c>
       <c r="D6" s="5"/>
-      <c r="E6" s="8"/>
+      <c r="E6" s="7"/>
       <c r="F6" s="9"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
       <c r="C7" s="1">
         <v>3</v>
       </c>
       <c r="D7" s="5"/>
-      <c r="E7" s="8"/>
+      <c r="E7" s="7"/>
       <c r="F7" s="9"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8">
+      <c r="A8" s="7"/>
+      <c r="B8" s="7">
         <v>0.6</v>
       </c>
       <c r="C8" s="1">
         <v>1</v>
       </c>
       <c r="D8" s="5"/>
-      <c r="E8" s="7" t="e">
+      <c r="E8" s="8" t="e">
         <f>AVERAGE(D8:D10)</f>
         <v>#DIV/0!</v>
       </c>
@@ -1460,35 +1519,35 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
       <c r="C9" s="1">
         <v>2</v>
       </c>
       <c r="D9" s="5"/>
-      <c r="E9" s="8"/>
+      <c r="E9" s="7"/>
       <c r="F9" s="9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
       <c r="C10" s="1">
         <v>3</v>
       </c>
       <c r="D10" s="5"/>
-      <c r="E10" s="8"/>
+      <c r="E10" s="7"/>
       <c r="F10" s="9"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7">
         <v>0.8</v>
       </c>
       <c r="C11" s="1">
         <v>1</v>
       </c>
       <c r="D11" s="5"/>
-      <c r="E11" s="7" t="e">
+      <c r="E11" s="8" t="e">
         <f>AVERAGE(D11:D13)</f>
         <v>#DIV/0!</v>
       </c>
@@ -1497,23 +1556,23 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
       <c r="C12" s="1">
         <v>2</v>
       </c>
       <c r="D12" s="5"/>
-      <c r="E12" s="8"/>
+      <c r="E12" s="7"/>
       <c r="F12" s="9"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
       <c r="C13" s="1">
         <v>3</v>
       </c>
       <c r="D13" s="5"/>
-      <c r="E13" s="8"/>
+      <c r="E13" s="7"/>
       <c r="F13" s="9"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -1581,7 +1640,7 @@
       <c r="A2" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="8">
+      <c r="B2" s="7">
         <v>0.2</v>
       </c>
       <c r="C2" s="1">
@@ -1590,7 +1649,7 @@
       <c r="D2" s="5">
         <v>1.10536709177707E-3</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="8">
         <f>AVERAGE(D2:D4)</f>
         <v>1.1309055570820001E-3</v>
       </c>
@@ -1600,24 +1659,24 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="11"/>
-      <c r="B3" s="8"/>
+      <c r="B3" s="7"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
       <c r="D3" s="5">
         <v>1.1564440223869299E-3</v>
       </c>
-      <c r="E3" s="8"/>
+      <c r="E3" s="7"/>
       <c r="F3" s="9"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="11"/>
-      <c r="B4" s="8"/>
+      <c r="B4" s="7"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
       <c r="D4" s="5"/>
-      <c r="E4" s="8"/>
+      <c r="E4" s="7"/>
       <c r="F4" s="9"/>
       <c r="H4" s="5">
         <v>1.0454979313277799E-3</v>
@@ -1625,7 +1684,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="11"/>
-      <c r="B5" s="8">
+      <c r="B5" s="7">
         <v>0.4</v>
       </c>
       <c r="C5" s="1">
@@ -1634,7 +1693,7 @@
       <c r="D5" s="5">
         <v>8.6130823085382702E-4</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="8">
         <f>AVERAGE(D5:D7)</f>
         <v>9.6691710734251137E-4</v>
       </c>
@@ -1644,31 +1703,31 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="11"/>
-      <c r="B6" s="8"/>
+      <c r="B6" s="7"/>
       <c r="C6" s="1">
         <v>2</v>
       </c>
       <c r="D6" s="5">
         <v>1.14094976896151E-3</v>
       </c>
-      <c r="E6" s="8"/>
+      <c r="E6" s="7"/>
       <c r="F6" s="9"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="11"/>
-      <c r="B7" s="8"/>
+      <c r="B7" s="7"/>
       <c r="C7" s="1">
         <v>3</v>
       </c>
       <c r="D7" s="5">
         <v>8.9849332221219702E-4</v>
       </c>
-      <c r="E7" s="8"/>
+      <c r="E7" s="7"/>
       <c r="F7" s="9"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="11"/>
-      <c r="B8" s="8">
+      <c r="B8" s="7">
         <v>0.6</v>
       </c>
       <c r="C8" s="1">
@@ -1677,7 +1736,7 @@
       <c r="D8" s="5">
         <v>9.1338658759890896E-4</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="8">
         <f>AVERAGE(D8:D10)</f>
         <v>8.8801660113643126E-4</v>
       </c>
@@ -1687,31 +1746,31 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="11"/>
-      <c r="B9" s="8"/>
+      <c r="B9" s="7"/>
       <c r="C9" s="1">
         <v>2</v>
       </c>
       <c r="D9" s="6">
         <v>9.8614258166756607E-4</v>
       </c>
-      <c r="E9" s="8"/>
+      <c r="E9" s="7"/>
       <c r="F9" s="9"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="11"/>
-      <c r="B10" s="8"/>
+      <c r="B10" s="7"/>
       <c r="C10" s="1">
         <v>3</v>
       </c>
       <c r="D10" s="5">
         <v>7.6452063414281896E-4</v>
       </c>
-      <c r="E10" s="8"/>
+      <c r="E10" s="7"/>
       <c r="F10" s="9"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="11"/>
-      <c r="B11" s="8">
+      <c r="B11" s="7">
         <v>0.8</v>
       </c>
       <c r="C11" s="1">
@@ -1720,7 +1779,7 @@
       <c r="D11" s="5">
         <v>7.3798692719643404E-4</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="8">
         <f>AVERAGE(D11:D13)</f>
         <v>7.3798692719643404E-4</v>
       </c>
@@ -1730,22 +1789,22 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="11"/>
-      <c r="B12" s="8"/>
+      <c r="B12" s="7"/>
       <c r="C12" s="1">
         <v>2</v>
       </c>
       <c r="D12" s="5"/>
-      <c r="E12" s="8"/>
+      <c r="E12" s="7"/>
       <c r="F12" s="9"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="11"/>
-      <c r="B13" s="8"/>
+      <c r="B13" s="7"/>
       <c r="C13" s="1">
         <v>3</v>
       </c>
       <c r="D13" s="5"/>
-      <c r="E13" s="8"/>
+      <c r="E13" s="7"/>
       <c r="F13" s="9"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
@@ -1809,10 +1868,10 @@
       <c r="F1" s="2"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="8">
+      <c r="B2" s="7">
         <v>0.2</v>
       </c>
       <c r="C2" s="1">
@@ -1821,7 +1880,7 @@
       <c r="D2" s="5">
         <v>1.0456008086864E-3</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="8">
         <f>AVERAGE(D2:D5)</f>
         <v>1.062493548102375E-3</v>
       </c>
@@ -1830,44 +1889,44 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
       <c r="D3" s="4">
         <v>1.09467266122671E-3</v>
       </c>
-      <c r="E3" s="8"/>
+      <c r="E3" s="7"/>
       <c r="F3" s="9"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
       <c r="D4" s="4">
         <v>1.0701604268465201E-3</v>
       </c>
-      <c r="E4" s="8"/>
+      <c r="E4" s="7"/>
       <c r="F4" s="9"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
       <c r="C5" s="1">
         <v>4</v>
       </c>
       <c r="D5" s="5">
         <v>1.0395402956498701E-3</v>
       </c>
-      <c r="E5" s="8"/>
+      <c r="E5" s="7"/>
       <c r="F5" s="9"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8">
+      <c r="A6" s="7"/>
+      <c r="B6" s="7">
         <v>0.4</v>
       </c>
       <c r="C6" s="1">
@@ -1876,7 +1935,7 @@
       <c r="D6" s="5">
         <v>1.3060672401840299E-3</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="8">
         <f>AVERAGE(D6:D9)</f>
         <v>1.0119003627781611E-3</v>
       </c>
@@ -1885,44 +1944,44 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
       <c r="C7" s="1">
         <v>2</v>
       </c>
       <c r="D7" s="4">
         <v>9.3494025407098202E-4</v>
       </c>
-      <c r="E7" s="8"/>
+      <c r="E7" s="7"/>
       <c r="F7" s="9"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
       <c r="C8" s="1">
         <v>3</v>
       </c>
       <c r="D8" s="4">
         <v>1.11627799419256E-3</v>
       </c>
-      <c r="E8" s="8"/>
+      <c r="E8" s="7"/>
       <c r="F8" s="9"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
       <c r="C9" s="1">
         <v>4</v>
       </c>
       <c r="D9" s="5">
         <v>6.9031596266507205E-4</v>
       </c>
-      <c r="E9" s="8"/>
+      <c r="E9" s="7"/>
       <c r="F9" s="9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8">
+      <c r="A10" s="7"/>
+      <c r="B10" s="7">
         <v>0.6</v>
       </c>
       <c r="C10" s="1">
@@ -1931,7 +1990,7 @@
       <c r="D10" s="5">
         <v>1.1258039438553501E-3</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="8">
         <f>AVERAGE(D10:D13)</f>
         <v>1.0913926731899966E-3</v>
       </c>
@@ -1940,44 +1999,44 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
       <c r="C11" s="1">
         <v>2</v>
       </c>
       <c r="D11" s="4">
         <v>9.6767982546831603E-4</v>
       </c>
-      <c r="E11" s="8"/>
+      <c r="E11" s="7"/>
       <c r="F11" s="9"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
       <c r="C12" s="1">
         <v>3</v>
       </c>
       <c r="D12" s="5">
         <v>1.0759200072066801E-3</v>
       </c>
-      <c r="E12" s="8"/>
+      <c r="E12" s="7"/>
       <c r="F12" s="9"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
       <c r="C13" s="1">
         <v>4</v>
       </c>
       <c r="D13" s="5">
         <v>1.1961669162296399E-3</v>
       </c>
-      <c r="E13" s="8"/>
+      <c r="E13" s="7"/>
       <c r="F13" s="9"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8">
+      <c r="A14" s="7"/>
+      <c r="B14" s="7">
         <v>0.8</v>
       </c>
       <c r="C14" s="1">
@@ -1986,7 +2045,7 @@
       <c r="D14" s="4">
         <v>8.5667911779765201E-4</v>
       </c>
-      <c r="E14" s="7">
+      <c r="E14" s="8">
         <f>AVERAGE(D14:D17)</f>
         <v>8.7466814763753067E-4</v>
       </c>
@@ -1995,39 +2054,39 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
       <c r="C15" s="1">
         <v>2</v>
       </c>
       <c r="D15" s="4">
         <v>6.7159374136605899E-4</v>
       </c>
-      <c r="E15" s="7"/>
+      <c r="E15" s="8"/>
       <c r="F15" s="9"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
       <c r="C16" s="1">
         <v>3</v>
       </c>
       <c r="D16" s="5">
         <v>9.2119835353706196E-4</v>
       </c>
-      <c r="E16" s="8"/>
+      <c r="E16" s="7"/>
       <c r="F16" s="9"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
       <c r="C17" s="1">
         <v>4</v>
       </c>
       <c r="D17" s="5">
         <v>1.0492013778493499E-3</v>
       </c>
-      <c r="E17" s="8"/>
+      <c r="E17" s="7"/>
       <c r="F17" s="9"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -2061,4 +2120,332 @@
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F08B2B3E-F6A2-47C0-8A42-E915C262D9EE}">
+  <dimension ref="A1:F23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="22.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="2"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="7">
+        <v>0.2</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="5">
+        <v>9.9861308351742407E-4</v>
+      </c>
+      <c r="E2" s="8">
+        <f>AVERAGE(D2:D6)</f>
+        <v>9.7673568309604702E-4</v>
+      </c>
+      <c r="F2" s="9">
+        <v>1.08E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="1">
+        <v>2</v>
+      </c>
+      <c r="D3" s="5">
+        <v>9.4235074996974397E-4</v>
+      </c>
+      <c r="E3" s="7"/>
+      <c r="F3" s="9"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="1">
+        <v>3</v>
+      </c>
+      <c r="D4" s="5">
+        <v>9.5469248937918197E-4</v>
+      </c>
+      <c r="E4" s="7"/>
+      <c r="F4" s="9"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="1">
+        <v>4</v>
+      </c>
+      <c r="D5" s="5">
+        <v>8.6633270051169502E-4</v>
+      </c>
+      <c r="E5" s="7"/>
+      <c r="F5" s="9"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="1">
+        <v>5</v>
+      </c>
+      <c r="D6" s="5">
+        <v>1.1216893921021901E-3</v>
+      </c>
+      <c r="E6" s="7"/>
+      <c r="F6" s="9"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7">
+        <v>0.4</v>
+      </c>
+      <c r="C7" s="1">
+        <v>1</v>
+      </c>
+      <c r="D7" s="5">
+        <v>8.9437967332690502E-4</v>
+      </c>
+      <c r="E7" s="8">
+        <f>AVERAGE(D7:D11)</f>
+        <v>9.1960146331700621E-4</v>
+      </c>
+      <c r="F7" s="9">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="1">
+        <v>2</v>
+      </c>
+      <c r="D8" s="5">
+        <v>8.0541983045422604E-4</v>
+      </c>
+      <c r="E8" s="7"/>
+      <c r="F8" s="9"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="1">
+        <v>3</v>
+      </c>
+      <c r="D9" s="5">
+        <v>1.00808827591755E-3</v>
+      </c>
+      <c r="E9" s="7"/>
+      <c r="F9" s="9"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="1">
+        <v>4</v>
+      </c>
+      <c r="D10" s="5">
+        <v>8.4824047590335004E-4</v>
+      </c>
+      <c r="E10" s="7"/>
+      <c r="F10" s="9"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="1">
+        <v>5</v>
+      </c>
+      <c r="D11" s="5">
+        <v>1.041879060983E-3</v>
+      </c>
+      <c r="E11" s="7"/>
+      <c r="F11" s="9"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="7"/>
+      <c r="B12" s="7">
+        <v>0.6</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1</v>
+      </c>
+      <c r="D12" s="5">
+        <v>1.0713286556024301E-3</v>
+      </c>
+      <c r="E12" s="8">
+        <f>AVERAGE(D12:D16)</f>
+        <v>9.9714248838866926E-4</v>
+      </c>
+      <c r="F12" s="9">
+        <v>8.9999999999999998E-4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="1">
+        <v>2</v>
+      </c>
+      <c r="D13" s="5">
+        <v>9.4514997141361995E-4</v>
+      </c>
+      <c r="E13" s="7"/>
+      <c r="F13" s="9"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="1">
+        <v>3</v>
+      </c>
+      <c r="D14" s="5">
+        <v>9.3634055614079403E-4</v>
+      </c>
+      <c r="E14" s="7"/>
+      <c r="F14" s="9"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="1">
+        <v>4</v>
+      </c>
+      <c r="D15" s="5">
+        <v>1.13227515241877E-3</v>
+      </c>
+      <c r="E15" s="7"/>
+      <c r="F15" s="9"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="1">
+        <v>5</v>
+      </c>
+      <c r="D16" s="5">
+        <v>9.0061810636773195E-4</v>
+      </c>
+      <c r="E16" s="7"/>
+      <c r="F16" s="9"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="7"/>
+      <c r="B17" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="C17" s="1">
+        <v>1</v>
+      </c>
+      <c r="D17" s="5">
+        <v>8.9938830820844096E-4</v>
+      </c>
+      <c r="E17" s="8">
+        <f>AVERAGE(D17:D21)</f>
+        <v>1.0868212538811403E-3</v>
+      </c>
+      <c r="F17" s="9">
+        <v>6.9999999999999999E-4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="1">
+        <v>2</v>
+      </c>
+      <c r="D18" s="5">
+        <v>1.1217861371005801E-3</v>
+      </c>
+      <c r="E18" s="8"/>
+      <c r="F18" s="9"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="1">
+        <v>3</v>
+      </c>
+      <c r="D19" s="5">
+        <v>1.1543127248442499E-3</v>
+      </c>
+      <c r="E19" s="7"/>
+      <c r="F19" s="9"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="1">
+        <v>4</v>
+      </c>
+      <c r="D20" s="5">
+        <v>1.1717978453712899E-3</v>
+      </c>
+      <c r="E20" s="7"/>
+      <c r="F20" s="9"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="7"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="1">
+        <v>5</v>
+      </c>
+      <c r="D21" s="5"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="9"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23" s="10"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="10"/>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="B17:B21"/>
+    <mergeCell ref="E17:E21"/>
+    <mergeCell ref="F17:F21"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A2:A21"/>
+    <mergeCell ref="B2:B6"/>
+    <mergeCell ref="E2:E6"/>
+    <mergeCell ref="F2:F6"/>
+    <mergeCell ref="B7:B11"/>
+    <mergeCell ref="E7:E11"/>
+    <mergeCell ref="F7:F11"/>
+    <mergeCell ref="B12:B16"/>
+    <mergeCell ref="E12:E16"/>
+    <mergeCell ref="F12:F16"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>
--- a/_resultados/_resultados.xlsx
+++ b/_resultados/_resultados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ravar\Documents\GitHub\recsys-fair-federation-flower\_resultados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6611E20E-C382-47DB-BB7A-8B353C0B1D32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB6FF37D-60E4-447D-9185-2CCFE5B8D23B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="7B-Backup" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="7M" sheetId="3" r:id="rId4"/>
     <sheet name="7N" sheetId="4" r:id="rId5"/>
     <sheet name="7O" sheetId="7" r:id="rId6"/>
+    <sheet name="7S" sheetId="8" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="17">
   <si>
     <t>Estratégia</t>
   </si>
@@ -172,6 +173,21 @@
   <si>
     <t>fairness_penalty = (group_mean_loss) * (lambda_fairness + normalized_variance)</t>
   </si>
+  <si>
+    <t>7S</t>
+  </si>
+  <si>
+    <t>fairness_penalty = (group_mean_loss) * (normalized_variance)</t>
+  </si>
+  <si>
+    <t>AVG</t>
+  </si>
+  <si>
+    <t>LOSS</t>
+  </si>
+  <si>
+    <t>FerFair</t>
+  </si>
 </sst>
 </file>
 
@@ -300,10 +316,10 @@
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -969,10 +985,10 @@
       <c r="F1" s="2"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="7">
+      <c r="A2" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="8">
         <v>0.2</v>
       </c>
       <c r="C2" s="1">
@@ -981,7 +997,7 @@
       <c r="D2" s="3">
         <v>6.0960731897987297E-4</v>
       </c>
-      <c r="E2" s="8">
+      <c r="E2" s="7">
         <f>AVERAGE(D2:D4)</f>
         <v>6.5436713648982334E-4</v>
       </c>
@@ -990,32 +1006,32 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="7"/>
-      <c r="B3" s="7"/>
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
       <c r="D3" s="4">
         <v>1.2366666655837901E-3</v>
       </c>
-      <c r="E3" s="7"/>
+      <c r="E3" s="8"/>
       <c r="F3" s="9"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
       <c r="D4" s="3">
         <v>1.16827424905807E-4</v>
       </c>
-      <c r="E4" s="7"/>
+      <c r="E4" s="8"/>
       <c r="F4" s="9"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7">
+      <c r="A5" s="8"/>
+      <c r="B5" s="8">
         <v>0.4</v>
       </c>
       <c r="C5" s="1">
@@ -1024,7 +1040,7 @@
       <c r="D5" s="4">
         <v>1.05738310578603E-3</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="7">
         <f>AVERAGE(D5:D7)</f>
         <v>9.3433828280417065E-4</v>
       </c>
@@ -1033,32 +1049,32 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
       <c r="C6" s="1">
         <v>2</v>
       </c>
       <c r="D6" s="3">
         <v>7.1366126257072198E-4</v>
       </c>
-      <c r="E6" s="7"/>
+      <c r="E6" s="8"/>
       <c r="F6" s="9"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
       <c r="C7" s="1">
         <v>3</v>
       </c>
       <c r="D7" s="4">
         <v>1.03197048005576E-3</v>
       </c>
-      <c r="E7" s="7"/>
+      <c r="E7" s="8"/>
       <c r="F7" s="9"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7">
+      <c r="A8" s="8"/>
+      <c r="B8" s="8">
         <v>0.6</v>
       </c>
       <c r="C8" s="1">
@@ -1067,7 +1083,7 @@
       <c r="D8" s="4">
         <v>8.5958764850758399E-4</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="7">
         <f>AVERAGE(D8:D10)</f>
         <v>3.5202572786763336E-4</v>
       </c>
@@ -1076,32 +1092,32 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
       <c r="C9" s="1">
         <v>2</v>
       </c>
       <c r="D9" s="3">
         <v>1.9315911817009E-5</v>
       </c>
-      <c r="E9" s="7"/>
+      <c r="E9" s="8"/>
       <c r="F9" s="9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
       <c r="C10" s="1">
         <v>3</v>
       </c>
       <c r="D10" s="3">
         <v>1.7717362327830701E-4</v>
       </c>
-      <c r="E10" s="7"/>
+      <c r="E10" s="8"/>
       <c r="F10" s="9"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8">
         <v>0.8</v>
       </c>
       <c r="C11" s="1">
@@ -1110,7 +1126,7 @@
       <c r="D11" s="3">
         <v>1.1074035510559501E-3</v>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="7">
         <f>AVERAGE(D11:D13)</f>
         <v>3.7258416738856505E-4</v>
       </c>
@@ -1119,31 +1135,36 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
       <c r="C12" s="1">
         <v>2</v>
       </c>
       <c r="D12" s="3">
         <v>3.1072735918849998E-6</v>
       </c>
-      <c r="E12" s="7"/>
+      <c r="E12" s="8"/>
       <c r="F12" s="9"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
       <c r="C13" s="1">
         <v>3</v>
       </c>
       <c r="D13" s="3">
         <v>7.2416775178600003E-6</v>
       </c>
-      <c r="E13" s="7"/>
+      <c r="E13" s="8"/>
       <c r="F13" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A2:A13"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="B11:B13"/>
     <mergeCell ref="E2:E4"/>
     <mergeCell ref="E5:E7"/>
     <mergeCell ref="E8:E10"/>
@@ -1152,11 +1173,6 @@
     <mergeCell ref="F5:F7"/>
     <mergeCell ref="F8:F10"/>
     <mergeCell ref="F11:F13"/>
-    <mergeCell ref="A2:A13"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="B11:B13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1192,10 +1208,10 @@
       <c r="F1" s="2"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="7">
+      <c r="A2" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="8">
         <v>0.2</v>
       </c>
       <c r="C2" s="1">
@@ -1204,7 +1220,7 @@
       <c r="D2" s="3">
         <v>6.0960731897987297E-4</v>
       </c>
-      <c r="E2" s="8">
+      <c r="E2" s="7">
         <f>AVERAGE(D2:D4)</f>
         <v>6.5436713648982334E-4</v>
       </c>
@@ -1213,32 +1229,32 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="7"/>
-      <c r="B3" s="7"/>
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
       <c r="D3" s="4">
         <v>1.2366666655837901E-3</v>
       </c>
-      <c r="E3" s="7"/>
+      <c r="E3" s="8"/>
       <c r="F3" s="9"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
       <c r="D4" s="3">
         <v>1.16827424905807E-4</v>
       </c>
-      <c r="E4" s="7"/>
+      <c r="E4" s="8"/>
       <c r="F4" s="9"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7">
+      <c r="A5" s="8"/>
+      <c r="B5" s="8">
         <v>0.4</v>
       </c>
       <c r="C5" s="1">
@@ -1247,7 +1263,7 @@
       <c r="D5" s="4">
         <v>1.05738310578603E-3</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="7">
         <f>AVERAGE(D5:D7)</f>
         <v>1.0018018224488051E-3</v>
       </c>
@@ -1256,32 +1272,32 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
       <c r="C6" s="1">
         <v>2</v>
       </c>
       <c r="D6" s="4">
         <v>9.1605188150462502E-4</v>
       </c>
-      <c r="E6" s="7"/>
+      <c r="E6" s="8"/>
       <c r="F6" s="9"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
       <c r="C7" s="1">
         <v>3</v>
       </c>
       <c r="D7" s="4">
         <v>1.03197048005576E-3</v>
       </c>
-      <c r="E7" s="7"/>
+      <c r="E7" s="8"/>
       <c r="F7" s="9"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7">
+      <c r="A8" s="8"/>
+      <c r="B8" s="8">
         <v>0.6</v>
       </c>
       <c r="C8" s="1">
@@ -1290,7 +1306,7 @@
       <c r="D8" s="4">
         <v>8.5958764850758399E-4</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="7">
         <f>AVERAGE(D8:D10)</f>
         <v>3.5202572786763336E-4</v>
       </c>
@@ -1299,32 +1315,32 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
       <c r="C9" s="1">
         <v>2</v>
       </c>
       <c r="D9" s="3">
         <v>1.9315911817009E-5</v>
       </c>
-      <c r="E9" s="7"/>
+      <c r="E9" s="8"/>
       <c r="F9" s="9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
       <c r="C10" s="1">
         <v>3</v>
       </c>
       <c r="D10" s="3">
         <v>1.7717362327830701E-4</v>
       </c>
-      <c r="E10" s="7"/>
+      <c r="E10" s="8"/>
       <c r="F10" s="9"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8">
         <v>0.8</v>
       </c>
       <c r="C11" s="1">
@@ -1333,7 +1349,7 @@
       <c r="D11" s="4">
         <v>2.59495713031E-7</v>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="7">
         <f>AVERAGE(D11:D13)</f>
         <v>3.5361489409253331E-6</v>
       </c>
@@ -1342,27 +1358,27 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
       <c r="C12" s="1">
         <v>2</v>
       </c>
       <c r="D12" s="4">
         <v>3.1072735918849998E-6</v>
       </c>
-      <c r="E12" s="7"/>
+      <c r="E12" s="8"/>
       <c r="F12" s="9"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
       <c r="C13" s="1">
         <v>3</v>
       </c>
       <c r="D13" s="4">
         <v>7.2416775178600003E-6</v>
       </c>
-      <c r="E13" s="7"/>
+      <c r="E13" s="8"/>
       <c r="F13" s="9"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -1426,17 +1442,17 @@
       <c r="F1" s="2"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="8">
         <v>0.2</v>
       </c>
       <c r="C2" s="1">
         <v>1</v>
       </c>
       <c r="D2" s="5"/>
-      <c r="E2" s="8" t="e">
+      <c r="E2" s="7" t="e">
         <f>AVERAGE(D2:D4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -1445,35 +1461,35 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="7"/>
-      <c r="B3" s="7"/>
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
       <c r="D3" s="5"/>
-      <c r="E3" s="7"/>
+      <c r="E3" s="8"/>
       <c r="F3" s="9"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
       <c r="D4" s="5"/>
-      <c r="E4" s="7"/>
+      <c r="E4" s="8"/>
       <c r="F4" s="9"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7">
+      <c r="A5" s="8"/>
+      <c r="B5" s="8">
         <v>0.4</v>
       </c>
       <c r="C5" s="1">
         <v>1</v>
       </c>
       <c r="D5" s="5"/>
-      <c r="E5" s="8" t="e">
+      <c r="E5" s="7" t="e">
         <f>AVERAGE(D5:D7)</f>
         <v>#DIV/0!</v>
       </c>
@@ -1482,35 +1498,35 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
       <c r="C6" s="1">
         <v>2</v>
       </c>
       <c r="D6" s="5"/>
-      <c r="E6" s="7"/>
+      <c r="E6" s="8"/>
       <c r="F6" s="9"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
       <c r="C7" s="1">
         <v>3</v>
       </c>
       <c r="D7" s="5"/>
-      <c r="E7" s="7"/>
+      <c r="E7" s="8"/>
       <c r="F7" s="9"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7">
+      <c r="A8" s="8"/>
+      <c r="B8" s="8">
         <v>0.6</v>
       </c>
       <c r="C8" s="1">
         <v>1</v>
       </c>
       <c r="D8" s="5"/>
-      <c r="E8" s="8" t="e">
+      <c r="E8" s="7" t="e">
         <f>AVERAGE(D8:D10)</f>
         <v>#DIV/0!</v>
       </c>
@@ -1519,35 +1535,35 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
       <c r="C9" s="1">
         <v>2</v>
       </c>
       <c r="D9" s="5"/>
-      <c r="E9" s="7"/>
+      <c r="E9" s="8"/>
       <c r="F9" s="9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
       <c r="C10" s="1">
         <v>3</v>
       </c>
       <c r="D10" s="5"/>
-      <c r="E10" s="7"/>
+      <c r="E10" s="8"/>
       <c r="F10" s="9"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8">
         <v>0.8</v>
       </c>
       <c r="C11" s="1">
         <v>1</v>
       </c>
       <c r="D11" s="5"/>
-      <c r="E11" s="8" t="e">
+      <c r="E11" s="7" t="e">
         <f>AVERAGE(D11:D13)</f>
         <v>#DIV/0!</v>
       </c>
@@ -1556,23 +1572,23 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
       <c r="C12" s="1">
         <v>2</v>
       </c>
       <c r="D12" s="5"/>
-      <c r="E12" s="7"/>
+      <c r="E12" s="8"/>
       <c r="F12" s="9"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
       <c r="C13" s="1">
         <v>3</v>
       </c>
       <c r="D13" s="5"/>
-      <c r="E13" s="7"/>
+      <c r="E13" s="8"/>
       <c r="F13" s="9"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -1640,7 +1656,7 @@
       <c r="A2" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="8">
         <v>0.2</v>
       </c>
       <c r="C2" s="1">
@@ -1649,7 +1665,7 @@
       <c r="D2" s="5">
         <v>1.10536709177707E-3</v>
       </c>
-      <c r="E2" s="8">
+      <c r="E2" s="7">
         <f>AVERAGE(D2:D4)</f>
         <v>1.1309055570820001E-3</v>
       </c>
@@ -1659,24 +1675,24 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="11"/>
-      <c r="B3" s="7"/>
+      <c r="B3" s="8"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
       <c r="D3" s="5">
         <v>1.1564440223869299E-3</v>
       </c>
-      <c r="E3" s="7"/>
+      <c r="E3" s="8"/>
       <c r="F3" s="9"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="11"/>
-      <c r="B4" s="7"/>
+      <c r="B4" s="8"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
       <c r="D4" s="5"/>
-      <c r="E4" s="7"/>
+      <c r="E4" s="8"/>
       <c r="F4" s="9"/>
       <c r="H4" s="5">
         <v>1.0454979313277799E-3</v>
@@ -1684,7 +1700,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="11"/>
-      <c r="B5" s="7">
+      <c r="B5" s="8">
         <v>0.4</v>
       </c>
       <c r="C5" s="1">
@@ -1693,7 +1709,7 @@
       <c r="D5" s="5">
         <v>8.6130823085382702E-4</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="7">
         <f>AVERAGE(D5:D7)</f>
         <v>9.6691710734251137E-4</v>
       </c>
@@ -1703,31 +1719,31 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="11"/>
-      <c r="B6" s="7"/>
+      <c r="B6" s="8"/>
       <c r="C6" s="1">
         <v>2</v>
       </c>
       <c r="D6" s="5">
         <v>1.14094976896151E-3</v>
       </c>
-      <c r="E6" s="7"/>
+      <c r="E6" s="8"/>
       <c r="F6" s="9"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="11"/>
-      <c r="B7" s="7"/>
+      <c r="B7" s="8"/>
       <c r="C7" s="1">
         <v>3</v>
       </c>
       <c r="D7" s="5">
         <v>8.9849332221219702E-4</v>
       </c>
-      <c r="E7" s="7"/>
+      <c r="E7" s="8"/>
       <c r="F7" s="9"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="11"/>
-      <c r="B8" s="7">
+      <c r="B8" s="8">
         <v>0.6</v>
       </c>
       <c r="C8" s="1">
@@ -1736,7 +1752,7 @@
       <c r="D8" s="5">
         <v>9.1338658759890896E-4</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="7">
         <f>AVERAGE(D8:D10)</f>
         <v>8.8801660113643126E-4</v>
       </c>
@@ -1746,31 +1762,31 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="11"/>
-      <c r="B9" s="7"/>
+      <c r="B9" s="8"/>
       <c r="C9" s="1">
         <v>2</v>
       </c>
       <c r="D9" s="6">
         <v>9.8614258166756607E-4</v>
       </c>
-      <c r="E9" s="7"/>
+      <c r="E9" s="8"/>
       <c r="F9" s="9"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="11"/>
-      <c r="B10" s="7"/>
+      <c r="B10" s="8"/>
       <c r="C10" s="1">
         <v>3</v>
       </c>
       <c r="D10" s="5">
         <v>7.6452063414281896E-4</v>
       </c>
-      <c r="E10" s="7"/>
+      <c r="E10" s="8"/>
       <c r="F10" s="9"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="11"/>
-      <c r="B11" s="7">
+      <c r="B11" s="8">
         <v>0.8</v>
       </c>
       <c r="C11" s="1">
@@ -1779,7 +1795,7 @@
       <c r="D11" s="5">
         <v>7.3798692719643404E-4</v>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="7">
         <f>AVERAGE(D11:D13)</f>
         <v>7.3798692719643404E-4</v>
       </c>
@@ -1789,22 +1805,22 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="11"/>
-      <c r="B12" s="7"/>
+      <c r="B12" s="8"/>
       <c r="C12" s="1">
         <v>2</v>
       </c>
       <c r="D12" s="5"/>
-      <c r="E12" s="7"/>
+      <c r="E12" s="8"/>
       <c r="F12" s="9"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="11"/>
-      <c r="B13" s="7"/>
+      <c r="B13" s="8"/>
       <c r="C13" s="1">
         <v>3</v>
       </c>
       <c r="D13" s="5"/>
-      <c r="E13" s="7"/>
+      <c r="E13" s="8"/>
       <c r="F13" s="9"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
@@ -1868,10 +1884,10 @@
       <c r="F1" s="2"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="8">
         <v>0.2</v>
       </c>
       <c r="C2" s="1">
@@ -1880,7 +1896,7 @@
       <c r="D2" s="5">
         <v>1.0456008086864E-3</v>
       </c>
-      <c r="E2" s="8">
+      <c r="E2" s="7">
         <f>AVERAGE(D2:D5)</f>
         <v>1.062493548102375E-3</v>
       </c>
@@ -1889,44 +1905,44 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="7"/>
-      <c r="B3" s="7"/>
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
       <c r="D3" s="4">
         <v>1.09467266122671E-3</v>
       </c>
-      <c r="E3" s="7"/>
+      <c r="E3" s="8"/>
       <c r="F3" s="9"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
       <c r="D4" s="4">
         <v>1.0701604268465201E-3</v>
       </c>
-      <c r="E4" s="7"/>
+      <c r="E4" s="8"/>
       <c r="F4" s="9"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7"/>
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
       <c r="C5" s="1">
         <v>4</v>
       </c>
       <c r="D5" s="5">
         <v>1.0395402956498701E-3</v>
       </c>
-      <c r="E5" s="7"/>
+      <c r="E5" s="8"/>
       <c r="F5" s="9"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7">
+      <c r="A6" s="8"/>
+      <c r="B6" s="8">
         <v>0.4</v>
       </c>
       <c r="C6" s="1">
@@ -1935,7 +1951,7 @@
       <c r="D6" s="5">
         <v>1.3060672401840299E-3</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="7">
         <f>AVERAGE(D6:D9)</f>
         <v>1.0119003627781611E-3</v>
       </c>
@@ -1944,44 +1960,44 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
       <c r="C7" s="1">
         <v>2</v>
       </c>
       <c r="D7" s="4">
         <v>9.3494025407098202E-4</v>
       </c>
-      <c r="E7" s="7"/>
+      <c r="E7" s="8"/>
       <c r="F7" s="9"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
       <c r="C8" s="1">
         <v>3</v>
       </c>
       <c r="D8" s="4">
         <v>1.11627799419256E-3</v>
       </c>
-      <c r="E8" s="7"/>
+      <c r="E8" s="8"/>
       <c r="F8" s="9"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
       <c r="C9" s="1">
         <v>4</v>
       </c>
       <c r="D9" s="5">
         <v>6.9031596266507205E-4</v>
       </c>
-      <c r="E9" s="7"/>
+      <c r="E9" s="8"/>
       <c r="F9" s="9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7">
+      <c r="A10" s="8"/>
+      <c r="B10" s="8">
         <v>0.6</v>
       </c>
       <c r="C10" s="1">
@@ -1990,7 +2006,7 @@
       <c r="D10" s="5">
         <v>1.1258039438553501E-3</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="7">
         <f>AVERAGE(D10:D13)</f>
         <v>1.0913926731899966E-3</v>
       </c>
@@ -1999,44 +2015,44 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
       <c r="C11" s="1">
         <v>2</v>
       </c>
       <c r="D11" s="4">
         <v>9.6767982546831603E-4</v>
       </c>
-      <c r="E11" s="7"/>
+      <c r="E11" s="8"/>
       <c r="F11" s="9"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
       <c r="C12" s="1">
         <v>3</v>
       </c>
       <c r="D12" s="5">
         <v>1.0759200072066801E-3</v>
       </c>
-      <c r="E12" s="7"/>
+      <c r="E12" s="8"/>
       <c r="F12" s="9"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
       <c r="C13" s="1">
         <v>4</v>
       </c>
       <c r="D13" s="5">
         <v>1.1961669162296399E-3</v>
       </c>
-      <c r="E13" s="7"/>
+      <c r="E13" s="8"/>
       <c r="F13" s="9"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7">
+      <c r="A14" s="8"/>
+      <c r="B14" s="8">
         <v>0.8</v>
       </c>
       <c r="C14" s="1">
@@ -2045,7 +2061,7 @@
       <c r="D14" s="4">
         <v>8.5667911779765201E-4</v>
       </c>
-      <c r="E14" s="8">
+      <c r="E14" s="7">
         <f>AVERAGE(D14:D17)</f>
         <v>8.7466814763753067E-4</v>
       </c>
@@ -2054,39 +2070,39 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
       <c r="C15" s="1">
         <v>2</v>
       </c>
       <c r="D15" s="4">
         <v>6.7159374136605899E-4</v>
       </c>
-      <c r="E15" s="8"/>
+      <c r="E15" s="7"/>
       <c r="F15" s="9"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
       <c r="C16" s="1">
         <v>3</v>
       </c>
       <c r="D16" s="5">
         <v>9.2119835353706196E-4</v>
       </c>
-      <c r="E16" s="7"/>
+      <c r="E16" s="8"/>
       <c r="F16" s="9"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
       <c r="C17" s="1">
         <v>4</v>
       </c>
       <c r="D17" s="5">
         <v>1.0492013778493499E-3</v>
       </c>
-      <c r="E17" s="7"/>
+      <c r="E17" s="8"/>
       <c r="F17" s="9"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -2150,10 +2166,10 @@
       <c r="F1" s="2"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="8">
         <v>0.2</v>
       </c>
       <c r="C2" s="1">
@@ -2162,7 +2178,7 @@
       <c r="D2" s="5">
         <v>9.9861308351742407E-4</v>
       </c>
-      <c r="E2" s="8">
+      <c r="E2" s="7">
         <f>AVERAGE(D2:D6)</f>
         <v>9.7673568309604702E-4</v>
       </c>
@@ -2171,56 +2187,56 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="7"/>
-      <c r="B3" s="7"/>
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
       <c r="D3" s="5">
         <v>9.4235074996974397E-4</v>
       </c>
-      <c r="E3" s="7"/>
+      <c r="E3" s="8"/>
       <c r="F3" s="9"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
       <c r="D4" s="5">
         <v>9.5469248937918197E-4</v>
       </c>
-      <c r="E4" s="7"/>
+      <c r="E4" s="8"/>
       <c r="F4" s="9"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7"/>
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
       <c r="C5" s="1">
         <v>4</v>
       </c>
       <c r="D5" s="5">
         <v>8.6633270051169502E-4</v>
       </c>
-      <c r="E5" s="7"/>
+      <c r="E5" s="8"/>
       <c r="F5" s="9"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
       <c r="C6" s="1">
         <v>5</v>
       </c>
       <c r="D6" s="5">
         <v>1.1216893921021901E-3</v>
       </c>
-      <c r="E6" s="7"/>
+      <c r="E6" s="8"/>
       <c r="F6" s="9"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7">
+      <c r="A7" s="8"/>
+      <c r="B7" s="8">
         <v>0.4</v>
       </c>
       <c r="C7" s="1">
@@ -2229,7 +2245,7 @@
       <c r="D7" s="5">
         <v>8.9437967332690502E-4</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="7">
         <f>AVERAGE(D7:D11)</f>
         <v>9.1960146331700621E-4</v>
       </c>
@@ -2238,56 +2254,56 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
       <c r="C8" s="1">
         <v>2</v>
       </c>
       <c r="D8" s="5">
         <v>8.0541983045422604E-4</v>
       </c>
-      <c r="E8" s="7"/>
+      <c r="E8" s="8"/>
       <c r="F8" s="9"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
       <c r="C9" s="1">
         <v>3</v>
       </c>
       <c r="D9" s="5">
         <v>1.00808827591755E-3</v>
       </c>
-      <c r="E9" s="7"/>
+      <c r="E9" s="8"/>
       <c r="F9" s="9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
       <c r="C10" s="1">
         <v>4</v>
       </c>
       <c r="D10" s="5">
         <v>8.4824047590335004E-4</v>
       </c>
-      <c r="E10" s="7"/>
+      <c r="E10" s="8"/>
       <c r="F10" s="9"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
       <c r="C11" s="1">
         <v>5</v>
       </c>
       <c r="D11" s="5">
         <v>1.041879060983E-3</v>
       </c>
-      <c r="E11" s="7"/>
+      <c r="E11" s="8"/>
       <c r="F11" s="9"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7">
+      <c r="A12" s="8"/>
+      <c r="B12" s="8">
         <v>0.6</v>
       </c>
       <c r="C12" s="1">
@@ -2296,7 +2312,7 @@
       <c r="D12" s="5">
         <v>1.0713286556024301E-3</v>
       </c>
-      <c r="E12" s="8">
+      <c r="E12" s="7">
         <f>AVERAGE(D12:D16)</f>
         <v>9.9714248838866926E-4</v>
       </c>
@@ -2305,56 +2321,56 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
       <c r="C13" s="1">
         <v>2</v>
       </c>
       <c r="D13" s="5">
         <v>9.4514997141361995E-4</v>
       </c>
-      <c r="E13" s="7"/>
+      <c r="E13" s="8"/>
       <c r="F13" s="9"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
       <c r="C14" s="1">
         <v>3</v>
       </c>
       <c r="D14" s="5">
         <v>9.3634055614079403E-4</v>
       </c>
-      <c r="E14" s="7"/>
+      <c r="E14" s="8"/>
       <c r="F14" s="9"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
       <c r="C15" s="1">
         <v>4</v>
       </c>
       <c r="D15" s="5">
         <v>1.13227515241877E-3</v>
       </c>
-      <c r="E15" s="7"/>
+      <c r="E15" s="8"/>
       <c r="F15" s="9"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
       <c r="C16" s="1">
         <v>5</v>
       </c>
       <c r="D16" s="5">
         <v>9.0061810636773195E-4</v>
       </c>
-      <c r="E16" s="7"/>
+      <c r="E16" s="8"/>
       <c r="F16" s="9"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7">
+      <c r="A17" s="8"/>
+      <c r="B17" s="8">
         <v>0.8</v>
       </c>
       <c r="C17" s="1">
@@ -2363,7 +2379,7 @@
       <c r="D17" s="5">
         <v>8.9938830820844096E-4</v>
       </c>
-      <c r="E17" s="8">
+      <c r="E17" s="7">
         <f>AVERAGE(D17:D21)</f>
         <v>1.0868212538811403E-3</v>
       </c>
@@ -2372,49 +2388,49 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
       <c r="C18" s="1">
         <v>2</v>
       </c>
       <c r="D18" s="5">
         <v>1.1217861371005801E-3</v>
       </c>
-      <c r="E18" s="8"/>
+      <c r="E18" s="7"/>
       <c r="F18" s="9"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
       <c r="C19" s="1">
         <v>3</v>
       </c>
       <c r="D19" s="5">
         <v>1.1543127248442499E-3</v>
       </c>
-      <c r="E19" s="7"/>
+      <c r="E19" s="8"/>
       <c r="F19" s="9"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
       <c r="C20" s="1">
         <v>4</v>
       </c>
       <c r="D20" s="5">
         <v>1.1717978453712899E-3</v>
       </c>
-      <c r="E20" s="7"/>
+      <c r="E20" s="8"/>
       <c r="F20" s="9"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
       <c r="C21" s="1">
         <v>5</v>
       </c>
       <c r="D21" s="5"/>
-      <c r="E21" s="7"/>
+      <c r="E21" s="8"/>
       <c r="F21" s="9"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
@@ -2448,4 +2464,227 @@
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1795133B-F2EB-4E04-AB6B-728F37460635}">
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="22.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="5">
+        <v>4.6060741068411704E-3</v>
+      </c>
+      <c r="E2" s="7">
+        <f>AVERAGE(D2:D6)</f>
+        <v>4.3943148562279851E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="1">
+        <v>2</v>
+      </c>
+      <c r="D3" s="5">
+        <v>4.1201631529217001E-3</v>
+      </c>
+      <c r="E3" s="8"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="1">
+        <v>3</v>
+      </c>
+      <c r="D4" s="5">
+        <v>4.3891970092903897E-3</v>
+      </c>
+      <c r="E4" s="8"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="1">
+        <v>4</v>
+      </c>
+      <c r="D5" s="5">
+        <v>4.4618251558586801E-3</v>
+      </c>
+      <c r="E5" s="8"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="1">
+        <v>5</v>
+      </c>
+      <c r="D6" s="5"/>
+      <c r="E6" s="8"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="8"/>
+      <c r="B7" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="1">
+        <v>1</v>
+      </c>
+      <c r="D7" s="5">
+        <v>1.04107924830786E-3</v>
+      </c>
+      <c r="E7" s="7">
+        <f>AVERAGE(D7:D11)</f>
+        <v>1.23803134268238E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="1">
+        <v>2</v>
+      </c>
+      <c r="D8" s="5">
+        <v>1.4349834370568999E-3</v>
+      </c>
+      <c r="E8" s="8"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="1">
+        <v>3</v>
+      </c>
+      <c r="D9" s="5"/>
+      <c r="E9" s="8"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="1">
+        <v>4</v>
+      </c>
+      <c r="D10" s="5"/>
+      <c r="E10" s="8"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="1">
+        <v>5</v>
+      </c>
+      <c r="D11" s="5"/>
+      <c r="E11" s="8"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="8"/>
+      <c r="B12" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1</v>
+      </c>
+      <c r="D12" s="5">
+        <v>8.6090646012557603E-4</v>
+      </c>
+      <c r="E12" s="7">
+        <f>AVERAGE(D12:D16)</f>
+        <v>9.0367629214962596E-4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="1">
+        <v>2</v>
+      </c>
+      <c r="D13" s="5">
+        <v>9.5744145788180795E-4</v>
+      </c>
+      <c r="E13" s="8"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="1">
+        <v>3</v>
+      </c>
+      <c r="D14" s="5">
+        <v>8.2489508743011997E-4</v>
+      </c>
+      <c r="E14" s="8"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="1">
+        <v>4</v>
+      </c>
+      <c r="D15" s="5">
+        <v>9.7146216316099999E-4</v>
+      </c>
+      <c r="E15" s="8"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="1">
+        <v>5</v>
+      </c>
+      <c r="D16" s="5"/>
+      <c r="E16" s="8"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A2:A16"/>
+    <mergeCell ref="B2:B6"/>
+    <mergeCell ref="E2:E6"/>
+    <mergeCell ref="B7:B11"/>
+    <mergeCell ref="E7:E11"/>
+    <mergeCell ref="B12:B16"/>
+    <mergeCell ref="E12:E16"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/_resultados/_resultados.xlsx
+++ b/_resultados/_resultados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ravar\Documents\GitHub\recsys-fair-federation-flower\_resultados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB6FF37D-60E4-447D-9185-2CCFE5B8D23B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58A8F297-BDED-4748-95F6-15D81B1AE9AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="7B-Backup" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,12 @@
     <sheet name="7N" sheetId="4" r:id="rId5"/>
     <sheet name="7O" sheetId="7" r:id="rId6"/>
     <sheet name="7S" sheetId="8" r:id="rId7"/>
+    <sheet name="Taxa0-Activity" sheetId="12" r:id="rId8"/>
+    <sheet name="Taxa0-Age" sheetId="13" r:id="rId9"/>
+    <sheet name="Taxa9-Activity" sheetId="9" r:id="rId10"/>
+    <sheet name="Taxa9-Age" sheetId="10" r:id="rId11"/>
+    <sheet name="Taxa0-Gender" sheetId="14" r:id="rId12"/>
+    <sheet name="Taxa9-Gender" sheetId="11" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="19">
   <si>
     <t>Estratégia</t>
   </si>
@@ -188,6 +194,12 @@
   <si>
     <t>FerFair</t>
   </si>
+  <si>
+    <t>Activity</t>
+  </si>
+  <si>
+    <t>Age</t>
+  </si>
 </sst>
 </file>
 
@@ -316,10 +328,10 @@
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -985,10 +997,10 @@
       <c r="F1" s="2"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="8">
+      <c r="A2" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="7">
         <v>0.2</v>
       </c>
       <c r="C2" s="1">
@@ -997,7 +1009,7 @@
       <c r="D2" s="3">
         <v>6.0960731897987297E-4</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="8">
         <f>AVERAGE(D2:D4)</f>
         <v>6.5436713648982334E-4</v>
       </c>
@@ -1006,32 +1018,32 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
       <c r="D3" s="4">
         <v>1.2366666655837901E-3</v>
       </c>
-      <c r="E3" s="8"/>
+      <c r="E3" s="7"/>
       <c r="F3" s="9"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
       <c r="D4" s="3">
         <v>1.16827424905807E-4</v>
       </c>
-      <c r="E4" s="8"/>
+      <c r="E4" s="7"/>
       <c r="F4" s="9"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7">
         <v>0.4</v>
       </c>
       <c r="C5" s="1">
@@ -1040,7 +1052,7 @@
       <c r="D5" s="4">
         <v>1.05738310578603E-3</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="8">
         <f>AVERAGE(D5:D7)</f>
         <v>9.3433828280417065E-4</v>
       </c>
@@ -1049,32 +1061,32 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
       <c r="C6" s="1">
         <v>2</v>
       </c>
       <c r="D6" s="3">
         <v>7.1366126257072198E-4</v>
       </c>
-      <c r="E6" s="8"/>
+      <c r="E6" s="7"/>
       <c r="F6" s="9"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
       <c r="C7" s="1">
         <v>3</v>
       </c>
       <c r="D7" s="4">
         <v>1.03197048005576E-3</v>
       </c>
-      <c r="E7" s="8"/>
+      <c r="E7" s="7"/>
       <c r="F7" s="9"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8">
+      <c r="A8" s="7"/>
+      <c r="B8" s="7">
         <v>0.6</v>
       </c>
       <c r="C8" s="1">
@@ -1083,7 +1095,7 @@
       <c r="D8" s="4">
         <v>8.5958764850758399E-4</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="8">
         <f>AVERAGE(D8:D10)</f>
         <v>3.5202572786763336E-4</v>
       </c>
@@ -1092,32 +1104,32 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
       <c r="C9" s="1">
         <v>2</v>
       </c>
       <c r="D9" s="3">
         <v>1.9315911817009E-5</v>
       </c>
-      <c r="E9" s="8"/>
+      <c r="E9" s="7"/>
       <c r="F9" s="9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
       <c r="C10" s="1">
         <v>3</v>
       </c>
       <c r="D10" s="3">
         <v>1.7717362327830701E-4</v>
       </c>
-      <c r="E10" s="8"/>
+      <c r="E10" s="7"/>
       <c r="F10" s="9"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7">
         <v>0.8</v>
       </c>
       <c r="C11" s="1">
@@ -1126,7 +1138,7 @@
       <c r="D11" s="3">
         <v>1.1074035510559501E-3</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="8">
         <f>AVERAGE(D11:D13)</f>
         <v>3.7258416738856505E-4</v>
       </c>
@@ -1135,36 +1147,31 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
       <c r="C12" s="1">
         <v>2</v>
       </c>
       <c r="D12" s="3">
         <v>3.1072735918849998E-6</v>
       </c>
-      <c r="E12" s="8"/>
+      <c r="E12" s="7"/>
       <c r="F12" s="9"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
       <c r="C13" s="1">
         <v>3</v>
       </c>
       <c r="D13" s="3">
         <v>7.2416775178600003E-6</v>
       </c>
-      <c r="E13" s="8"/>
+      <c r="E13" s="7"/>
       <c r="F13" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A2:A13"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="B5:B7"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="B11:B13"/>
     <mergeCell ref="E2:E4"/>
     <mergeCell ref="E5:E7"/>
     <mergeCell ref="E8:E10"/>
@@ -1173,10 +1180,865 @@
     <mergeCell ref="F5:F7"/>
     <mergeCell ref="F8:F10"/>
     <mergeCell ref="F11:F13"/>
+    <mergeCell ref="A2:A13"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="B11:B13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A4E0EFC-60B3-4A89-9B9D-DE2DE952C266}">
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="22.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="5">
+        <v>1.81177350386232E-3</v>
+      </c>
+      <c r="E2" s="8">
+        <f>AVERAGE(D2:D6)</f>
+        <v>1.8132870925671599E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="1">
+        <v>2</v>
+      </c>
+      <c r="D3" s="5">
+        <v>1.8148006812720001E-3</v>
+      </c>
+      <c r="E3" s="7"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="1">
+        <v>3</v>
+      </c>
+      <c r="D4" s="5"/>
+      <c r="E4" s="7"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="1">
+        <v>4</v>
+      </c>
+      <c r="D5" s="5"/>
+      <c r="E5" s="7"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="1">
+        <v>5</v>
+      </c>
+      <c r="D6" s="5"/>
+      <c r="E6" s="7"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="1">
+        <v>1</v>
+      </c>
+      <c r="D7" s="5">
+        <v>1.22745404238443E-3</v>
+      </c>
+      <c r="E7" s="8">
+        <f>AVERAGE(D7:D11)</f>
+        <v>1.220176512275965E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="1">
+        <v>2</v>
+      </c>
+      <c r="D8" s="5">
+        <v>1.2128989821674999E-3</v>
+      </c>
+      <c r="E8" s="7"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="1">
+        <v>3</v>
+      </c>
+      <c r="D9" s="5"/>
+      <c r="E9" s="7"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="1">
+        <v>4</v>
+      </c>
+      <c r="D10" s="5"/>
+      <c r="E10" s="7"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="1">
+        <v>5</v>
+      </c>
+      <c r="D11" s="5"/>
+      <c r="E11" s="7"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="7"/>
+      <c r="B12" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1</v>
+      </c>
+      <c r="D12" s="5">
+        <v>7.2837430705559596E-4</v>
+      </c>
+      <c r="E12" s="8">
+        <f>AVERAGE(D12:D16)</f>
+        <v>7.2837430705559596E-4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="1">
+        <v>2</v>
+      </c>
+      <c r="D13" s="5"/>
+      <c r="E13" s="7"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="1">
+        <v>3</v>
+      </c>
+      <c r="D14" s="5"/>
+      <c r="E14" s="7"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="1">
+        <v>4</v>
+      </c>
+      <c r="D15" s="5"/>
+      <c r="E15" s="7"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="1">
+        <v>5</v>
+      </c>
+      <c r="D16" s="5"/>
+      <c r="E16" s="7"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A2:A16"/>
+    <mergeCell ref="B2:B6"/>
+    <mergeCell ref="E2:E6"/>
+    <mergeCell ref="B7:B11"/>
+    <mergeCell ref="E7:E11"/>
+    <mergeCell ref="B12:B16"/>
+    <mergeCell ref="E12:E16"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B15EF7D7-78A7-47B3-A2F0-0D82FA15EBA8}">
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="22.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="5">
+        <v>8.8432581244842993E-3</v>
+      </c>
+      <c r="E2" s="8">
+        <f>AVERAGE(D2:D6)</f>
+        <v>8.8432581244842993E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="1">
+        <v>2</v>
+      </c>
+      <c r="D3" s="5"/>
+      <c r="E3" s="7"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="1">
+        <v>3</v>
+      </c>
+      <c r="D4" s="5"/>
+      <c r="E4" s="7"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="1">
+        <v>4</v>
+      </c>
+      <c r="D5" s="5"/>
+      <c r="E5" s="7"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="1">
+        <v>5</v>
+      </c>
+      <c r="D6" s="5"/>
+      <c r="E6" s="7"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="1">
+        <v>1</v>
+      </c>
+      <c r="D7" s="5">
+        <v>8.4438215453025E-3</v>
+      </c>
+      <c r="E7" s="8">
+        <f>AVERAGE(D7:D11)</f>
+        <v>8.2572491277925208E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="1">
+        <v>2</v>
+      </c>
+      <c r="D8" s="5">
+        <v>8.07067671028254E-3</v>
+      </c>
+      <c r="E8" s="7"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="1">
+        <v>3</v>
+      </c>
+      <c r="D9" s="5"/>
+      <c r="E9" s="7"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="1">
+        <v>4</v>
+      </c>
+      <c r="D10" s="5"/>
+      <c r="E10" s="7"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="1">
+        <v>5</v>
+      </c>
+      <c r="D11" s="5"/>
+      <c r="E11" s="7"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="7"/>
+      <c r="B12" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1</v>
+      </c>
+      <c r="D12" s="5">
+        <v>7.1778871123947098E-3</v>
+      </c>
+      <c r="E12" s="8">
+        <f>AVERAGE(D12:D16)</f>
+        <v>7.1778871123947098E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="1">
+        <v>2</v>
+      </c>
+      <c r="D13" s="5"/>
+      <c r="E13" s="7"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="1">
+        <v>3</v>
+      </c>
+      <c r="D14" s="5"/>
+      <c r="E14" s="7"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="1">
+        <v>4</v>
+      </c>
+      <c r="D15" s="5"/>
+      <c r="E15" s="7"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="1">
+        <v>5</v>
+      </c>
+      <c r="D16" s="5"/>
+      <c r="E16" s="7"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A2:A16"/>
+    <mergeCell ref="B2:B6"/>
+    <mergeCell ref="E2:E6"/>
+    <mergeCell ref="B7:B11"/>
+    <mergeCell ref="E7:E11"/>
+    <mergeCell ref="B12:B16"/>
+    <mergeCell ref="E12:E16"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DD90B87-E05B-497D-A050-F1EDBF1A792F}">
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="22.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="5">
+        <v>3.0401932235441099E-3</v>
+      </c>
+      <c r="E2" s="8">
+        <f>AVERAGE(D2:D6)</f>
+        <v>3.036665834008875E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="1">
+        <v>2</v>
+      </c>
+      <c r="D3" s="5">
+        <v>3.0331384444736401E-3</v>
+      </c>
+      <c r="E3" s="7"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="1">
+        <v>3</v>
+      </c>
+      <c r="D4" s="5"/>
+      <c r="E4" s="7"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="1">
+        <v>4</v>
+      </c>
+      <c r="D5" s="5"/>
+      <c r="E5" s="7"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="1">
+        <v>5</v>
+      </c>
+      <c r="D6" s="5"/>
+      <c r="E6" s="7"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="1">
+        <v>1</v>
+      </c>
+      <c r="D7" s="5">
+        <v>2.56045791222035E-3</v>
+      </c>
+      <c r="E7" s="8">
+        <f>AVERAGE(D7:D11)</f>
+        <v>2.56045791222035E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="1">
+        <v>2</v>
+      </c>
+      <c r="D8" s="5">
+        <v>2.56045791222035E-3</v>
+      </c>
+      <c r="E8" s="7"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="1">
+        <v>3</v>
+      </c>
+      <c r="D9" s="5"/>
+      <c r="E9" s="7"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="1">
+        <v>4</v>
+      </c>
+      <c r="D10" s="5"/>
+      <c r="E10" s="7"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="1">
+        <v>5</v>
+      </c>
+      <c r="D11" s="5"/>
+      <c r="E11" s="7"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="7"/>
+      <c r="B12" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1</v>
+      </c>
+      <c r="D12" s="5">
+        <v>2.4814469061344799E-3</v>
+      </c>
+      <c r="E12" s="8">
+        <f>AVERAGE(D12:D16)</f>
+        <v>2.4814469061344799E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="1">
+        <v>2</v>
+      </c>
+      <c r="D13" s="5"/>
+      <c r="E13" s="7"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="1">
+        <v>3</v>
+      </c>
+      <c r="D14" s="5"/>
+      <c r="E14" s="7"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="1">
+        <v>4</v>
+      </c>
+      <c r="D15" s="5"/>
+      <c r="E15" s="7"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="1">
+        <v>5</v>
+      </c>
+      <c r="D16" s="5"/>
+      <c r="E16" s="7"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A2:A16"/>
+    <mergeCell ref="B2:B6"/>
+    <mergeCell ref="E2:E6"/>
+    <mergeCell ref="B7:B11"/>
+    <mergeCell ref="E7:E11"/>
+    <mergeCell ref="B12:B16"/>
+    <mergeCell ref="E12:E16"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8151F7D3-D47C-4DB1-A710-38A98088E576}">
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="22.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="5">
+        <v>3.0401932235441099E-3</v>
+      </c>
+      <c r="E2" s="8">
+        <f>AVERAGE(D2:D6)</f>
+        <v>3.036665834008875E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="1">
+        <v>2</v>
+      </c>
+      <c r="D3" s="5">
+        <v>3.0331384444736401E-3</v>
+      </c>
+      <c r="E3" s="7"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="1">
+        <v>3</v>
+      </c>
+      <c r="D4" s="5"/>
+      <c r="E4" s="7"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="1">
+        <v>4</v>
+      </c>
+      <c r="D5" s="5"/>
+      <c r="E5" s="7"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="1">
+        <v>5</v>
+      </c>
+      <c r="D6" s="5"/>
+      <c r="E6" s="7"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="1">
+        <v>1</v>
+      </c>
+      <c r="D7" s="5">
+        <v>2.56045791222035E-3</v>
+      </c>
+      <c r="E7" s="8">
+        <f>AVERAGE(D7:D11)</f>
+        <v>2.56045791222035E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="1">
+        <v>2</v>
+      </c>
+      <c r="D8" s="5">
+        <v>2.56045791222035E-3</v>
+      </c>
+      <c r="E8" s="7"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="1">
+        <v>3</v>
+      </c>
+      <c r="D9" s="5"/>
+      <c r="E9" s="7"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="1">
+        <v>4</v>
+      </c>
+      <c r="D10" s="5"/>
+      <c r="E10" s="7"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="1">
+        <v>5</v>
+      </c>
+      <c r="D11" s="5"/>
+      <c r="E11" s="7"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="7"/>
+      <c r="B12" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1</v>
+      </c>
+      <c r="D12" s="5">
+        <v>2.58438912178445E-3</v>
+      </c>
+      <c r="E12" s="8">
+        <f>AVERAGE(D12:D16)</f>
+        <v>2.58438912178445E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="1">
+        <v>2</v>
+      </c>
+      <c r="D13" s="5"/>
+      <c r="E13" s="7"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="1">
+        <v>3</v>
+      </c>
+      <c r="D14" s="5"/>
+      <c r="E14" s="7"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="1">
+        <v>4</v>
+      </c>
+      <c r="D15" s="5"/>
+      <c r="E15" s="7"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="1">
+        <v>5</v>
+      </c>
+      <c r="D16" s="5"/>
+      <c r="E16" s="7"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A2:A16"/>
+    <mergeCell ref="B2:B6"/>
+    <mergeCell ref="E2:E6"/>
+    <mergeCell ref="B7:B11"/>
+    <mergeCell ref="E7:E11"/>
+    <mergeCell ref="B12:B16"/>
+    <mergeCell ref="E12:E16"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1208,10 +2070,10 @@
       <c r="F1" s="2"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="8">
+      <c r="A2" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="7">
         <v>0.2</v>
       </c>
       <c r="C2" s="1">
@@ -1220,7 +2082,7 @@
       <c r="D2" s="3">
         <v>6.0960731897987297E-4</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="8">
         <f>AVERAGE(D2:D4)</f>
         <v>6.5436713648982334E-4</v>
       </c>
@@ -1229,32 +2091,32 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
       <c r="D3" s="4">
         <v>1.2366666655837901E-3</v>
       </c>
-      <c r="E3" s="8"/>
+      <c r="E3" s="7"/>
       <c r="F3" s="9"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
       <c r="D4" s="3">
         <v>1.16827424905807E-4</v>
       </c>
-      <c r="E4" s="8"/>
+      <c r="E4" s="7"/>
       <c r="F4" s="9"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7">
         <v>0.4</v>
       </c>
       <c r="C5" s="1">
@@ -1263,7 +2125,7 @@
       <c r="D5" s="4">
         <v>1.05738310578603E-3</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="8">
         <f>AVERAGE(D5:D7)</f>
         <v>1.0018018224488051E-3</v>
       </c>
@@ -1272,32 +2134,32 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
       <c r="C6" s="1">
         <v>2</v>
       </c>
       <c r="D6" s="4">
         <v>9.1605188150462502E-4</v>
       </c>
-      <c r="E6" s="8"/>
+      <c r="E6" s="7"/>
       <c r="F6" s="9"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
       <c r="C7" s="1">
         <v>3</v>
       </c>
       <c r="D7" s="4">
         <v>1.03197048005576E-3</v>
       </c>
-      <c r="E7" s="8"/>
+      <c r="E7" s="7"/>
       <c r="F7" s="9"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8">
+      <c r="A8" s="7"/>
+      <c r="B8" s="7">
         <v>0.6</v>
       </c>
       <c r="C8" s="1">
@@ -1306,7 +2168,7 @@
       <c r="D8" s="4">
         <v>8.5958764850758399E-4</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="8">
         <f>AVERAGE(D8:D10)</f>
         <v>3.5202572786763336E-4</v>
       </c>
@@ -1315,32 +2177,32 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
       <c r="C9" s="1">
         <v>2</v>
       </c>
       <c r="D9" s="3">
         <v>1.9315911817009E-5</v>
       </c>
-      <c r="E9" s="8"/>
+      <c r="E9" s="7"/>
       <c r="F9" s="9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
       <c r="C10" s="1">
         <v>3</v>
       </c>
       <c r="D10" s="3">
         <v>1.7717362327830701E-4</v>
       </c>
-      <c r="E10" s="8"/>
+      <c r="E10" s="7"/>
       <c r="F10" s="9"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7">
         <v>0.8</v>
       </c>
       <c r="C11" s="1">
@@ -1349,7 +2211,7 @@
       <c r="D11" s="4">
         <v>2.59495713031E-7</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="8">
         <f>AVERAGE(D11:D13)</f>
         <v>3.5361489409253331E-6</v>
       </c>
@@ -1358,27 +2220,27 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
       <c r="C12" s="1">
         <v>2</v>
       </c>
       <c r="D12" s="4">
         <v>3.1072735918849998E-6</v>
       </c>
-      <c r="E12" s="8"/>
+      <c r="E12" s="7"/>
       <c r="F12" s="9"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
       <c r="C13" s="1">
         <v>3</v>
       </c>
       <c r="D13" s="4">
         <v>7.2416775178600003E-6</v>
       </c>
-      <c r="E13" s="8"/>
+      <c r="E13" s="7"/>
       <c r="F13" s="9"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -1442,17 +2304,17 @@
       <c r="F1" s="2"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="8">
+      <c r="B2" s="7">
         <v>0.2</v>
       </c>
       <c r="C2" s="1">
         <v>1</v>
       </c>
       <c r="D2" s="5"/>
-      <c r="E2" s="7" t="e">
+      <c r="E2" s="8" t="e">
         <f>AVERAGE(D2:D4)</f>
         <v>#DIV/0!</v>
       </c>
@@ -1461,35 +2323,35 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
       <c r="D3" s="5"/>
-      <c r="E3" s="8"/>
+      <c r="E3" s="7"/>
       <c r="F3" s="9"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
       <c r="D4" s="5"/>
-      <c r="E4" s="8"/>
+      <c r="E4" s="7"/>
       <c r="F4" s="9"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7">
         <v>0.4</v>
       </c>
       <c r="C5" s="1">
         <v>1</v>
       </c>
       <c r="D5" s="5"/>
-      <c r="E5" s="7" t="e">
+      <c r="E5" s="8" t="e">
         <f>AVERAGE(D5:D7)</f>
         <v>#DIV/0!</v>
       </c>
@@ -1498,35 +2360,35 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
       <c r="C6" s="1">
         <v>2</v>
       </c>
       <c r="D6" s="5"/>
-      <c r="E6" s="8"/>
+      <c r="E6" s="7"/>
       <c r="F6" s="9"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
       <c r="C7" s="1">
         <v>3</v>
       </c>
       <c r="D7" s="5"/>
-      <c r="E7" s="8"/>
+      <c r="E7" s="7"/>
       <c r="F7" s="9"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8">
+      <c r="A8" s="7"/>
+      <c r="B8" s="7">
         <v>0.6</v>
       </c>
       <c r="C8" s="1">
         <v>1</v>
       </c>
       <c r="D8" s="5"/>
-      <c r="E8" s="7" t="e">
+      <c r="E8" s="8" t="e">
         <f>AVERAGE(D8:D10)</f>
         <v>#DIV/0!</v>
       </c>
@@ -1535,35 +2397,35 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
       <c r="C9" s="1">
         <v>2</v>
       </c>
       <c r="D9" s="5"/>
-      <c r="E9" s="8"/>
+      <c r="E9" s="7"/>
       <c r="F9" s="9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
       <c r="C10" s="1">
         <v>3</v>
       </c>
       <c r="D10" s="5"/>
-      <c r="E10" s="8"/>
+      <c r="E10" s="7"/>
       <c r="F10" s="9"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7">
         <v>0.8</v>
       </c>
       <c r="C11" s="1">
         <v>1</v>
       </c>
       <c r="D11" s="5"/>
-      <c r="E11" s="7" t="e">
+      <c r="E11" s="8" t="e">
         <f>AVERAGE(D11:D13)</f>
         <v>#DIV/0!</v>
       </c>
@@ -1572,23 +2434,23 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
       <c r="C12" s="1">
         <v>2</v>
       </c>
       <c r="D12" s="5"/>
-      <c r="E12" s="8"/>
+      <c r="E12" s="7"/>
       <c r="F12" s="9"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
       <c r="C13" s="1">
         <v>3</v>
       </c>
       <c r="D13" s="5"/>
-      <c r="E13" s="8"/>
+      <c r="E13" s="7"/>
       <c r="F13" s="9"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -1656,7 +2518,7 @@
       <c r="A2" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="8">
+      <c r="B2" s="7">
         <v>0.2</v>
       </c>
       <c r="C2" s="1">
@@ -1665,7 +2527,7 @@
       <c r="D2" s="5">
         <v>1.10536709177707E-3</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="8">
         <f>AVERAGE(D2:D4)</f>
         <v>1.1309055570820001E-3</v>
       </c>
@@ -1675,24 +2537,24 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="11"/>
-      <c r="B3" s="8"/>
+      <c r="B3" s="7"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
       <c r="D3" s="5">
         <v>1.1564440223869299E-3</v>
       </c>
-      <c r="E3" s="8"/>
+      <c r="E3" s="7"/>
       <c r="F3" s="9"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="11"/>
-      <c r="B4" s="8"/>
+      <c r="B4" s="7"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
       <c r="D4" s="5"/>
-      <c r="E4" s="8"/>
+      <c r="E4" s="7"/>
       <c r="F4" s="9"/>
       <c r="H4" s="5">
         <v>1.0454979313277799E-3</v>
@@ -1700,7 +2562,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="11"/>
-      <c r="B5" s="8">
+      <c r="B5" s="7">
         <v>0.4</v>
       </c>
       <c r="C5" s="1">
@@ -1709,7 +2571,7 @@
       <c r="D5" s="5">
         <v>8.6130823085382702E-4</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="8">
         <f>AVERAGE(D5:D7)</f>
         <v>9.6691710734251137E-4</v>
       </c>
@@ -1719,31 +2581,31 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="11"/>
-      <c r="B6" s="8"/>
+      <c r="B6" s="7"/>
       <c r="C6" s="1">
         <v>2</v>
       </c>
       <c r="D6" s="5">
         <v>1.14094976896151E-3</v>
       </c>
-      <c r="E6" s="8"/>
+      <c r="E6" s="7"/>
       <c r="F6" s="9"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="11"/>
-      <c r="B7" s="8"/>
+      <c r="B7" s="7"/>
       <c r="C7" s="1">
         <v>3</v>
       </c>
       <c r="D7" s="5">
         <v>8.9849332221219702E-4</v>
       </c>
-      <c r="E7" s="8"/>
+      <c r="E7" s="7"/>
       <c r="F7" s="9"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="11"/>
-      <c r="B8" s="8">
+      <c r="B8" s="7">
         <v>0.6</v>
       </c>
       <c r="C8" s="1">
@@ -1752,7 +2614,7 @@
       <c r="D8" s="5">
         <v>9.1338658759890896E-4</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="8">
         <f>AVERAGE(D8:D10)</f>
         <v>8.8801660113643126E-4</v>
       </c>
@@ -1762,31 +2624,31 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="11"/>
-      <c r="B9" s="8"/>
+      <c r="B9" s="7"/>
       <c r="C9" s="1">
         <v>2</v>
       </c>
       <c r="D9" s="6">
         <v>9.8614258166756607E-4</v>
       </c>
-      <c r="E9" s="8"/>
+      <c r="E9" s="7"/>
       <c r="F9" s="9"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="11"/>
-      <c r="B10" s="8"/>
+      <c r="B10" s="7"/>
       <c r="C10" s="1">
         <v>3</v>
       </c>
       <c r="D10" s="5">
         <v>7.6452063414281896E-4</v>
       </c>
-      <c r="E10" s="8"/>
+      <c r="E10" s="7"/>
       <c r="F10" s="9"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="11"/>
-      <c r="B11" s="8">
+      <c r="B11" s="7">
         <v>0.8</v>
       </c>
       <c r="C11" s="1">
@@ -1795,7 +2657,7 @@
       <c r="D11" s="5">
         <v>7.3798692719643404E-4</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="8">
         <f>AVERAGE(D11:D13)</f>
         <v>7.3798692719643404E-4</v>
       </c>
@@ -1805,22 +2667,22 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="11"/>
-      <c r="B12" s="8"/>
+      <c r="B12" s="7"/>
       <c r="C12" s="1">
         <v>2</v>
       </c>
       <c r="D12" s="5"/>
-      <c r="E12" s="8"/>
+      <c r="E12" s="7"/>
       <c r="F12" s="9"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="11"/>
-      <c r="B13" s="8"/>
+      <c r="B13" s="7"/>
       <c r="C13" s="1">
         <v>3</v>
       </c>
       <c r="D13" s="5"/>
-      <c r="E13" s="8"/>
+      <c r="E13" s="7"/>
       <c r="F13" s="9"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
@@ -1884,10 +2746,10 @@
       <c r="F1" s="2"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="8">
+      <c r="B2" s="7">
         <v>0.2</v>
       </c>
       <c r="C2" s="1">
@@ -1896,7 +2758,7 @@
       <c r="D2" s="5">
         <v>1.0456008086864E-3</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="8">
         <f>AVERAGE(D2:D5)</f>
         <v>1.062493548102375E-3</v>
       </c>
@@ -1905,44 +2767,44 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
       <c r="D3" s="4">
         <v>1.09467266122671E-3</v>
       </c>
-      <c r="E3" s="8"/>
+      <c r="E3" s="7"/>
       <c r="F3" s="9"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
       <c r="D4" s="4">
         <v>1.0701604268465201E-3</v>
       </c>
-      <c r="E4" s="8"/>
+      <c r="E4" s="7"/>
       <c r="F4" s="9"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
       <c r="C5" s="1">
         <v>4</v>
       </c>
       <c r="D5" s="5">
         <v>1.0395402956498701E-3</v>
       </c>
-      <c r="E5" s="8"/>
+      <c r="E5" s="7"/>
       <c r="F5" s="9"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8">
+      <c r="A6" s="7"/>
+      <c r="B6" s="7">
         <v>0.4</v>
       </c>
       <c r="C6" s="1">
@@ -1951,7 +2813,7 @@
       <c r="D6" s="5">
         <v>1.3060672401840299E-3</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="8">
         <f>AVERAGE(D6:D9)</f>
         <v>1.0119003627781611E-3</v>
       </c>
@@ -1960,44 +2822,44 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
       <c r="C7" s="1">
         <v>2</v>
       </c>
       <c r="D7" s="4">
         <v>9.3494025407098202E-4</v>
       </c>
-      <c r="E7" s="8"/>
+      <c r="E7" s="7"/>
       <c r="F7" s="9"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
       <c r="C8" s="1">
         <v>3</v>
       </c>
       <c r="D8" s="4">
         <v>1.11627799419256E-3</v>
       </c>
-      <c r="E8" s="8"/>
+      <c r="E8" s="7"/>
       <c r="F8" s="9"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
       <c r="C9" s="1">
         <v>4</v>
       </c>
       <c r="D9" s="5">
         <v>6.9031596266507205E-4</v>
       </c>
-      <c r="E9" s="8"/>
+      <c r="E9" s="7"/>
       <c r="F9" s="9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8">
+      <c r="A10" s="7"/>
+      <c r="B10" s="7">
         <v>0.6</v>
       </c>
       <c r="C10" s="1">
@@ -2006,7 +2868,7 @@
       <c r="D10" s="5">
         <v>1.1258039438553501E-3</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="8">
         <f>AVERAGE(D10:D13)</f>
         <v>1.0913926731899966E-3</v>
       </c>
@@ -2015,44 +2877,44 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
       <c r="C11" s="1">
         <v>2</v>
       </c>
       <c r="D11" s="4">
         <v>9.6767982546831603E-4</v>
       </c>
-      <c r="E11" s="8"/>
+      <c r="E11" s="7"/>
       <c r="F11" s="9"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
       <c r="C12" s="1">
         <v>3</v>
       </c>
       <c r="D12" s="5">
         <v>1.0759200072066801E-3</v>
       </c>
-      <c r="E12" s="8"/>
+      <c r="E12" s="7"/>
       <c r="F12" s="9"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
       <c r="C13" s="1">
         <v>4</v>
       </c>
       <c r="D13" s="5">
         <v>1.1961669162296399E-3</v>
       </c>
-      <c r="E13" s="8"/>
+      <c r="E13" s="7"/>
       <c r="F13" s="9"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8">
+      <c r="A14" s="7"/>
+      <c r="B14" s="7">
         <v>0.8</v>
       </c>
       <c r="C14" s="1">
@@ -2061,7 +2923,7 @@
       <c r="D14" s="4">
         <v>8.5667911779765201E-4</v>
       </c>
-      <c r="E14" s="7">
+      <c r="E14" s="8">
         <f>AVERAGE(D14:D17)</f>
         <v>8.7466814763753067E-4</v>
       </c>
@@ -2070,39 +2932,39 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
       <c r="C15" s="1">
         <v>2</v>
       </c>
       <c r="D15" s="4">
         <v>6.7159374136605899E-4</v>
       </c>
-      <c r="E15" s="7"/>
+      <c r="E15" s="8"/>
       <c r="F15" s="9"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
       <c r="C16" s="1">
         <v>3</v>
       </c>
       <c r="D16" s="5">
         <v>9.2119835353706196E-4</v>
       </c>
-      <c r="E16" s="8"/>
+      <c r="E16" s="7"/>
       <c r="F16" s="9"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
       <c r="C17" s="1">
         <v>4</v>
       </c>
       <c r="D17" s="5">
         <v>1.0492013778493499E-3</v>
       </c>
-      <c r="E17" s="8"/>
+      <c r="E17" s="7"/>
       <c r="F17" s="9"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -2166,10 +3028,10 @@
       <c r="F1" s="2"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="8">
+      <c r="B2" s="7">
         <v>0.2</v>
       </c>
       <c r="C2" s="1">
@@ -2178,7 +3040,7 @@
       <c r="D2" s="5">
         <v>9.9861308351742407E-4</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="8">
         <f>AVERAGE(D2:D6)</f>
         <v>9.7673568309604702E-4</v>
       </c>
@@ -2187,56 +3049,56 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
       <c r="D3" s="5">
         <v>9.4235074996974397E-4</v>
       </c>
-      <c r="E3" s="8"/>
+      <c r="E3" s="7"/>
       <c r="F3" s="9"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
       <c r="D4" s="5">
         <v>9.5469248937918197E-4</v>
       </c>
-      <c r="E4" s="8"/>
+      <c r="E4" s="7"/>
       <c r="F4" s="9"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
       <c r="C5" s="1">
         <v>4</v>
       </c>
       <c r="D5" s="5">
         <v>8.6633270051169502E-4</v>
       </c>
-      <c r="E5" s="8"/>
+      <c r="E5" s="7"/>
       <c r="F5" s="9"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
       <c r="C6" s="1">
         <v>5</v>
       </c>
       <c r="D6" s="5">
         <v>1.1216893921021901E-3</v>
       </c>
-      <c r="E6" s="8"/>
+      <c r="E6" s="7"/>
       <c r="F6" s="9"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7">
         <v>0.4</v>
       </c>
       <c r="C7" s="1">
@@ -2245,7 +3107,7 @@
       <c r="D7" s="5">
         <v>8.9437967332690502E-4</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="8">
         <f>AVERAGE(D7:D11)</f>
         <v>9.1960146331700621E-4</v>
       </c>
@@ -2254,56 +3116,56 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
       <c r="C8" s="1">
         <v>2</v>
       </c>
       <c r="D8" s="5">
         <v>8.0541983045422604E-4</v>
       </c>
-      <c r="E8" s="8"/>
+      <c r="E8" s="7"/>
       <c r="F8" s="9"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
       <c r="C9" s="1">
         <v>3</v>
       </c>
       <c r="D9" s="5">
         <v>1.00808827591755E-3</v>
       </c>
-      <c r="E9" s="8"/>
+      <c r="E9" s="7"/>
       <c r="F9" s="9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
       <c r="C10" s="1">
         <v>4</v>
       </c>
       <c r="D10" s="5">
         <v>8.4824047590335004E-4</v>
       </c>
-      <c r="E10" s="8"/>
+      <c r="E10" s="7"/>
       <c r="F10" s="9"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
       <c r="C11" s="1">
         <v>5</v>
       </c>
       <c r="D11" s="5">
         <v>1.041879060983E-3</v>
       </c>
-      <c r="E11" s="8"/>
+      <c r="E11" s="7"/>
       <c r="F11" s="9"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8">
+      <c r="A12" s="7"/>
+      <c r="B12" s="7">
         <v>0.6</v>
       </c>
       <c r="C12" s="1">
@@ -2312,7 +3174,7 @@
       <c r="D12" s="5">
         <v>1.0713286556024301E-3</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="8">
         <f>AVERAGE(D12:D16)</f>
         <v>9.9714248838866926E-4</v>
       </c>
@@ -2321,56 +3183,56 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
       <c r="C13" s="1">
         <v>2</v>
       </c>
       <c r="D13" s="5">
         <v>9.4514997141361995E-4</v>
       </c>
-      <c r="E13" s="8"/>
+      <c r="E13" s="7"/>
       <c r="F13" s="9"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
       <c r="C14" s="1">
         <v>3</v>
       </c>
       <c r="D14" s="5">
         <v>9.3634055614079403E-4</v>
       </c>
-      <c r="E14" s="8"/>
+      <c r="E14" s="7"/>
       <c r="F14" s="9"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
       <c r="C15" s="1">
         <v>4</v>
       </c>
       <c r="D15" s="5">
         <v>1.13227515241877E-3</v>
       </c>
-      <c r="E15" s="8"/>
+      <c r="E15" s="7"/>
       <c r="F15" s="9"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
       <c r="C16" s="1">
         <v>5</v>
       </c>
       <c r="D16" s="5">
         <v>9.0061810636773195E-4</v>
       </c>
-      <c r="E16" s="8"/>
+      <c r="E16" s="7"/>
       <c r="F16" s="9"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8">
+      <c r="A17" s="7"/>
+      <c r="B17" s="7">
         <v>0.8</v>
       </c>
       <c r="C17" s="1">
@@ -2379,7 +3241,7 @@
       <c r="D17" s="5">
         <v>8.9938830820844096E-4</v>
       </c>
-      <c r="E17" s="7">
+      <c r="E17" s="8">
         <f>AVERAGE(D17:D21)</f>
         <v>1.0868212538811403E-3</v>
       </c>
@@ -2388,49 +3250,49 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
       <c r="C18" s="1">
         <v>2</v>
       </c>
       <c r="D18" s="5">
         <v>1.1217861371005801E-3</v>
       </c>
-      <c r="E18" s="7"/>
+      <c r="E18" s="8"/>
       <c r="F18" s="9"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
       <c r="C19" s="1">
         <v>3</v>
       </c>
       <c r="D19" s="5">
         <v>1.1543127248442499E-3</v>
       </c>
-      <c r="E19" s="8"/>
+      <c r="E19" s="7"/>
       <c r="F19" s="9"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
       <c r="C20" s="1">
         <v>4</v>
       </c>
       <c r="D20" s="5">
         <v>1.1717978453712899E-3</v>
       </c>
-      <c r="E20" s="8"/>
+      <c r="E20" s="7"/>
       <c r="F20" s="9"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
+      <c r="A21" s="7"/>
+      <c r="B21" s="7"/>
       <c r="C21" s="1">
         <v>5</v>
       </c>
       <c r="D21" s="5"/>
-      <c r="E21" s="8"/>
+      <c r="E21" s="7"/>
       <c r="F21" s="9"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
@@ -2493,10 +3355,10 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="7" t="s">
         <v>14</v>
       </c>
       <c r="C2" s="1">
@@ -2505,56 +3367,56 @@
       <c r="D2" s="5">
         <v>4.6060741068411704E-3</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="8">
         <f>AVERAGE(D2:D6)</f>
         <v>4.3943148562279851E-3</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
       <c r="D3" s="5">
         <v>4.1201631529217001E-3</v>
       </c>
-      <c r="E3" s="8"/>
+      <c r="E3" s="7"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
       <c r="D4" s="5">
         <v>4.3891970092903897E-3</v>
       </c>
-      <c r="E4" s="8"/>
+      <c r="E4" s="7"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
       <c r="C5" s="1">
         <v>4</v>
       </c>
       <c r="D5" s="5">
         <v>4.4618251558586801E-3</v>
       </c>
-      <c r="E5" s="8"/>
+      <c r="E5" s="7"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
       <c r="C6" s="1">
         <v>5</v>
       </c>
       <c r="D6" s="5"/>
-      <c r="E6" s="8"/>
+      <c r="E6" s="7"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8" t="s">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C7" s="1">
@@ -2563,52 +3425,52 @@
       <c r="D7" s="5">
         <v>1.04107924830786E-3</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="8">
         <f>AVERAGE(D7:D11)</f>
         <v>1.23803134268238E-3</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
       <c r="C8" s="1">
         <v>2</v>
       </c>
       <c r="D8" s="5">
         <v>1.4349834370568999E-3</v>
       </c>
-      <c r="E8" s="8"/>
+      <c r="E8" s="7"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
       <c r="C9" s="1">
         <v>3</v>
       </c>
       <c r="D9" s="5"/>
-      <c r="E9" s="8"/>
+      <c r="E9" s="7"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
       <c r="C10" s="1">
         <v>4</v>
       </c>
       <c r="D10" s="5"/>
-      <c r="E10" s="8"/>
+      <c r="E10" s="7"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
       <c r="C11" s="1">
         <v>5</v>
       </c>
       <c r="D11" s="5"/>
-      <c r="E11" s="8"/>
+      <c r="E11" s="7"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8" t="s">
+      <c r="A12" s="7"/>
+      <c r="B12" s="7" t="s">
         <v>16</v>
       </c>
       <c r="C12" s="1">
@@ -2617,52 +3479,476 @@
       <c r="D12" s="5">
         <v>8.6090646012557603E-4</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="8">
         <f>AVERAGE(D12:D16)</f>
         <v>9.0367629214962596E-4</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
       <c r="C13" s="1">
         <v>2</v>
       </c>
       <c r="D13" s="5">
         <v>9.5744145788180795E-4</v>
       </c>
-      <c r="E13" s="8"/>
+      <c r="E13" s="7"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
       <c r="C14" s="1">
         <v>3</v>
       </c>
       <c r="D14" s="5">
         <v>8.2489508743011997E-4</v>
       </c>
-      <c r="E14" s="8"/>
+      <c r="E14" s="7"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
       <c r="C15" s="1">
         <v>4</v>
       </c>
       <c r="D15" s="5">
         <v>9.7146216316099999E-4</v>
       </c>
-      <c r="E15" s="8"/>
+      <c r="E15" s="7"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
       <c r="C16" s="1">
         <v>5</v>
       </c>
       <c r="D16" s="5"/>
-      <c r="E16" s="8"/>
+      <c r="E16" s="7"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A2:A16"/>
+    <mergeCell ref="B2:B6"/>
+    <mergeCell ref="E2:E6"/>
+    <mergeCell ref="B7:B11"/>
+    <mergeCell ref="E7:E11"/>
+    <mergeCell ref="B12:B16"/>
+    <mergeCell ref="E12:E16"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70966A2D-672A-451B-A3A3-B783FCE2984F}">
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="22.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="5">
+        <v>1.81177350386232E-3</v>
+      </c>
+      <c r="E2" s="8">
+        <f>AVERAGE(D2:D6)</f>
+        <v>1.8132870925671599E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="1">
+        <v>2</v>
+      </c>
+      <c r="D3" s="5">
+        <v>1.8148006812720001E-3</v>
+      </c>
+      <c r="E3" s="7"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="1">
+        <v>3</v>
+      </c>
+      <c r="D4" s="5"/>
+      <c r="E4" s="7"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="1">
+        <v>4</v>
+      </c>
+      <c r="D5" s="5"/>
+      <c r="E5" s="7"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="1">
+        <v>5</v>
+      </c>
+      <c r="D6" s="5"/>
+      <c r="E6" s="7"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="1">
+        <v>1</v>
+      </c>
+      <c r="D7" s="5">
+        <v>1.22745404238443E-3</v>
+      </c>
+      <c r="E7" s="8">
+        <f>AVERAGE(D7:D11)</f>
+        <v>1.220176512275965E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="1">
+        <v>2</v>
+      </c>
+      <c r="D8" s="5">
+        <v>1.2128989821674999E-3</v>
+      </c>
+      <c r="E8" s="7"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="1">
+        <v>3</v>
+      </c>
+      <c r="D9" s="5"/>
+      <c r="E9" s="7"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="1">
+        <v>4</v>
+      </c>
+      <c r="D10" s="5"/>
+      <c r="E10" s="7"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="1">
+        <v>5</v>
+      </c>
+      <c r="D11" s="5"/>
+      <c r="E11" s="7"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="7"/>
+      <c r="B12" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1</v>
+      </c>
+      <c r="D12" s="5">
+        <v>8.3363125861713003E-4</v>
+      </c>
+      <c r="E12" s="8">
+        <f>AVERAGE(D12:D16)</f>
+        <v>8.3363125861713003E-4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="1">
+        <v>2</v>
+      </c>
+      <c r="D13" s="5"/>
+      <c r="E13" s="7"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="1">
+        <v>3</v>
+      </c>
+      <c r="D14" s="5"/>
+      <c r="E14" s="7"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="1">
+        <v>4</v>
+      </c>
+      <c r="D15" s="5"/>
+      <c r="E15" s="7"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="1">
+        <v>5</v>
+      </c>
+      <c r="D16" s="5"/>
+      <c r="E16" s="7"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A2:A16"/>
+    <mergeCell ref="B2:B6"/>
+    <mergeCell ref="E2:E6"/>
+    <mergeCell ref="B7:B11"/>
+    <mergeCell ref="E7:E11"/>
+    <mergeCell ref="B12:B16"/>
+    <mergeCell ref="E12:E16"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E822B54-E6B9-4F6D-BD17-4242A3C7CFDB}">
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="22.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="5">
+        <v>8.8432581244842993E-3</v>
+      </c>
+      <c r="E2" s="8">
+        <f>AVERAGE(D2:D6)</f>
+        <v>8.8432581244842993E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="7"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="1">
+        <v>2</v>
+      </c>
+      <c r="D3" s="5"/>
+      <c r="E3" s="7"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="1">
+        <v>3</v>
+      </c>
+      <c r="D4" s="5"/>
+      <c r="E4" s="7"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="1">
+        <v>4</v>
+      </c>
+      <c r="D5" s="5"/>
+      <c r="E5" s="7"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="1">
+        <v>5</v>
+      </c>
+      <c r="D6" s="5"/>
+      <c r="E6" s="7"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="1">
+        <v>1</v>
+      </c>
+      <c r="D7" s="5">
+        <v>8.4438215453025E-3</v>
+      </c>
+      <c r="E7" s="8">
+        <f>AVERAGE(D7:D11)</f>
+        <v>8.2572491277925208E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="1">
+        <v>2</v>
+      </c>
+      <c r="D8" s="5">
+        <v>8.07067671028254E-3</v>
+      </c>
+      <c r="E8" s="7"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="1">
+        <v>3</v>
+      </c>
+      <c r="D9" s="5"/>
+      <c r="E9" s="7"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="1">
+        <v>4</v>
+      </c>
+      <c r="D10" s="5"/>
+      <c r="E10" s="7"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="1">
+        <v>5</v>
+      </c>
+      <c r="D11" s="5"/>
+      <c r="E11" s="7"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="7"/>
+      <c r="B12" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1</v>
+      </c>
+      <c r="D12" s="5">
+        <v>6.9609433108972002E-3</v>
+      </c>
+      <c r="E12" s="8">
+        <f>AVERAGE(D12:D16)</f>
+        <v>6.9609433108972002E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="1">
+        <v>2</v>
+      </c>
+      <c r="D13" s="5"/>
+      <c r="E13" s="7"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="1">
+        <v>3</v>
+      </c>
+      <c r="D14" s="5"/>
+      <c r="E14" s="7"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="1">
+        <v>4</v>
+      </c>
+      <c r="D15" s="5"/>
+      <c r="E15" s="7"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="1">
+        <v>5</v>
+      </c>
+      <c r="D16" s="5"/>
+      <c r="E16" s="7"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="10" t="s">

--- a/_resultados/_resultados.xlsx
+++ b/_resultados/_resultados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ravar\Documents\GitHub\recsys-fair-federation-flower\_resultados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68A895CF-C1D5-4780-B5D5-272815B2F365}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82489BED-CE83-4DCE-B8C1-80276CB458BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="14">
   <si>
     <t>Estratégia</t>
   </si>
@@ -133,6 +133,12 @@
   <si>
     <t>Gender</t>
   </si>
+  <si>
+    <t>0.0028247020506802223</t>
+  </si>
+  <si>
+    <t>0.002841222981759123</t>
+  </si>
 </sst>
 </file>
 
@@ -179,7 +185,7 @@
       <family val="3"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -201,12 +207,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -245,16 +245,16 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -736,13 +736,13 @@
       <c r="E16" s="5"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -858,14 +858,9 @@
       </c>
       <c r="E7" s="6">
         <f>AVERAGE(D7:D11)</f>
-        <v>8.380429677643176E-3</v>
-      </c>
-      <c r="G7" s="3">
-        <v>7.8134741912483999E-3</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
+        <v>8.5661684923472904E-3</v>
+      </c>
+      <c r="G7" s="7"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="5"/>
@@ -874,15 +869,10 @@
         <v>2</v>
       </c>
       <c r="D8" s="3">
-        <v>8.07067671028254E-3</v>
+        <v>8.9993707838031105E-3</v>
       </c>
       <c r="E8" s="5"/>
-      <c r="G8" s="4">
-        <v>8.2299496186085501E-3</v>
-      </c>
-      <c r="H8">
-        <v>2</v>
-      </c>
+      <c r="G8" s="7"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="5"/>
@@ -894,12 +884,7 @@
         <v>8.5229916662684403E-3</v>
       </c>
       <c r="E9" s="5"/>
-      <c r="G9" s="3">
-        <v>8.0214303230703894E-3</v>
-      </c>
-      <c r="H9">
-        <v>3</v>
-      </c>
+      <c r="G9" s="7"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="5"/>
@@ -911,7 +896,7 @@
         <v>8.6347088477538494E-3</v>
       </c>
       <c r="E10" s="5"/>
-      <c r="G10" s="3"/>
+      <c r="G10" s="7"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="5"/>
@@ -923,7 +908,7 @@
         <v>8.2299496186085501E-3</v>
       </c>
       <c r="E11" s="5"/>
-      <c r="G11" s="3"/>
+      <c r="G11" s="7"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="5"/>
@@ -934,11 +919,17 @@
         <v>1</v>
       </c>
       <c r="D12" s="3">
-        <v>7.55287640110498E-3</v>
+        <v>6.2969138289247001E-3</v>
       </c>
       <c r="E12" s="6">
         <f>AVERAGE(D12:D16)</f>
-        <v>6.9125969549290039E-3</v>
+        <v>6.4232932671029145E-3</v>
+      </c>
+      <c r="G12" s="3">
+        <v>6.9679785064951797E-3</v>
+      </c>
+      <c r="H12">
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
@@ -951,6 +942,12 @@
         <v>6.4076776396648598E-3</v>
       </c>
       <c r="E13" s="5"/>
+      <c r="G13" s="3">
+        <v>6.9169172748136899E-3</v>
+      </c>
+      <c r="H13">
+        <v>8</v>
+      </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="5"/>
@@ -959,9 +956,10 @@
         <v>3</v>
       </c>
       <c r="D14" s="3">
-        <v>6.9679785064951797E-3</v>
+        <v>6.2667263273711001E-3</v>
       </c>
       <c r="E14" s="5"/>
+      <c r="G14" s="3"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="5"/>
@@ -973,6 +971,7 @@
         <v>6.7218552724509998E-3</v>
       </c>
       <c r="E15" s="5"/>
+      <c r="G15" s="3"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="5"/>
@@ -982,15 +981,16 @@
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="5"/>
+      <c r="G16" s="3"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -1015,7 +1015,7 @@
   <cols>
     <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="22.77734375" customWidth="1"/>
-    <col min="7" max="7" width="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.6" x14ac:dyDescent="0.35">
@@ -1108,11 +1108,11 @@
         <f>AVERAGE(D7:D11)</f>
         <v>2.7172660575796701E-3</v>
       </c>
-      <c r="G7" s="4">
-        <v>2.67957260688739E-3</v>
+      <c r="G7" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -1125,11 +1125,11 @@
         <v>2.7552147060860401E-3</v>
       </c>
       <c r="E8" s="5"/>
-      <c r="G8" s="4">
-        <v>2.7552147060860401E-3</v>
+      <c r="G8" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="H8">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
@@ -1142,12 +1142,7 @@
         <v>2.62843134317815E-3</v>
       </c>
       <c r="E9" s="5"/>
-      <c r="G9" s="4">
-        <v>2.62843134317815E-3</v>
-      </c>
-      <c r="H9">
-        <v>3</v>
-      </c>
+      <c r="G9" s="7"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="5"/>
@@ -1184,7 +1179,10 @@
       </c>
       <c r="E12" s="6">
         <f>AVERAGE(D12:D16)</f>
-        <v>2.4034746433161101E-3</v>
+        <v>2.4650105258814206E-3</v>
+      </c>
+      <c r="G12" s="3">
+        <v>2.5224244786699302E-3</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
@@ -1197,6 +1195,9 @@
         <v>2.4762825423162902E-3</v>
       </c>
       <c r="E13" s="5"/>
+      <c r="G13" s="3">
+        <v>2.5922042207888402E-3</v>
+      </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="5"/>
@@ -1208,6 +1209,7 @@
         <v>2.2977682884525799E-3</v>
       </c>
       <c r="E14" s="5"/>
+      <c r="G14" s="3"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="5"/>
@@ -1215,8 +1217,11 @@
       <c r="C15" s="1">
         <v>4</v>
       </c>
-      <c r="D15" s="3"/>
+      <c r="D15" s="3">
+        <v>2.5224244786699302E-3</v>
+      </c>
       <c r="E15" s="5"/>
+      <c r="G15" s="3"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="5"/>
@@ -1224,17 +1229,20 @@
       <c r="C16" s="1">
         <v>5</v>
       </c>
-      <c r="D16" s="3"/>
+      <c r="D16" s="3">
+        <v>2.5922042207888402E-3</v>
+      </c>
       <c r="E16" s="5"/>
+      <c r="G16" s="3"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/_resultados/_resultados.xlsx
+++ b/_resultados/_resultados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ravar\Documents\GitHub\recsys-fair-federation-flower\_resultados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82489BED-CE83-4DCE-B8C1-80276CB458BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ABD6506-4088-463C-A120-7069B41A585D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Activity" sheetId="12" r:id="rId1"/>
@@ -245,6 +245,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -254,7 +255,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -560,10 +560,10 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="1">
@@ -572,54 +572,54 @@
       <c r="D2" s="3">
         <v>1.81177350386232E-3</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="7">
         <f>AVERAGE(D2:D6)</f>
         <v>1.8485946957060599E-3</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
       <c r="D3" s="3">
         <v>1.8148006812720001E-3</v>
       </c>
-      <c r="E3" s="5"/>
+      <c r="E3" s="6"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
       <c r="D4" s="3">
         <v>1.9192099019838601E-3</v>
       </c>
-      <c r="E4" s="5"/>
+      <c r="E4" s="6"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="5"/>
-      <c r="B5" s="5"/>
+      <c r="A5" s="6"/>
+      <c r="B5" s="6"/>
       <c r="C5" s="1">
         <v>4</v>
       </c>
       <c r="D5" s="3"/>
-      <c r="E5" s="5"/>
+      <c r="E5" s="6"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5"/>
+      <c r="A6" s="6"/>
+      <c r="B6" s="6"/>
       <c r="C6" s="1">
         <v>5</v>
       </c>
       <c r="D6" s="3"/>
-      <c r="E6" s="5"/>
+      <c r="E6" s="6"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="5"/>
-      <c r="B7" s="5" t="s">
+      <c r="A7" s="6"/>
+      <c r="B7" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="1">
@@ -628,56 +628,56 @@
       <c r="D7" s="3">
         <v>1.22745404238443E-3</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="7">
         <f>AVERAGE(D7:D11)</f>
         <v>1.2352179388571624E-3</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5"/>
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
       <c r="C8" s="1">
         <v>2</v>
       </c>
       <c r="D8" s="3">
         <v>1.2128989821674999E-3</v>
       </c>
-      <c r="E8" s="5"/>
+      <c r="E8" s="6"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
       <c r="C9" s="1">
         <v>3</v>
       </c>
       <c r="D9" s="3">
         <v>1.2072314178239499E-3</v>
       </c>
-      <c r="E9" s="5"/>
+      <c r="E9" s="6"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
       <c r="C10" s="1">
         <v>4</v>
       </c>
       <c r="D10" s="3">
         <v>1.2932873130527701E-3</v>
       </c>
-      <c r="E10" s="5"/>
+      <c r="E10" s="6"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
+      <c r="A11" s="6"/>
+      <c r="B11" s="6"/>
       <c r="C11" s="1">
         <v>5</v>
       </c>
       <c r="D11" s="3"/>
-      <c r="E11" s="5"/>
+      <c r="E11" s="6"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5" t="s">
+      <c r="A12" s="6"/>
+      <c r="B12" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C12" s="1">
@@ -686,63 +686,63 @@
       <c r="D12" s="3">
         <v>7.2837430705559596E-4</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="7">
         <f>AVERAGE(D12:D16)</f>
         <v>8.179226084032836E-4</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
       <c r="C13" s="1">
         <v>2</v>
       </c>
       <c r="D13" s="3">
         <v>8.4607791428294903E-4</v>
       </c>
-      <c r="E13" s="5"/>
+      <c r="E13" s="6"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
       <c r="C14" s="1">
         <v>3</v>
       </c>
       <c r="D14" s="3">
         <v>8.6882802551990898E-4</v>
       </c>
-      <c r="E14" s="5"/>
+      <c r="E14" s="6"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
       <c r="C15" s="1">
         <v>4</v>
       </c>
       <c r="D15" s="3">
         <v>8.6728801473186397E-4</v>
       </c>
-      <c r="E15" s="5"/>
+      <c r="E15" s="6"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
       <c r="C16" s="1">
         <v>5</v>
       </c>
       <c r="D16" s="3">
         <v>7.7904478042610005E-4</v>
       </c>
-      <c r="E16" s="5"/>
+      <c r="E16" s="6"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -788,10 +788,10 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="1">
@@ -800,54 +800,54 @@
       <c r="D2" s="3">
         <v>8.8432581244842993E-3</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="7">
         <f>AVERAGE(D2:D6)</f>
         <v>8.9594988217164395E-3</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
       <c r="D3" s="3">
         <v>8.9353771851844298E-3</v>
       </c>
-      <c r="E3" s="5"/>
+      <c r="E3" s="6"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
       <c r="D4" s="3">
         <v>9.0998611554805892E-3</v>
       </c>
-      <c r="E4" s="5"/>
+      <c r="E4" s="6"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="5"/>
-      <c r="B5" s="5"/>
+      <c r="A5" s="6"/>
+      <c r="B5" s="6"/>
       <c r="C5" s="1">
         <v>4</v>
       </c>
       <c r="D5" s="3"/>
-      <c r="E5" s="5"/>
+      <c r="E5" s="6"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5"/>
+      <c r="A6" s="6"/>
+      <c r="B6" s="6"/>
       <c r="C6" s="1">
         <v>5</v>
       </c>
       <c r="D6" s="3"/>
-      <c r="E6" s="5"/>
+      <c r="E6" s="6"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="5"/>
-      <c r="B7" s="5" t="s">
+      <c r="A7" s="6"/>
+      <c r="B7" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="1">
@@ -856,63 +856,63 @@
       <c r="D7" s="3">
         <v>8.4438215453025E-3</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="7">
         <f>AVERAGE(D7:D11)</f>
         <v>8.5661684923472904E-3</v>
       </c>
-      <c r="G7" s="7"/>
+      <c r="G7" s="4"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5"/>
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
       <c r="C8" s="1">
         <v>2</v>
       </c>
       <c r="D8" s="3">
         <v>8.9993707838031105E-3</v>
       </c>
-      <c r="E8" s="5"/>
-      <c r="G8" s="7"/>
+      <c r="E8" s="6"/>
+      <c r="G8" s="4"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
       <c r="C9" s="1">
         <v>3</v>
       </c>
       <c r="D9" s="3">
         <v>8.5229916662684403E-3</v>
       </c>
-      <c r="E9" s="5"/>
-      <c r="G9" s="7"/>
+      <c r="E9" s="6"/>
+      <c r="G9" s="4"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
       <c r="C10" s="1">
         <v>4</v>
       </c>
       <c r="D10" s="3">
         <v>8.6347088477538494E-3</v>
       </c>
-      <c r="E10" s="5"/>
-      <c r="G10" s="7"/>
+      <c r="E10" s="6"/>
+      <c r="G10" s="4"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
+      <c r="A11" s="6"/>
+      <c r="B11" s="6"/>
       <c r="C11" s="1">
         <v>5</v>
       </c>
       <c r="D11" s="3">
         <v>8.2299496186085501E-3</v>
       </c>
-      <c r="E11" s="5"/>
-      <c r="G11" s="7"/>
+      <c r="E11" s="6"/>
+      <c r="G11" s="4"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5" t="s">
+      <c r="A12" s="6"/>
+      <c r="B12" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C12" s="1">
@@ -921,7 +921,7 @@
       <c r="D12" s="3">
         <v>6.2969138289247001E-3</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="7">
         <f>AVERAGE(D12:D16)</f>
         <v>6.4232932671029145E-3</v>
       </c>
@@ -933,15 +933,15 @@
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
       <c r="C13" s="1">
         <v>2</v>
       </c>
       <c r="D13" s="3">
         <v>6.4076776396648598E-3</v>
       </c>
-      <c r="E13" s="5"/>
+      <c r="E13" s="6"/>
       <c r="G13" s="3">
         <v>6.9169172748136899E-3</v>
       </c>
@@ -950,47 +950,47 @@
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
       <c r="C14" s="1">
         <v>3</v>
       </c>
       <c r="D14" s="3">
         <v>6.2667263273711001E-3</v>
       </c>
-      <c r="E14" s="5"/>
+      <c r="E14" s="6"/>
       <c r="G14" s="3"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
       <c r="C15" s="1">
         <v>4</v>
       </c>
       <c r="D15" s="3">
         <v>6.7218552724509998E-3</v>
       </c>
-      <c r="E15" s="5"/>
+      <c r="E15" s="6"/>
       <c r="G15" s="3"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
       <c r="C16" s="1">
         <v>5</v>
       </c>
       <c r="D16" s="3"/>
-      <c r="E16" s="5"/>
+      <c r="E16" s="6"/>
       <c r="G16" s="3"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -1036,10 +1036,10 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="1">
@@ -1048,54 +1048,54 @@
       <c r="D2" s="3">
         <v>3.0401932235441099E-3</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="7">
         <f>AVERAGE(D2:D6)</f>
         <v>3.0638693805223236E-3</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
       <c r="D3" s="3">
         <v>3.0331384444736401E-3</v>
       </c>
-      <c r="E3" s="5"/>
+      <c r="E3" s="6"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
       <c r="D4" s="3">
         <v>3.1182764735492199E-3</v>
       </c>
-      <c r="E4" s="5"/>
+      <c r="E4" s="6"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="5"/>
-      <c r="B5" s="5"/>
+      <c r="A5" s="6"/>
+      <c r="B5" s="6"/>
       <c r="C5" s="1">
         <v>4</v>
       </c>
       <c r="D5" s="3"/>
-      <c r="E5" s="5"/>
+      <c r="E5" s="6"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5"/>
+      <c r="A6" s="6"/>
+      <c r="B6" s="6"/>
       <c r="C6" s="1">
         <v>5</v>
       </c>
       <c r="D6" s="3"/>
-      <c r="E6" s="5"/>
+      <c r="E6" s="6"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="5"/>
-      <c r="B7" s="5" t="s">
+      <c r="A7" s="6"/>
+      <c r="B7" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="1">
@@ -1104,11 +1104,11 @@
       <c r="D7" s="3">
         <v>2.67957260688739E-3</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="7">
         <f>AVERAGE(D7:D11)</f>
         <v>2.7172660575796701E-3</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="4" t="s">
         <v>12</v>
       </c>
       <c r="H7">
@@ -1116,16 +1116,16 @@
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5"/>
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
       <c r="C8" s="1">
         <v>2</v>
       </c>
       <c r="D8" s="3">
         <v>2.7552147060860401E-3</v>
       </c>
-      <c r="E8" s="5"/>
-      <c r="G8" s="7" t="s">
+      <c r="E8" s="6"/>
+      <c r="G8" s="4" t="s">
         <v>13</v>
       </c>
       <c r="H8">
@@ -1133,42 +1133,42 @@
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
       <c r="C9" s="1">
         <v>3</v>
       </c>
       <c r="D9" s="3">
         <v>2.62843134317815E-3</v>
       </c>
-      <c r="E9" s="5"/>
-      <c r="G9" s="7"/>
+      <c r="E9" s="6"/>
+      <c r="G9" s="4"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
       <c r="C10" s="1">
         <v>4</v>
       </c>
       <c r="D10" s="3">
         <v>2.8058455741671001E-3</v>
       </c>
-      <c r="E10" s="5"/>
+      <c r="E10" s="6"/>
       <c r="G10" s="3"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
+      <c r="A11" s="6"/>
+      <c r="B11" s="6"/>
       <c r="C11" s="1">
         <v>5</v>
       </c>
       <c r="D11" s="3"/>
-      <c r="E11" s="5"/>
+      <c r="E11" s="6"/>
       <c r="G11" s="3"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5" t="s">
+      <c r="A12" s="6"/>
+      <c r="B12" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C12" s="1">
@@ -1177,72 +1177,68 @@
       <c r="D12" s="3">
         <v>2.4363730991794601E-3</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="7">
         <f>AVERAGE(D12:D16)</f>
         <v>2.4650105258814206E-3</v>
       </c>
-      <c r="G12" s="3">
-        <v>2.5224244786699302E-3</v>
-      </c>
+      <c r="G12" s="3"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
       <c r="C13" s="1">
         <v>2</v>
       </c>
       <c r="D13" s="3">
         <v>2.4762825423162902E-3</v>
       </c>
-      <c r="E13" s="5"/>
-      <c r="G13" s="3">
-        <v>2.5922042207888402E-3</v>
-      </c>
+      <c r="E13" s="6"/>
+      <c r="G13" s="3"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
       <c r="C14" s="1">
         <v>3</v>
       </c>
       <c r="D14" s="3">
         <v>2.2977682884525799E-3</v>
       </c>
-      <c r="E14" s="5"/>
+      <c r="E14" s="6"/>
       <c r="G14" s="3"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
       <c r="C15" s="1">
         <v>4</v>
       </c>
       <c r="D15" s="3">
         <v>2.5224244786699302E-3</v>
       </c>
-      <c r="E15" s="5"/>
+      <c r="E15" s="6"/>
       <c r="G15" s="3"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
       <c r="C16" s="1">
         <v>5</v>
       </c>
       <c r="D16" s="3">
         <v>2.5922042207888402E-3</v>
       </c>
-      <c r="E16" s="5"/>
+      <c r="E16" s="6"/>
       <c r="G16" s="3"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/_resultados/_resultados.xlsx
+++ b/_resultados/_resultados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ravar\Documents\GitHub\recsys-fair-federation-flower\_resultados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ABD6506-4088-463C-A120-7069B41A585D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{378C6316-7F09-4DFD-B2C0-2B14652CB225}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Activity" sheetId="12" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="12">
   <si>
     <t>Estratégia</t>
   </si>
@@ -132,12 +132,6 @@
   </si>
   <si>
     <t>Gender</t>
-  </si>
-  <si>
-    <t>0.0028247020506802223</t>
-  </si>
-  <si>
-    <t>0.002841222981759123</t>
   </si>
 </sst>
 </file>
@@ -238,14 +232,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -560,10 +553,10 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="1">
@@ -572,54 +565,54 @@
       <c r="D2" s="3">
         <v>1.81177350386232E-3</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="6">
         <f>AVERAGE(D2:D6)</f>
         <v>1.8485946957060599E-3</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6"/>
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
       <c r="D3" s="3">
         <v>1.8148006812720001E-3</v>
       </c>
-      <c r="E3" s="6"/>
+      <c r="E3" s="5"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
       <c r="D4" s="3">
         <v>1.9192099019838601E-3</v>
       </c>
-      <c r="E4" s="6"/>
+      <c r="E4" s="5"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6"/>
+      <c r="A5" s="5"/>
+      <c r="B5" s="5"/>
       <c r="C5" s="1">
         <v>4</v>
       </c>
       <c r="D5" s="3"/>
-      <c r="E5" s="6"/>
+      <c r="E5" s="5"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6"/>
+      <c r="A6" s="5"/>
+      <c r="B6" s="5"/>
       <c r="C6" s="1">
         <v>5</v>
       </c>
       <c r="D6" s="3"/>
-      <c r="E6" s="6"/>
+      <c r="E6" s="5"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6" t="s">
+      <c r="A7" s="5"/>
+      <c r="B7" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="1">
@@ -628,56 +621,56 @@
       <c r="D7" s="3">
         <v>1.22745404238443E-3</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="6">
         <f>AVERAGE(D7:D11)</f>
         <v>1.2352179388571624E-3</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
+      <c r="A8" s="5"/>
+      <c r="B8" s="5"/>
       <c r="C8" s="1">
         <v>2</v>
       </c>
       <c r="D8" s="3">
         <v>1.2128989821674999E-3</v>
       </c>
-      <c r="E8" s="6"/>
+      <c r="E8" s="5"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
       <c r="C9" s="1">
         <v>3</v>
       </c>
       <c r="D9" s="3">
         <v>1.2072314178239499E-3</v>
       </c>
-      <c r="E9" s="6"/>
+      <c r="E9" s="5"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
       <c r="C10" s="1">
         <v>4</v>
       </c>
       <c r="D10" s="3">
         <v>1.2932873130527701E-3</v>
       </c>
-      <c r="E10" s="6"/>
+      <c r="E10" s="5"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
       <c r="C11" s="1">
         <v>5</v>
       </c>
       <c r="D11" s="3"/>
-      <c r="E11" s="6"/>
+      <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6" t="s">
+      <c r="A12" s="5"/>
+      <c r="B12" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C12" s="1">
@@ -686,63 +679,63 @@
       <c r="D12" s="3">
         <v>7.2837430705559596E-4</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="6">
         <f>AVERAGE(D12:D16)</f>
         <v>8.179226084032836E-4</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
+      <c r="A13" s="5"/>
+      <c r="B13" s="5"/>
       <c r="C13" s="1">
         <v>2</v>
       </c>
       <c r="D13" s="3">
         <v>8.4607791428294903E-4</v>
       </c>
-      <c r="E13" s="6"/>
+      <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
       <c r="C14" s="1">
         <v>3</v>
       </c>
       <c r="D14" s="3">
         <v>8.6882802551990898E-4</v>
       </c>
-      <c r="E14" s="6"/>
+      <c r="E14" s="5"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
+      <c r="A15" s="5"/>
+      <c r="B15" s="5"/>
       <c r="C15" s="1">
         <v>4</v>
       </c>
       <c r="D15" s="3">
         <v>8.6728801473186397E-4</v>
       </c>
-      <c r="E15" s="6"/>
+      <c r="E15" s="5"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
+      <c r="A16" s="5"/>
+      <c r="B16" s="5"/>
       <c r="C16" s="1">
         <v>5</v>
       </c>
       <c r="D16" s="3">
         <v>7.7904478042610005E-4</v>
       </c>
-      <c r="E16" s="6"/>
+      <c r="E16" s="5"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -762,15 +755,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E822B54-E6B9-4F6D-BD17-4242A3C7CFDB}">
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="22.77734375" customWidth="1"/>
-    <col min="7" max="7" width="21" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -787,11 +779,11 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="1">
@@ -800,54 +792,54 @@
       <c r="D2" s="3">
         <v>8.8432581244842993E-3</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="6">
         <f>AVERAGE(D2:D6)</f>
         <v>8.9594988217164395E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6"/>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
       <c r="D3" s="3">
         <v>8.9353771851844298E-3</v>
       </c>
-      <c r="E3" s="6"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
+      <c r="E3" s="5"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
       <c r="D4" s="3">
         <v>9.0998611554805892E-3</v>
       </c>
-      <c r="E4" s="6"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6"/>
+      <c r="E4" s="5"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="5"/>
+      <c r="B5" s="5"/>
       <c r="C5" s="1">
         <v>4</v>
       </c>
       <c r="D5" s="3"/>
-      <c r="E5" s="6"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6"/>
+      <c r="E5" s="5"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="5"/>
+      <c r="B6" s="5"/>
       <c r="C6" s="1">
         <v>5</v>
       </c>
       <c r="D6" s="3"/>
-      <c r="E6" s="6"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6" t="s">
+      <c r="E6" s="5"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="5"/>
+      <c r="B7" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="1">
@@ -856,63 +848,58 @@
       <c r="D7" s="3">
         <v>8.4438215453025E-3</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="6">
         <f>AVERAGE(D7:D11)</f>
-        <v>8.5661684923472904E-3</v>
-      </c>
-      <c r="G7" s="4"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
+        <v>8.3887123899537321E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="5"/>
+      <c r="B8" s="5"/>
       <c r="C8" s="1">
         <v>2</v>
       </c>
       <c r="D8" s="3">
-        <v>8.9993707838031105E-3</v>
-      </c>
-      <c r="E8" s="6"/>
-      <c r="G8" s="4"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
+        <v>8.1120902718353205E-3</v>
+      </c>
+      <c r="E8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
       <c r="C9" s="1">
         <v>3</v>
       </c>
       <c r="D9" s="3">
         <v>8.5229916662684403E-3</v>
       </c>
-      <c r="E9" s="6"/>
-      <c r="G9" s="4"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
+      <c r="E9" s="5"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
       <c r="C10" s="1">
         <v>4</v>
       </c>
       <c r="D10" s="3">
         <v>8.6347088477538494E-3</v>
       </c>
-      <c r="E10" s="6"/>
-      <c r="G10" s="4"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
+      <c r="E10" s="5"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
       <c r="C11" s="1">
         <v>5</v>
       </c>
       <c r="D11" s="3">
         <v>8.2299496186085501E-3</v>
       </c>
-      <c r="E11" s="6"/>
-      <c r="G11" s="4"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6" t="s">
+      <c r="E11" s="5"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="5"/>
+      <c r="B12" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C12" s="1">
@@ -921,76 +908,63 @@
       <c r="D12" s="3">
         <v>6.2969138289247001E-3</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="6">
         <f>AVERAGE(D12:D16)</f>
-        <v>6.4232932671029145E-3</v>
-      </c>
-      <c r="G12" s="3">
-        <v>6.9679785064951797E-3</v>
-      </c>
-      <c r="H12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
+        <v>6.377811555868626E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="5"/>
+      <c r="B13" s="5"/>
       <c r="C13" s="1">
         <v>2</v>
       </c>
       <c r="D13" s="3">
         <v>6.4076776396648598E-3</v>
       </c>
-      <c r="E13" s="6"/>
-      <c r="G13" s="3">
-        <v>6.9169172748136899E-3</v>
-      </c>
-      <c r="H13">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
+      <c r="E13" s="5"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
       <c r="C14" s="1">
         <v>3</v>
       </c>
       <c r="D14" s="3">
         <v>6.2667263273711001E-3</v>
       </c>
-      <c r="E14" s="6"/>
-      <c r="G14" s="3"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
+      <c r="E14" s="5"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="5"/>
+      <c r="B15" s="5"/>
       <c r="C15" s="1">
         <v>4</v>
       </c>
       <c r="D15" s="3">
         <v>6.7218552724509998E-3</v>
       </c>
-      <c r="E15" s="6"/>
-      <c r="G15" s="3"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
+      <c r="E15" s="5"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="5"/>
+      <c r="B16" s="5"/>
       <c r="C16" s="1">
         <v>5</v>
       </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="6"/>
-      <c r="G16" s="3"/>
+      <c r="D16" s="3">
+        <v>6.1958847109314704E-3</v>
+      </c>
+      <c r="E16" s="5"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -1010,15 +984,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DD90B87-E05B-497D-A050-F1EDBF1A792F}">
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="22.77734375" customWidth="1"/>
-    <col min="7" max="7" width="22.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1035,11 +1008,11 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="1">
@@ -1048,54 +1021,54 @@
       <c r="D2" s="3">
         <v>3.0401932235441099E-3</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="6">
         <f>AVERAGE(D2:D6)</f>
         <v>3.0638693805223236E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6"/>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
       <c r="D3" s="3">
         <v>3.0331384444736401E-3</v>
       </c>
-      <c r="E3" s="6"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
+      <c r="E3" s="5"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
       <c r="D4" s="3">
         <v>3.1182764735492199E-3</v>
       </c>
-      <c r="E4" s="6"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6"/>
+      <c r="E4" s="5"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="5"/>
+      <c r="B5" s="5"/>
       <c r="C5" s="1">
         <v>4</v>
       </c>
       <c r="D5" s="3"/>
-      <c r="E5" s="6"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6"/>
+      <c r="E5" s="5"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="5"/>
+      <c r="B6" s="5"/>
       <c r="C6" s="1">
         <v>5</v>
       </c>
       <c r="D6" s="3"/>
-      <c r="E6" s="6"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6" t="s">
+      <c r="E6" s="5"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="5"/>
+      <c r="B7" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="1">
@@ -1104,71 +1077,58 @@
       <c r="D7" s="3">
         <v>2.67957260688739E-3</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="6">
         <f>AVERAGE(D7:D11)</f>
-        <v>2.7172660575796701E-3</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="H7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
+        <v>2.7813115839159745E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="5"/>
+      <c r="B8" s="5"/>
       <c r="C8" s="1">
         <v>2</v>
       </c>
       <c r="D8" s="3">
         <v>2.7552147060860401E-3</v>
       </c>
-      <c r="E8" s="6"/>
-      <c r="G8" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
+      <c r="E8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
       <c r="C9" s="1">
         <v>3</v>
       </c>
       <c r="D9" s="3">
-        <v>2.62843134317815E-3</v>
-      </c>
-      <c r="E9" s="6"/>
-      <c r="G9" s="4"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
+        <v>2.8412229817591202E-3</v>
+      </c>
+      <c r="E9" s="5"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
       <c r="C10" s="1">
         <v>4</v>
       </c>
       <c r="D10" s="3">
         <v>2.8058455741671001E-3</v>
       </c>
-      <c r="E10" s="6"/>
-      <c r="G10" s="3"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
+      <c r="E10" s="5"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
       <c r="C11" s="1">
         <v>5</v>
       </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="6"/>
-      <c r="G11" s="3"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6" t="s">
+      <c r="D11" s="3">
+        <v>2.8247020506802201E-3</v>
+      </c>
+      <c r="E11" s="5"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="5"/>
+      <c r="B12" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C12" s="1">
@@ -1177,68 +1137,63 @@
       <c r="D12" s="3">
         <v>2.4363730991794601E-3</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="6">
         <f>AVERAGE(D12:D16)</f>
         <v>2.4650105258814206E-3</v>
       </c>
-      <c r="G12" s="3"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="5"/>
+      <c r="B13" s="5"/>
       <c r="C13" s="1">
         <v>2</v>
       </c>
       <c r="D13" s="3">
         <v>2.4762825423162902E-3</v>
       </c>
-      <c r="E13" s="6"/>
-      <c r="G13" s="3"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
+      <c r="E13" s="5"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
       <c r="C14" s="1">
         <v>3</v>
       </c>
       <c r="D14" s="3">
         <v>2.2977682884525799E-3</v>
       </c>
-      <c r="E14" s="6"/>
-      <c r="G14" s="3"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
+      <c r="E14" s="5"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="5"/>
+      <c r="B15" s="5"/>
       <c r="C15" s="1">
         <v>4</v>
       </c>
       <c r="D15" s="3">
         <v>2.5224244786699302E-3</v>
       </c>
-      <c r="E15" s="6"/>
-      <c r="G15" s="3"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
+      <c r="E15" s="5"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="5"/>
+      <c r="B16" s="5"/>
       <c r="C16" s="1">
         <v>5</v>
       </c>
       <c r="D16" s="3">
         <v>2.5922042207888402E-3</v>
       </c>
-      <c r="E16" s="6"/>
-      <c r="G16" s="3"/>
+      <c r="E16" s="5"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/_resultados/_resultados.xlsx
+++ b/_resultados/_resultados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ravar\Documents\GitHub\recsys-fair-federation-flower\_resultados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{378C6316-7F09-4DFD-B2C0-2B14652CB225}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB612817-3677-44F8-AB41-142E3EE4833E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="1104" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Activity" sheetId="12" r:id="rId1"/>
@@ -567,7 +567,7 @@
       </c>
       <c r="E2" s="6">
         <f>AVERAGE(D2:D6)</f>
-        <v>1.8485946957060599E-3</v>
+        <v>1.8086049537491718E-3</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -598,7 +598,9 @@
       <c r="C5" s="1">
         <v>4</v>
       </c>
-      <c r="D5" s="3"/>
+      <c r="D5" s="3">
+        <v>1.7683693332491801E-3</v>
+      </c>
       <c r="E5" s="5"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -607,7 +609,9 @@
       <c r="C6" s="1">
         <v>5</v>
       </c>
-      <c r="D6" s="3"/>
+      <c r="D6" s="3">
+        <v>1.7288713483785E-3</v>
+      </c>
       <c r="E6" s="5"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -623,7 +627,7 @@
       </c>
       <c r="E7" s="6">
         <f>AVERAGE(D7:D11)</f>
-        <v>1.2352179388571624E-3</v>
+        <v>1.22628181690779E-3</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -665,7 +669,9 @@
       <c r="C11" s="1">
         <v>5</v>
       </c>
-      <c r="D11" s="3"/>
+      <c r="D11" s="3">
+        <v>1.1905373291103E-3</v>
+      </c>
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -794,7 +800,7 @@
       </c>
       <c r="E2" s="6">
         <f>AVERAGE(D2:D6)</f>
-        <v>8.9594988217164395E-3</v>
+        <v>8.8390938647225532E-3</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -825,7 +831,9 @@
       <c r="C5" s="1">
         <v>4</v>
       </c>
-      <c r="D5" s="3"/>
+      <c r="D5" s="3">
+        <v>8.7097429395581304E-3</v>
+      </c>
       <c r="E5" s="5"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -834,7 +842,9 @@
       <c r="C6" s="1">
         <v>5</v>
       </c>
-      <c r="D6" s="3"/>
+      <c r="D6" s="3">
+        <v>8.6072299189053209E-3</v>
+      </c>
       <c r="E6" s="5"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -1023,7 +1033,7 @@
       </c>
       <c r="E2" s="6">
         <f>AVERAGE(D2:D6)</f>
-        <v>3.0638693805223236E-3</v>
+        <v>3.05091106736371E-3</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -1054,7 +1064,9 @@
       <c r="C5" s="1">
         <v>4</v>
       </c>
-      <c r="D5" s="3"/>
+      <c r="D5" s="3">
+        <v>3.0575230874511799E-3</v>
+      </c>
       <c r="E5" s="5"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -1063,7 +1075,9 @@
       <c r="C6" s="1">
         <v>5</v>
       </c>
-      <c r="D6" s="3"/>
+      <c r="D6" s="3">
+        <v>3.0054241078004001E-3</v>
+      </c>
       <c r="E6" s="5"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -1139,7 +1153,7 @@
       </c>
       <c r="E12" s="6">
         <f>AVERAGE(D12:D16)</f>
-        <v>2.4650105258814206E-3</v>
+        <v>2.3687334646183382E-3</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -1182,7 +1196,7 @@
         <v>5</v>
       </c>
       <c r="D16" s="3">
-        <v>2.5922042207888402E-3</v>
+        <v>2.1108189144734301E-3</v>
       </c>
       <c r="E16" s="5"/>
     </row>

--- a/_resultados/_resultados.xlsx
+++ b/_resultados/_resultados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ravar\Documents\GitHub\recsys-fair-federation-flower\_resultados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB612817-3677-44F8-AB41-142E3EE4833E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34246997-44CE-4F09-9107-33E03E68F470}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="1104" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Activity" sheetId="12" r:id="rId1"/>

--- a/_resultados/_resultados.xlsx
+++ b/_resultados/_resultados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ravar\Documents\GitHub\recsys-fair-federation-flower\_resultados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34246997-44CE-4F09-9107-33E03E68F470}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1FC1E1F-0DEA-4574-BF2D-370A94ADF7E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Activity" sheetId="12" r:id="rId1"/>
@@ -567,7 +567,7 @@
       </c>
       <c r="E2" s="6">
         <f>AVERAGE(D2:D6)</f>
-        <v>1.8086049537491718E-3</v>
+        <v>1.8257771737235358E-3</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -610,7 +610,7 @@
         <v>5</v>
       </c>
       <c r="D6" s="3">
-        <v>1.7288713483785E-3</v>
+        <v>1.81473244825032E-3</v>
       </c>
       <c r="E6" s="5"/>
     </row>

--- a/_resultados/_resultados.xlsx
+++ b/_resultados/_resultados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ravar\Documents\GitHub\recsys-fair-federation-flower\_resultados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1FC1E1F-0DEA-4574-BF2D-370A94ADF7E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87AFCAD8-8737-4EA7-BD97-87999F89B356}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Activity" sheetId="12" r:id="rId1"/>
@@ -232,7 +232,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -247,6 +247,9 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -528,11 +531,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70966A2D-672A-451B-A3A3-B783FCE2984F}">
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="22.77734375" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" style="7"/>
+    <col min="8" max="8" width="22.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.35">
@@ -627,7 +632,7 @@
       </c>
       <c r="E7" s="6">
         <f>AVERAGE(D7:D11)</f>
-        <v>1.22628181690779E-3</v>
+        <v>1.2341300465112119E-3</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -670,7 +675,7 @@
         <v>5</v>
       </c>
       <c r="D11" s="3">
-        <v>1.1905373291103E-3</v>
+        <v>1.22977847712741E-3</v>
       </c>
       <c r="E11" s="5"/>
     </row>
@@ -761,11 +766,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E822B54-E6B9-4F6D-BD17-4242A3C7CFDB}">
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="22.77734375" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.35">
@@ -860,7 +866,7 @@
       </c>
       <c r="E7" s="6">
         <f>AVERAGE(D7:D11)</f>
-        <v>8.3887123899537321E-3</v>
+        <v>8.4770465602232586E-3</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -870,7 +876,7 @@
         <v>2</v>
       </c>
       <c r="D8" s="3">
-        <v>8.1120902718353205E-3</v>
+        <v>8.5537611231829604E-3</v>
       </c>
       <c r="E8" s="5"/>
     </row>
@@ -994,11 +1000,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DD90B87-E05B-497D-A050-F1EDBF1A792F}">
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="22.77734375" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" style="7"/>
+    <col min="8" max="8" width="21" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.35">
@@ -1089,11 +1097,11 @@
         <v>1</v>
       </c>
       <c r="D7" s="3">
-        <v>2.67957260688739E-3</v>
+        <v>2.76881779349106E-3</v>
       </c>
       <c r="E7" s="6">
         <f>AVERAGE(D7:D11)</f>
-        <v>2.7813115839159745E-3</v>
+        <v>2.7991606212367081E-3</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">

--- a/_resultados/_resultados.xlsx
+++ b/_resultados/_resultados.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ravar\Documents\GitHub\recsys-fair-federation-flower\_resultados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87AFCAD8-8737-4EA7-BD97-87999F89B356}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89CC8209-EC64-4103-BCB4-BF500B468ABC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Activity" sheetId="12" r:id="rId1"/>
     <sheet name="Age" sheetId="13" r:id="rId2"/>
-    <sheet name="Gender" sheetId="14" r:id="rId3"/>
+    <sheet name="Gender" sheetId="15" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -179,7 +179,7 @@
       <family val="3"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -201,6 +201,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -232,13 +244,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -248,9 +263,8 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -531,12 +545,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70966A2D-672A-451B-A3A3-B783FCE2984F}">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="22.77734375" customWidth="1"/>
-    <col min="7" max="7" width="8.88671875" style="7"/>
+    <col min="7" max="7" width="8.88671875" style="4"/>
     <col min="8" max="8" width="22.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -558,10 +572,10 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="1">
@@ -570,58 +584,58 @@
       <c r="D2" s="3">
         <v>1.81177350386232E-3</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="7">
         <f>AVERAGE(D2:D6)</f>
         <v>1.8257771737235358E-3</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
       <c r="D3" s="3">
         <v>1.8148006812720001E-3</v>
       </c>
-      <c r="E3" s="5"/>
+      <c r="E3" s="6"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="8">
         <v>1.9192099019838601E-3</v>
       </c>
-      <c r="E4" s="5"/>
+      <c r="E4" s="6"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="5"/>
-      <c r="B5" s="5"/>
+      <c r="A5" s="6"/>
+      <c r="B5" s="6"/>
       <c r="C5" s="1">
         <v>4</v>
       </c>
       <c r="D5" s="3">
         <v>1.7683693332491801E-3</v>
       </c>
-      <c r="E5" s="5"/>
+      <c r="E5" s="6"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5"/>
+      <c r="A6" s="6"/>
+      <c r="B6" s="6"/>
       <c r="C6" s="1">
         <v>5</v>
       </c>
       <c r="D6" s="3">
         <v>1.81473244825032E-3</v>
       </c>
-      <c r="E6" s="5"/>
+      <c r="E6" s="6"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="5"/>
-      <c r="B7" s="5" t="s">
+      <c r="A7" s="6"/>
+      <c r="B7" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="1">
@@ -630,134 +644,156 @@
       <c r="D7" s="3">
         <v>1.22745404238443E-3</v>
       </c>
-      <c r="E7" s="6">
-        <f>AVERAGE(D7:D11)</f>
-        <v>1.2341300465112119E-3</v>
+      <c r="E7" s="7">
+        <f>AVERAGE(D7:D13)</f>
+        <v>1.255405521012254E-3</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5"/>
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
       <c r="C8" s="1">
         <v>2</v>
       </c>
       <c r="D8" s="3">
         <v>1.2128989821674999E-3</v>
       </c>
-      <c r="E8" s="5"/>
+      <c r="E8" s="6"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
       <c r="C9" s="1">
         <v>3</v>
       </c>
       <c r="D9" s="3">
         <v>1.2072314178239499E-3</v>
       </c>
-      <c r="E9" s="5"/>
+      <c r="E9" s="6"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
       <c r="C10" s="1">
         <v>4</v>
       </c>
       <c r="D10" s="3">
         <v>1.2932873130527701E-3</v>
       </c>
-      <c r="E10" s="5"/>
+      <c r="E10" s="6"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
+      <c r="A11" s="6"/>
+      <c r="B11" s="6"/>
       <c r="C11" s="1">
         <v>5</v>
       </c>
       <c r="D11" s="3">
         <v>1.22977847712741E-3</v>
       </c>
-      <c r="E11" s="5"/>
+      <c r="E11" s="6"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5" t="s">
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="1">
+        <v>6</v>
+      </c>
+      <c r="D12" s="3">
+        <v>1.3025872216186299E-3</v>
+      </c>
+      <c r="E12" s="6"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="1">
+        <v>7</v>
+      </c>
+      <c r="D13" s="8">
+        <v>1.31460119291109E-3</v>
+      </c>
+      <c r="E13" s="6"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="6"/>
+      <c r="B14" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C14" s="1">
         <v>1</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D14" s="9">
         <v>7.2837430705559596E-4</v>
       </c>
-      <c r="E12" s="6">
-        <f>AVERAGE(D12:D16)</f>
+      <c r="E14" s="7">
+        <f>AVERAGE(D14:D18)</f>
         <v>8.179226084032836E-4</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="1">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="1">
         <v>2</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D15" s="3">
         <v>8.4607791428294903E-4</v>
       </c>
-      <c r="E13" s="5"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="1">
+      <c r="E15" s="6"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="1">
         <v>3</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D16" s="3">
         <v>8.6882802551990898E-4</v>
       </c>
-      <c r="E14" s="5"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="1">
+      <c r="E16" s="6"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="1">
         <v>4</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D17" s="3">
         <v>8.6728801473186397E-4</v>
       </c>
-      <c r="E15" s="5"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="1">
+      <c r="E17" s="6"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="6"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="1">
         <v>5</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D18" s="3">
         <v>7.7904478042610005E-4</v>
       </c>
-      <c r="E16" s="5"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
+      <c r="E18" s="6"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A2:A16"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A2:A18"/>
     <mergeCell ref="B2:B6"/>
     <mergeCell ref="E2:E6"/>
-    <mergeCell ref="B7:B11"/>
-    <mergeCell ref="E7:E11"/>
-    <mergeCell ref="B12:B16"/>
-    <mergeCell ref="E12:E16"/>
+    <mergeCell ref="B7:B13"/>
+    <mergeCell ref="E7:E13"/>
+    <mergeCell ref="B14:B18"/>
+    <mergeCell ref="E14:E18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -766,12 +802,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E822B54-E6B9-4F6D-BD17-4242A3C7CFDB}">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="22.77734375" customWidth="1"/>
-    <col min="7" max="7" width="8.88671875" style="7"/>
+    <col min="7" max="7" width="8.88671875" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.35">
@@ -792,10 +828,10 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="1">
@@ -804,58 +840,58 @@
       <c r="D2" s="3">
         <v>8.8432581244842993E-3</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="7">
         <f>AVERAGE(D2:D6)</f>
         <v>8.8390938647225532E-3</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
       <c r="D3" s="3">
         <v>8.9353771851844298E-3</v>
       </c>
-      <c r="E3" s="5"/>
+      <c r="E3" s="6"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="8">
         <v>9.0998611554805892E-3</v>
       </c>
-      <c r="E4" s="5"/>
+      <c r="E4" s="6"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="5"/>
-      <c r="B5" s="5"/>
+      <c r="A5" s="6"/>
+      <c r="B5" s="6"/>
       <c r="C5" s="1">
         <v>4</v>
       </c>
       <c r="D5" s="3">
         <v>8.7097429395581304E-3</v>
       </c>
-      <c r="E5" s="5"/>
+      <c r="E5" s="6"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5"/>
+      <c r="A6" s="6"/>
+      <c r="B6" s="6"/>
       <c r="C6" s="1">
         <v>5</v>
       </c>
       <c r="D6" s="3">
         <v>8.6072299189053209E-3</v>
       </c>
-      <c r="E6" s="5"/>
+      <c r="E6" s="6"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="5"/>
-      <c r="B7" s="5" t="s">
+      <c r="A7" s="6"/>
+      <c r="B7" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="1">
@@ -864,134 +900,148 @@
       <c r="D7" s="3">
         <v>8.4438215453025E-3</v>
       </c>
-      <c r="E7" s="6">
-        <f>AVERAGE(D7:D11)</f>
+      <c r="E7" s="7">
+        <f>AVERAGE(D7:D13)</f>
         <v>8.4770465602232586E-3</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5"/>
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
       <c r="C8" s="1">
         <v>2</v>
       </c>
       <c r="D8" s="3">
         <v>8.5537611231829604E-3</v>
       </c>
-      <c r="E8" s="5"/>
+      <c r="E8" s="6"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
       <c r="C9" s="1">
         <v>3</v>
       </c>
       <c r="D9" s="3">
         <v>8.5229916662684403E-3</v>
       </c>
-      <c r="E9" s="5"/>
+      <c r="E9" s="6"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
       <c r="C10" s="1">
         <v>4</v>
       </c>
       <c r="D10" s="3">
         <v>8.6347088477538494E-3</v>
       </c>
-      <c r="E10" s="5"/>
+      <c r="E10" s="6"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
+      <c r="A11" s="6"/>
+      <c r="B11" s="6"/>
       <c r="C11" s="1">
         <v>5</v>
       </c>
       <c r="D11" s="3">
         <v>8.2299496186085501E-3</v>
       </c>
-      <c r="E11" s="5"/>
+      <c r="E11" s="6"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5" t="s">
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="6"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="6"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="6"/>
+      <c r="B14" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C14" s="1">
         <v>1</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D14" s="3">
         <v>6.2969138289247001E-3</v>
       </c>
-      <c r="E12" s="6">
-        <f>AVERAGE(D12:D16)</f>
-        <v>6.377811555868626E-3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="1">
+      <c r="E14" s="7">
+        <f>AVERAGE(D14:D18)</f>
+        <v>6.2922385583522407E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="1">
         <v>2</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D15" s="3">
         <v>6.4076776396648598E-3</v>
       </c>
-      <c r="E13" s="5"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="1">
+      <c r="E15" s="6"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="1">
         <v>3</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D16" s="3">
         <v>6.2667263273711001E-3</v>
       </c>
-      <c r="E14" s="5"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="1">
+      <c r="E16" s="6"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="1">
         <v>4</v>
       </c>
-      <c r="D15" s="3">
-        <v>6.7218552724509998E-3</v>
-      </c>
-      <c r="E15" s="5"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="1">
+      <c r="D17" s="3">
+        <v>6.2939902848690703E-3</v>
+      </c>
+      <c r="E17" s="6"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="6"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="1">
         <v>5</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D18" s="9">
         <v>6.1958847109314704E-3</v>
       </c>
-      <c r="E16" s="5"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
+      <c r="E18" s="6"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A2:A16"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A2:A18"/>
     <mergeCell ref="B2:B6"/>
     <mergeCell ref="E2:E6"/>
-    <mergeCell ref="B7:B11"/>
-    <mergeCell ref="E7:E11"/>
-    <mergeCell ref="B12:B16"/>
-    <mergeCell ref="E12:E16"/>
+    <mergeCell ref="B7:B13"/>
+    <mergeCell ref="E7:E13"/>
+    <mergeCell ref="B14:B18"/>
+    <mergeCell ref="E14:E18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -999,14 +1049,13 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DD90B87-E05B-497D-A050-F1EDBF1A792F}">
-  <dimension ref="A1:G18"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0018FF42-DB9B-49FF-AD34-CF6CC8AED773}">
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="22.77734375" customWidth="1"/>
-    <col min="7" max="7" width="8.88671875" style="7"/>
-    <col min="8" max="8" width="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.6" x14ac:dyDescent="0.35">
@@ -1027,10 +1076,10 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="1">
@@ -1039,194 +1088,227 @@
       <c r="D2" s="3">
         <v>3.0401932235441099E-3</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="7">
         <f>AVERAGE(D2:D6)</f>
         <v>3.05091106736371E-3</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
       <c r="D3" s="3">
         <v>3.0331384444736401E-3</v>
       </c>
-      <c r="E3" s="5"/>
+      <c r="E3" s="6"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
       <c r="D4" s="3">
         <v>3.1182764735492199E-3</v>
       </c>
-      <c r="E4" s="5"/>
+      <c r="E4" s="6"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="5"/>
-      <c r="B5" s="5"/>
+      <c r="A5" s="6"/>
+      <c r="B5" s="6"/>
       <c r="C5" s="1">
         <v>4</v>
       </c>
       <c r="D5" s="3">
         <v>3.0575230874511799E-3</v>
       </c>
-      <c r="E5" s="5"/>
+      <c r="E5" s="6"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5"/>
+      <c r="A6" s="6"/>
+      <c r="B6" s="6"/>
       <c r="C6" s="1">
         <v>5</v>
       </c>
       <c r="D6" s="3">
         <v>3.0054241078004001E-3</v>
       </c>
-      <c r="E6" s="5"/>
+      <c r="E6" s="6"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="5"/>
-      <c r="B7" s="5" t="s">
+      <c r="A7" s="6"/>
+      <c r="B7" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="1">
         <v>1</v>
       </c>
       <c r="D7" s="3">
-        <v>2.76881779349106E-3</v>
-      </c>
-      <c r="E7" s="6">
-        <f>AVERAGE(D7:D11)</f>
-        <v>2.7991606212367081E-3</v>
+        <v>2.67957260688739E-3</v>
+      </c>
+      <c r="E7" s="7">
+        <f>AVERAGE(D7:D14)</f>
+        <v>2.7855731457791487E-3</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5"/>
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
       <c r="C8" s="1">
         <v>2</v>
       </c>
       <c r="D8" s="3">
         <v>2.7552147060860401E-3</v>
       </c>
-      <c r="E8" s="5"/>
+      <c r="E8" s="6"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
       <c r="C9" s="1">
         <v>3</v>
       </c>
       <c r="D9" s="3">
         <v>2.8412229817591202E-3</v>
       </c>
-      <c r="E9" s="5"/>
+      <c r="E9" s="6"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
       <c r="C10" s="1">
         <v>4</v>
       </c>
       <c r="D10" s="3">
         <v>2.8058455741671001E-3</v>
       </c>
-      <c r="E10" s="5"/>
+      <c r="E10" s="6"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
+      <c r="A11" s="6"/>
+      <c r="B11" s="6"/>
       <c r="C11" s="1">
         <v>5</v>
       </c>
       <c r="D11" s="3">
         <v>2.8247020506802201E-3</v>
       </c>
-      <c r="E11" s="5"/>
+      <c r="E11" s="6"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5" t="s">
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="1">
+        <v>6</v>
+      </c>
+      <c r="D12" s="3">
+        <v>2.76881779349106E-3</v>
+      </c>
+      <c r="E12" s="6"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="1">
+        <v>7</v>
+      </c>
+      <c r="D13" s="3">
+        <v>2.6488434196267801E-3</v>
+      </c>
+      <c r="E13" s="6"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="1">
         <v>8</v>
       </c>
-      <c r="C12" s="1">
+      <c r="D14" s="3">
+        <v>2.9603660335354798E-3</v>
+      </c>
+      <c r="E14" s="6"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="6"/>
+      <c r="B15" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="1">
         <v>1</v>
       </c>
-      <c r="D12" s="3">
-        <v>2.4363730991794601E-3</v>
-      </c>
-      <c r="E12" s="6">
-        <f>AVERAGE(D12:D16)</f>
-        <v>2.3687334646183382E-3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="1">
+      <c r="D15" s="9">
+        <v>2.0622498441260802E-3</v>
+      </c>
+      <c r="E15" s="7">
+        <f>AVERAGE(D15:D19)</f>
+        <v>2.2569335674385918E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="1">
         <v>2</v>
       </c>
-      <c r="D13" s="3">
-        <v>2.4762825423162902E-3</v>
-      </c>
-      <c r="E13" s="5"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="1">
+      <c r="D16" s="3">
+        <v>2.3794685929811499E-3</v>
+      </c>
+      <c r="E16" s="6"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="1">
         <v>3</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D17" s="3">
         <v>2.2977682884525799E-3</v>
       </c>
-      <c r="E14" s="5"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="1">
+      <c r="E17" s="6"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="6"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="1">
         <v>4</v>
       </c>
-      <c r="D15" s="3">
-        <v>2.5224244786699302E-3</v>
-      </c>
-      <c r="E15" s="5"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="1">
+      <c r="D18" s="3">
+        <v>2.4343621971597198E-3</v>
+      </c>
+      <c r="E18" s="6"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="6"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="1">
         <v>5</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D19" s="3">
         <v>2.1108189144734301E-3</v>
       </c>
-      <c r="E16" s="5"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
+      <c r="E19" s="6"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A2:A16"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A2:A19"/>
     <mergeCell ref="B2:B6"/>
     <mergeCell ref="E2:E6"/>
-    <mergeCell ref="B7:B11"/>
-    <mergeCell ref="E7:E11"/>
-    <mergeCell ref="B12:B16"/>
-    <mergeCell ref="E12:E16"/>
+    <mergeCell ref="B7:B14"/>
+    <mergeCell ref="E7:E14"/>
+    <mergeCell ref="B15:B19"/>
+    <mergeCell ref="E15:E19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/_resultados/_resultados.xlsx
+++ b/_resultados/_resultados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ravar\Documents\GitHub\recsys-fair-federation-flower\_resultados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89CC8209-EC64-4103-BCB4-BF500B468ABC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C2A9E30-9EEB-49CD-9F7F-E364A04FF40C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Activity" sheetId="12" r:id="rId1"/>
@@ -254,6 +254,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -263,8 +265,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -572,10 +572,10 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="8" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="1">
@@ -584,58 +584,58 @@
       <c r="D2" s="3">
         <v>1.81177350386232E-3</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="9">
         <f>AVERAGE(D2:D6)</f>
         <v>1.8257771737235358E-3</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6"/>
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
       <c r="D3" s="3">
         <v>1.8148006812720001E-3</v>
       </c>
-      <c r="E3" s="6"/>
+      <c r="E3" s="8"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="5">
         <v>1.9192099019838601E-3</v>
       </c>
-      <c r="E4" s="6"/>
+      <c r="E4" s="8"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6"/>
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
       <c r="C5" s="1">
         <v>4</v>
       </c>
       <c r="D5" s="3">
         <v>1.7683693332491801E-3</v>
       </c>
-      <c r="E5" s="6"/>
+      <c r="E5" s="8"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6"/>
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
       <c r="C6" s="1">
         <v>5</v>
       </c>
       <c r="D6" s="3">
         <v>1.81473244825032E-3</v>
       </c>
-      <c r="E6" s="6"/>
+      <c r="E6" s="8"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6" t="s">
+      <c r="A7" s="8"/>
+      <c r="B7" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="1">
@@ -644,145 +644,145 @@
       <c r="D7" s="3">
         <v>1.22745404238443E-3</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="9">
         <f>AVERAGE(D7:D13)</f>
         <v>1.255405521012254E-3</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
       <c r="C8" s="1">
         <v>2</v>
       </c>
       <c r="D8" s="3">
         <v>1.2128989821674999E-3</v>
       </c>
-      <c r="E8" s="6"/>
+      <c r="E8" s="8"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
       <c r="C9" s="1">
         <v>3</v>
       </c>
       <c r="D9" s="3">
         <v>1.2072314178239499E-3</v>
       </c>
-      <c r="E9" s="6"/>
+      <c r="E9" s="8"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
       <c r="C10" s="1">
         <v>4</v>
       </c>
       <c r="D10" s="3">
         <v>1.2932873130527701E-3</v>
       </c>
-      <c r="E10" s="6"/>
+      <c r="E10" s="8"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
       <c r="C11" s="1">
         <v>5</v>
       </c>
       <c r="D11" s="3">
         <v>1.22977847712741E-3</v>
       </c>
-      <c r="E11" s="6"/>
+      <c r="E11" s="8"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
       <c r="C12" s="1">
         <v>6</v>
       </c>
       <c r="D12" s="3">
         <v>1.3025872216186299E-3</v>
       </c>
-      <c r="E12" s="6"/>
+      <c r="E12" s="8"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
       <c r="C13" s="1">
         <v>7</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="5">
         <v>1.31460119291109E-3</v>
       </c>
-      <c r="E13" s="6"/>
+      <c r="E13" s="8"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6" t="s">
+      <c r="A14" s="8"/>
+      <c r="B14" s="8" t="s">
         <v>8</v>
       </c>
       <c r="C14" s="1">
         <v>1</v>
       </c>
-      <c r="D14" s="9">
+      <c r="D14" s="6">
         <v>7.2837430705559596E-4</v>
       </c>
-      <c r="E14" s="7">
+      <c r="E14" s="9">
         <f>AVERAGE(D14:D18)</f>
         <v>8.179226084032836E-4</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
       <c r="C15" s="1">
         <v>2</v>
       </c>
       <c r="D15" s="3">
         <v>8.4607791428294903E-4</v>
       </c>
-      <c r="E15" s="6"/>
+      <c r="E15" s="8"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
       <c r="C16" s="1">
         <v>3</v>
       </c>
       <c r="D16" s="3">
         <v>8.6882802551990898E-4</v>
       </c>
-      <c r="E16" s="6"/>
+      <c r="E16" s="8"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
       <c r="C17" s="1">
         <v>4</v>
       </c>
       <c r="D17" s="3">
         <v>8.6728801473186397E-4</v>
       </c>
-      <c r="E17" s="6"/>
+      <c r="E17" s="8"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6"/>
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
       <c r="C18" s="1">
         <v>5</v>
       </c>
       <c r="D18" s="3">
         <v>7.7904478042610005E-4</v>
       </c>
-      <c r="E18" s="6"/>
+      <c r="E18" s="8"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -802,7 +802,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E822B54-E6B9-4F6D-BD17-4242A3C7CFDB}">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
@@ -828,10 +828,10 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="8" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="1">
@@ -840,58 +840,58 @@
       <c r="D2" s="3">
         <v>8.8432581244842993E-3</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="9">
         <f>AVERAGE(D2:D6)</f>
         <v>8.8390938647225532E-3</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6"/>
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
       <c r="D3" s="3">
         <v>8.9353771851844298E-3</v>
       </c>
-      <c r="E3" s="6"/>
+      <c r="E3" s="8"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="5">
         <v>9.0998611554805892E-3</v>
       </c>
-      <c r="E4" s="6"/>
+      <c r="E4" s="8"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6"/>
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
       <c r="C5" s="1">
         <v>4</v>
       </c>
       <c r="D5" s="3">
         <v>8.7097429395581304E-3</v>
       </c>
-      <c r="E5" s="6"/>
+      <c r="E5" s="8"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6"/>
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
       <c r="C6" s="1">
         <v>5</v>
       </c>
       <c r="D6" s="3">
         <v>8.6072299189053209E-3</v>
       </c>
-      <c r="E6" s="6"/>
+      <c r="E6" s="8"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6" t="s">
+      <c r="A7" s="8"/>
+      <c r="B7" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="1">
@@ -900,148 +900,145 @@
       <c r="D7" s="3">
         <v>8.4438215453025E-3</v>
       </c>
-      <c r="E7" s="7">
-        <f>AVERAGE(D7:D13)</f>
-        <v>8.4770465602232586E-3</v>
+      <c r="E7" s="9">
+        <f>AVERAGE(D7:D12)</f>
+        <v>8.5087860683188653E-3</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
       <c r="C8" s="1">
         <v>2</v>
       </c>
       <c r="D8" s="3">
         <v>8.5537611231829604E-3</v>
       </c>
-      <c r="E8" s="6"/>
+      <c r="E8" s="8"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
       <c r="C9" s="1">
         <v>3</v>
       </c>
       <c r="D9" s="3">
         <v>8.5229916662684403E-3</v>
       </c>
-      <c r="E9" s="6"/>
+      <c r="E9" s="8"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
       <c r="C10" s="1">
         <v>4</v>
       </c>
       <c r="D10" s="3">
         <v>8.6347088477538494E-3</v>
       </c>
-      <c r="E10" s="6"/>
+      <c r="E10" s="8"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
       <c r="C11" s="1">
         <v>5</v>
       </c>
       <c r="D11" s="3">
         <v>8.2299496186085501E-3</v>
       </c>
-      <c r="E11" s="6"/>
+      <c r="E11" s="8"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="6"/>
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="1">
+        <v>6</v>
+      </c>
+      <c r="D12" s="5">
+        <v>8.6674836087969002E-3</v>
+      </c>
+      <c r="E12" s="8"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="6"/>
+      <c r="A13" s="8"/>
+      <c r="B13" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="1">
+        <v>1</v>
+      </c>
+      <c r="D13" s="3">
+        <v>6.2969138289247001E-3</v>
+      </c>
+      <c r="E13" s="9">
+        <f>AVERAGE(D13:D17)</f>
+        <v>6.2922385583522407E-3</v>
+      </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6" t="s">
-        <v>8</v>
-      </c>
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
       <c r="C14" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" s="3">
-        <v>6.2969138289247001E-3</v>
-      </c>
-      <c r="E14" s="7">
-        <f>AVERAGE(D14:D18)</f>
-        <v>6.2922385583522407E-3</v>
-      </c>
+        <v>6.4076776396648598E-3</v>
+      </c>
+      <c r="E14" s="8"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
       <c r="C15" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D15" s="3">
-        <v>6.4076776396648598E-3</v>
-      </c>
-      <c r="E15" s="6"/>
+        <v>6.2667263273711001E-3</v>
+      </c>
+      <c r="E15" s="8"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
       <c r="C16" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D16" s="3">
-        <v>6.2667263273711001E-3</v>
-      </c>
-      <c r="E16" s="6"/>
+        <v>6.2939902848690703E-3</v>
+      </c>
+      <c r="E16" s="8"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
       <c r="C17" s="1">
-        <v>4</v>
-      </c>
-      <c r="D17" s="3">
-        <v>6.2939902848690703E-3</v>
-      </c>
-      <c r="E17" s="6"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="1">
         <v>5</v>
       </c>
-      <c r="D18" s="9">
+      <c r="D17" s="6">
         <v>6.1958847109314704E-3</v>
       </c>
-      <c r="E18" s="6"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="5" t="s">
+      <c r="E17" s="8"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A2:A18"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A2:A17"/>
     <mergeCell ref="B2:B6"/>
     <mergeCell ref="E2:E6"/>
-    <mergeCell ref="B7:B13"/>
-    <mergeCell ref="E7:E13"/>
-    <mergeCell ref="B14:B18"/>
-    <mergeCell ref="E14:E18"/>
+    <mergeCell ref="B7:B12"/>
+    <mergeCell ref="E7:E12"/>
+    <mergeCell ref="B13:B17"/>
+    <mergeCell ref="E13:E17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1076,10 +1073,10 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="8" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="1">
@@ -1088,58 +1085,58 @@
       <c r="D2" s="3">
         <v>3.0401932235441099E-3</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="9">
         <f>AVERAGE(D2:D6)</f>
         <v>3.05091106736371E-3</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6"/>
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
       <c r="D3" s="3">
         <v>3.0331384444736401E-3</v>
       </c>
-      <c r="E3" s="6"/>
+      <c r="E3" s="8"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="5">
         <v>3.1182764735492199E-3</v>
       </c>
-      <c r="E4" s="6"/>
+      <c r="E4" s="8"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6"/>
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
       <c r="C5" s="1">
         <v>4</v>
       </c>
       <c r="D5" s="3">
         <v>3.0575230874511799E-3</v>
       </c>
-      <c r="E5" s="6"/>
+      <c r="E5" s="8"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6"/>
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
       <c r="C6" s="1">
         <v>5</v>
       </c>
       <c r="D6" s="3">
         <v>3.0054241078004001E-3</v>
       </c>
-      <c r="E6" s="6"/>
+      <c r="E6" s="8"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6" t="s">
+      <c r="A7" s="8"/>
+      <c r="B7" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="1">
@@ -1148,156 +1145,156 @@
       <c r="D7" s="3">
         <v>2.67957260688739E-3</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="9">
         <f>AVERAGE(D7:D14)</f>
         <v>2.7855731457791487E-3</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
       <c r="C8" s="1">
         <v>2</v>
       </c>
       <c r="D8" s="3">
         <v>2.7552147060860401E-3</v>
       </c>
-      <c r="E8" s="6"/>
+      <c r="E8" s="8"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
       <c r="C9" s="1">
         <v>3</v>
       </c>
       <c r="D9" s="3">
         <v>2.8412229817591202E-3</v>
       </c>
-      <c r="E9" s="6"/>
+      <c r="E9" s="8"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
       <c r="C10" s="1">
         <v>4</v>
       </c>
       <c r="D10" s="3">
         <v>2.8058455741671001E-3</v>
       </c>
-      <c r="E10" s="6"/>
+      <c r="E10" s="8"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
       <c r="C11" s="1">
         <v>5</v>
       </c>
       <c r="D11" s="3">
         <v>2.8247020506802201E-3</v>
       </c>
-      <c r="E11" s="6"/>
+      <c r="E11" s="8"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
       <c r="C12" s="1">
         <v>6</v>
       </c>
       <c r="D12" s="3">
         <v>2.76881779349106E-3</v>
       </c>
-      <c r="E12" s="6"/>
+      <c r="E12" s="8"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
       <c r="C13" s="1">
         <v>7</v>
       </c>
       <c r="D13" s="3">
         <v>2.6488434196267801E-3</v>
       </c>
-      <c r="E13" s="6"/>
+      <c r="E13" s="8"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
       <c r="C14" s="1">
         <v>8</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="5">
         <v>2.9603660335354798E-3</v>
       </c>
-      <c r="E14" s="6"/>
+      <c r="E14" s="8"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6" t="s">
+      <c r="A15" s="8"/>
+      <c r="B15" s="8" t="s">
         <v>8</v>
       </c>
       <c r="C15" s="1">
         <v>1</v>
       </c>
-      <c r="D15" s="9">
+      <c r="D15" s="6">
         <v>2.0622498441260802E-3</v>
       </c>
-      <c r="E15" s="7">
+      <c r="E15" s="9">
         <f>AVERAGE(D15:D19)</f>
         <v>2.2569335674385918E-3</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
       <c r="C16" s="1">
         <v>2</v>
       </c>
       <c r="D16" s="3">
         <v>2.3794685929811499E-3</v>
       </c>
-      <c r="E16" s="6"/>
+      <c r="E16" s="8"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
       <c r="C17" s="1">
         <v>3</v>
       </c>
       <c r="D17" s="3">
         <v>2.2977682884525799E-3</v>
       </c>
-      <c r="E17" s="6"/>
+      <c r="E17" s="8"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6"/>
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
       <c r="C18" s="1">
         <v>4</v>
       </c>
       <c r="D18" s="3">
         <v>2.4343621971597198E-3</v>
       </c>
-      <c r="E18" s="6"/>
+      <c r="E18" s="8"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="6"/>
-      <c r="B19" s="6"/>
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
       <c r="C19" s="1">
         <v>5</v>
       </c>
       <c r="D19" s="3">
         <v>2.1108189144734301E-3</v>
       </c>
-      <c r="E19" s="6"/>
+      <c r="E19" s="8"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/_resultados/_resultados.xlsx
+++ b/_resultados/_resultados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ravar\Documents\GitHub\recsys-fair-federation-flower\_resultados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C2A9E30-9EEB-49CD-9F7F-E364A04FF40C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{622C10A1-9423-4880-AE8F-D9882C718177}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Activity" sheetId="12" r:id="rId1"/>
@@ -802,7 +802,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E822B54-E6B9-4F6D-BD17-4242A3C7CFDB}">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
@@ -901,8 +901,8 @@
         <v>8.4438215453025E-3</v>
       </c>
       <c r="E7" s="9">
-        <f>AVERAGE(D7:D12)</f>
-        <v>8.5087860683188653E-3</v>
+        <f>AVERAGE(D7:D18)</f>
+        <v>8.3527363327023305E-3</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -911,7 +911,7 @@
       <c r="C8" s="1">
         <v>2</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="5">
         <v>8.5537611231829604E-3</v>
       </c>
       <c r="E8" s="8"/>
@@ -922,7 +922,7 @@
       <c r="C9" s="1">
         <v>3</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="5">
         <v>8.5229916662684403E-3</v>
       </c>
       <c r="E9" s="8"/>
@@ -933,7 +933,7 @@
       <c r="C10" s="1">
         <v>4</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="5">
         <v>8.6347088477538494E-3</v>
       </c>
       <c r="E10" s="8"/>
@@ -956,34 +956,29 @@
         <v>6</v>
       </c>
       <c r="D12" s="5">
-        <v>8.6674836087969002E-3</v>
+        <v>8.9993707838031105E-3</v>
       </c>
       <c r="E12" s="8"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="8"/>
-      <c r="B13" s="8" t="s">
-        <v>8</v>
-      </c>
+      <c r="B13" s="8"/>
       <c r="C13" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D13" s="3">
-        <v>6.2969138289247001E-3</v>
-      </c>
-      <c r="E13" s="9">
-        <f>AVERAGE(D13:D17)</f>
-        <v>6.2922385583522407E-3</v>
-      </c>
+        <v>8.1120902718353205E-3</v>
+      </c>
+      <c r="E13" s="8"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="8"/>
       <c r="B14" s="8"/>
       <c r="C14" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D14" s="3">
-        <v>6.4076776396648598E-3</v>
+        <v>7.9466454675489392E-3</v>
       </c>
       <c r="E14" s="8"/>
     </row>
@@ -991,10 +986,10 @@
       <c r="A15" s="8"/>
       <c r="B15" s="8"/>
       <c r="C15" s="1">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D15" s="3">
-        <v>6.2667263273711001E-3</v>
+        <v>8.04085674766436E-3</v>
       </c>
       <c r="E15" s="8"/>
     </row>
@@ -1002,10 +997,10 @@
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D16" s="3">
-        <v>6.2939902848690703E-3</v>
+        <v>7.9055709078614603E-3</v>
       </c>
       <c r="E16" s="8"/>
     </row>
@@ -1013,32 +1008,103 @@
       <c r="A17" s="8"/>
       <c r="B17" s="8"/>
       <c r="C17" s="1">
+        <v>11</v>
+      </c>
+      <c r="D17" s="3">
+        <v>8.1755854038015902E-3</v>
+      </c>
+      <c r="E17" s="8"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="1">
+        <v>12</v>
+      </c>
+      <c r="D18" s="5">
+        <v>8.6674836087969002E-3</v>
+      </c>
+      <c r="E18" s="8"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="8"/>
+      <c r="B19" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="1">
+        <v>1</v>
+      </c>
+      <c r="D19" s="3">
+        <v>6.2969138289247001E-3</v>
+      </c>
+      <c r="E19" s="9">
+        <f>AVERAGE(D19:D23)</f>
+        <v>6.2922385583522407E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="1">
+        <v>2</v>
+      </c>
+      <c r="D20" s="3">
+        <v>6.4076776396648598E-3</v>
+      </c>
+      <c r="E20" s="8"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="1">
+        <v>3</v>
+      </c>
+      <c r="D21" s="3">
+        <v>6.2667263273711001E-3</v>
+      </c>
+      <c r="E21" s="8"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="1">
+        <v>4</v>
+      </c>
+      <c r="D22" s="3">
+        <v>6.2939902848690703E-3</v>
+      </c>
+      <c r="E22" s="8"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="1">
         <v>5</v>
       </c>
-      <c r="D17" s="6">
+      <c r="D23" s="3">
         <v>6.1958847109314704E-3</v>
       </c>
-      <c r="E17" s="8"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="7" t="s">
+      <c r="E23" s="8"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A2:A17"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A2:A23"/>
     <mergeCell ref="B2:B6"/>
     <mergeCell ref="E2:E6"/>
-    <mergeCell ref="B7:B12"/>
-    <mergeCell ref="E7:E12"/>
-    <mergeCell ref="B13:B17"/>
-    <mergeCell ref="E13:E17"/>
+    <mergeCell ref="B7:B18"/>
+    <mergeCell ref="E7:E18"/>
+    <mergeCell ref="B19:B23"/>
+    <mergeCell ref="E19:E23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1167,7 +1233,7 @@
       <c r="C9" s="1">
         <v>3</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="5">
         <v>2.8412229817591202E-3</v>
       </c>
       <c r="E9" s="8"/>
@@ -1178,7 +1244,7 @@
       <c r="C10" s="1">
         <v>4</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="5">
         <v>2.8058455741671001E-3</v>
       </c>
       <c r="E10" s="8"/>
@@ -1189,7 +1255,7 @@
       <c r="C11" s="1">
         <v>5</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="5">
         <v>2.8247020506802201E-3</v>
       </c>
       <c r="E11" s="8"/>
@@ -1200,7 +1266,7 @@
       <c r="C12" s="1">
         <v>6</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="5">
         <v>2.76881779349106E-3</v>
       </c>
       <c r="E12" s="8"/>

--- a/_resultados/_resultados.xlsx
+++ b/_resultados/_resultados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ravar\Documents\GitHub\recsys-fair-federation-flower\_resultados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{622C10A1-9423-4880-AE8F-D9882C718177}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D87AE40-4AF6-4488-B35B-AF04B495F1F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Activity" sheetId="12" r:id="rId1"/>
@@ -802,7 +802,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E822B54-E6B9-4F6D-BD17-4242A3C7CFDB}">
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
@@ -1038,7 +1038,7 @@
         <v>6.2969138289247001E-3</v>
       </c>
       <c r="E19" s="9">
-        <f>AVERAGE(D19:D23)</f>
+        <f>AVERAGE(D19:D28)</f>
         <v>6.2922385583522407E-3</v>
       </c>
     </row>
@@ -1086,25 +1086,70 @@
       </c>
       <c r="E23" s="8"/>
     </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="1">
+        <v>6</v>
+      </c>
+      <c r="D24" s="3"/>
+      <c r="E24" s="8"/>
+    </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="7" t="s">
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="1">
+        <v>7</v>
+      </c>
+      <c r="D25" s="3"/>
+      <c r="E25" s="8"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="1">
+        <v>8</v>
+      </c>
+      <c r="D26" s="3"/>
+      <c r="E26" s="8"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="8"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="1">
+        <v>9</v>
+      </c>
+      <c r="D27" s="3"/>
+      <c r="E27" s="8"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="8"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="1">
+        <v>10</v>
+      </c>
+      <c r="D28" s="3"/>
+      <c r="E28" s="8"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A2:A23"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A2:A28"/>
     <mergeCell ref="B2:B6"/>
     <mergeCell ref="E2:E6"/>
     <mergeCell ref="B7:B18"/>
     <mergeCell ref="E7:E18"/>
-    <mergeCell ref="B19:B23"/>
-    <mergeCell ref="E19:E23"/>
+    <mergeCell ref="B19:B28"/>
+    <mergeCell ref="E19:E28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1113,7 +1158,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0018FF42-DB9B-49FF-AD34-CF6CC8AED773}">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
@@ -1305,7 +1350,7 @@
         <v>2.0622498441260802E-3</v>
       </c>
       <c r="E15" s="9">
-        <f>AVERAGE(D15:D19)</f>
+        <f>AVERAGE(D15:D24)</f>
         <v>2.2569335674385918E-3</v>
       </c>
     </row>
@@ -1353,25 +1398,70 @@
       </c>
       <c r="E19" s="8"/>
     </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="1">
+        <v>6</v>
+      </c>
+      <c r="D20" s="3"/>
+      <c r="E20" s="8"/>
+    </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="1">
+        <v>7</v>
+      </c>
+      <c r="D21" s="3"/>
+      <c r="E21" s="8"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="1">
+        <v>8</v>
+      </c>
+      <c r="D22" s="3"/>
+      <c r="E22" s="8"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="1">
+        <v>9</v>
+      </c>
+      <c r="D23" s="3"/>
+      <c r="E23" s="8"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="1">
+        <v>10</v>
+      </c>
+      <c r="D24" s="3"/>
+      <c r="E24" s="8"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A2:A19"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A2:A24"/>
     <mergeCell ref="B2:B6"/>
     <mergeCell ref="E2:E6"/>
     <mergeCell ref="B7:B14"/>
     <mergeCell ref="E7:E14"/>
-    <mergeCell ref="B15:B19"/>
-    <mergeCell ref="E15:E19"/>
+    <mergeCell ref="B15:B24"/>
+    <mergeCell ref="E15:E24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/_resultados/_resultados.xlsx
+++ b/_resultados/_resultados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ravar\Documents\GitHub\recsys-fair-federation-flower\_resultados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D87AE40-4AF6-4488-B35B-AF04B495F1F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{370FEFCB-0184-4EA8-8792-E8C20DE92242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Activity" sheetId="12" r:id="rId1"/>
@@ -217,7 +217,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -240,11 +240,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -263,6 +300,28 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -545,7 +604,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70966A2D-672A-451B-A3A3-B783FCE2984F}">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
@@ -635,7 +694,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="8"/>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="12" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="1">
@@ -644,156 +703,228 @@
       <c r="D7" s="3">
         <v>1.22745404238443E-3</v>
       </c>
-      <c r="E7" s="9">
-        <f>AVERAGE(D7:D13)</f>
+      <c r="E7" s="15">
+        <f>AVERAGE(D7:D16)</f>
         <v>1.255405521012254E-3</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
+      <c r="B8" s="13"/>
       <c r="C8" s="1">
         <v>2</v>
       </c>
       <c r="D8" s="3">
         <v>1.2128989821674999E-3</v>
       </c>
-      <c r="E8" s="8"/>
+      <c r="E8" s="16"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
+      <c r="B9" s="13"/>
       <c r="C9" s="1">
         <v>3</v>
       </c>
       <c r="D9" s="3">
         <v>1.2072314178239499E-3</v>
       </c>
-      <c r="E9" s="8"/>
+      <c r="E9" s="16"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
+      <c r="B10" s="13"/>
       <c r="C10" s="1">
         <v>4</v>
       </c>
       <c r="D10" s="3">
         <v>1.2932873130527701E-3</v>
       </c>
-      <c r="E10" s="8"/>
+      <c r="E10" s="16"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
+      <c r="B11" s="13"/>
       <c r="C11" s="1">
         <v>5</v>
       </c>
       <c r="D11" s="3">
         <v>1.22977847712741E-3</v>
       </c>
-      <c r="E11" s="8"/>
+      <c r="E11" s="16"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
+      <c r="B12" s="13"/>
       <c r="C12" s="1">
         <v>6</v>
       </c>
       <c r="D12" s="3">
         <v>1.3025872216186299E-3</v>
       </c>
-      <c r="E12" s="8"/>
+      <c r="E12" s="16"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
+      <c r="B13" s="13"/>
       <c r="C13" s="1">
         <v>7</v>
       </c>
       <c r="D13" s="5">
         <v>1.31460119291109E-3</v>
       </c>
-      <c r="E13" s="8"/>
+      <c r="E13" s="16"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="8"/>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="13"/>
+      <c r="C14" s="1">
         <v>8</v>
       </c>
-      <c r="C14" s="1">
-        <v>1</v>
-      </c>
-      <c r="D14" s="6">
-        <v>7.2837430705559596E-4</v>
-      </c>
-      <c r="E14" s="9">
-        <f>AVERAGE(D14:D18)</f>
-        <v>8.179226084032836E-4</v>
-      </c>
+      <c r="D14" s="3"/>
+      <c r="E14" s="16"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
+      <c r="B15" s="13"/>
       <c r="C15" s="1">
-        <v>2</v>
-      </c>
-      <c r="D15" s="3">
-        <v>8.4607791428294903E-4</v>
-      </c>
-      <c r="E15" s="8"/>
+        <v>9</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="16"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
+      <c r="B16" s="14"/>
       <c r="C16" s="1">
-        <v>3</v>
-      </c>
-      <c r="D16" s="3">
-        <v>8.6882802551990898E-4</v>
-      </c>
-      <c r="E16" s="8"/>
+        <v>10</v>
+      </c>
+      <c r="D16" s="3"/>
+      <c r="E16" s="17"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
+      <c r="B17" s="8" t="s">
+        <v>8</v>
+      </c>
       <c r="C17" s="1">
-        <v>4</v>
-      </c>
-      <c r="D17" s="3">
-        <v>8.6728801473186397E-4</v>
-      </c>
-      <c r="E17" s="8"/>
+        <v>1</v>
+      </c>
+      <c r="D17" s="6">
+        <v>7.2837430705559596E-4</v>
+      </c>
+      <c r="E17" s="9">
+        <f>AVERAGE(D17:D26)</f>
+        <v>8.179226084032836E-4</v>
+      </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
       <c r="C18" s="1">
+        <v>2</v>
+      </c>
+      <c r="D18" s="3">
+        <v>8.4607791428294903E-4</v>
+      </c>
+      <c r="E18" s="8"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="1">
+        <v>3</v>
+      </c>
+      <c r="D19" s="3">
+        <v>8.6882802551990898E-4</v>
+      </c>
+      <c r="E19" s="8"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="1">
+        <v>4</v>
+      </c>
+      <c r="D20" s="3">
+        <v>8.6728801473186397E-4</v>
+      </c>
+      <c r="E20" s="8"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="1">
         <v>5</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D21" s="3">
         <v>7.7904478042610005E-4</v>
       </c>
-      <c r="E18" s="8"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="7" t="s">
+      <c r="E21" s="8"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="1">
+        <v>6</v>
+      </c>
+      <c r="D22" s="3"/>
+      <c r="E22" s="8"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="1">
+        <v>7</v>
+      </c>
+      <c r="D23" s="3"/>
+      <c r="E23" s="8"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="1">
+        <v>8</v>
+      </c>
+      <c r="D24" s="3"/>
+      <c r="E24" s="8"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="1">
+        <v>9</v>
+      </c>
+      <c r="D25" s="3"/>
+      <c r="E25" s="8"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="1">
+        <v>10</v>
+      </c>
+      <c r="D26" s="3"/>
+      <c r="E26" s="8"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A2:A18"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A2:A26"/>
     <mergeCell ref="B2:B6"/>
     <mergeCell ref="E2:E6"/>
-    <mergeCell ref="B7:B13"/>
-    <mergeCell ref="E7:E13"/>
-    <mergeCell ref="B14:B18"/>
-    <mergeCell ref="E14:E18"/>
+    <mergeCell ref="B17:B26"/>
+    <mergeCell ref="E17:E26"/>
+    <mergeCell ref="B7:B16"/>
+    <mergeCell ref="E7:E16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -806,7 +937,8 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="22.77734375" customWidth="1"/>
+    <col min="4" max="4" width="22.77734375" style="11" customWidth="1"/>
+    <col min="5" max="5" width="22.77734375" customWidth="1"/>
     <col min="7" max="7" width="8.88671875" style="4"/>
   </cols>
   <sheetData>
@@ -820,7 +952,7 @@
       <c r="C1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="10" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="2" t="s">
@@ -862,7 +994,7 @@
       <c r="C4" s="1">
         <v>3</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="3">
         <v>9.0998611554805892E-3</v>
       </c>
       <c r="E4" s="8"/>
@@ -902,7 +1034,7 @@
       </c>
       <c r="E7" s="9">
         <f>AVERAGE(D7:D18)</f>
-        <v>8.3527363327023305E-3</v>
+        <v>8.5087860683188653E-3</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
@@ -911,7 +1043,7 @@
       <c r="C8" s="1">
         <v>2</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="3">
         <v>8.5537611231829604E-3</v>
       </c>
       <c r="E8" s="8"/>
@@ -922,7 +1054,7 @@
       <c r="C9" s="1">
         <v>3</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="3">
         <v>8.5229916662684403E-3</v>
       </c>
       <c r="E9" s="8"/>
@@ -933,7 +1065,7 @@
       <c r="C10" s="1">
         <v>4</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="3">
         <v>8.6347088477538494E-3</v>
       </c>
       <c r="E10" s="8"/>
@@ -955,8 +1087,8 @@
       <c r="C12" s="1">
         <v>6</v>
       </c>
-      <c r="D12" s="5">
-        <v>8.9993707838031105E-3</v>
+      <c r="D12" s="3">
+        <v>8.6674836087969002E-3</v>
       </c>
       <c r="E12" s="8"/>
     </row>
@@ -966,9 +1098,7 @@
       <c r="C13" s="1">
         <v>7</v>
       </c>
-      <c r="D13" s="3">
-        <v>8.1120902718353205E-3</v>
-      </c>
+      <c r="D13" s="3"/>
       <c r="E13" s="8"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -977,9 +1107,7 @@
       <c r="C14" s="1">
         <v>8</v>
       </c>
-      <c r="D14" s="3">
-        <v>7.9466454675489392E-3</v>
-      </c>
+      <c r="D14" s="3"/>
       <c r="E14" s="8"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -988,9 +1116,7 @@
       <c r="C15" s="1">
         <v>9</v>
       </c>
-      <c r="D15" s="3">
-        <v>8.04085674766436E-3</v>
-      </c>
+      <c r="D15" s="3"/>
       <c r="E15" s="8"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -999,9 +1125,7 @@
       <c r="C16" s="1">
         <v>10</v>
       </c>
-      <c r="D16" s="3">
-        <v>7.9055709078614603E-3</v>
-      </c>
+      <c r="D16" s="3"/>
       <c r="E16" s="8"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -1010,9 +1134,7 @@
       <c r="C17" s="1">
         <v>11</v>
       </c>
-      <c r="D17" s="3">
-        <v>8.1755854038015902E-3</v>
-      </c>
+      <c r="D17" s="3"/>
       <c r="E17" s="8"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -1021,9 +1143,7 @@
       <c r="C18" s="1">
         <v>12</v>
       </c>
-      <c r="D18" s="5">
-        <v>8.6674836087969002E-3</v>
-      </c>
+      <c r="D18" s="3"/>
       <c r="E18" s="8"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -1039,7 +1159,7 @@
       </c>
       <c r="E19" s="9">
         <f>AVERAGE(D19:D28)</f>
-        <v>6.2922385583522407E-3</v>
+        <v>6.1674863148601993E-3</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -1092,7 +1212,9 @@
       <c r="C24" s="1">
         <v>6</v>
       </c>
-      <c r="D24" s="3"/>
+      <c r="D24" s="3">
+        <v>5.8309748107789102E-3</v>
+      </c>
       <c r="E24" s="8"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
@@ -1101,7 +1223,9 @@
       <c r="C25" s="1">
         <v>7</v>
       </c>
-      <c r="D25" s="3"/>
+      <c r="D25" s="3">
+        <v>5.5695092562729398E-3</v>
+      </c>
       <c r="E25" s="8"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
@@ -1110,7 +1234,9 @@
       <c r="C26" s="1">
         <v>8</v>
       </c>
-      <c r="D26" s="3"/>
+      <c r="D26" s="3">
+        <v>6.4782136600685398E-3</v>
+      </c>
       <c r="E26" s="8"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
@@ -1158,11 +1284,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0018FF42-DB9B-49FF-AD34-CF6CC8AED773}">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="22.77734375" customWidth="1"/>
+    <col min="4" max="4" width="22.77734375" style="11" customWidth="1"/>
+    <col min="5" max="5" width="22.77734375" customWidth="1"/>
     <col min="7" max="7" width="8.88671875" style="4"/>
   </cols>
   <sheetData>
@@ -1176,7 +1303,7 @@
       <c r="C1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="10" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="2" t="s">
@@ -1218,7 +1345,7 @@
       <c r="C4" s="1">
         <v>3</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="3">
         <v>3.1182764735492199E-3</v>
       </c>
       <c r="E4" s="8"/>
@@ -1257,7 +1384,7 @@
         <v>2.67957260688739E-3</v>
       </c>
       <c r="E7" s="9">
-        <f>AVERAGE(D7:D14)</f>
+        <f>AVERAGE(D7:D16)</f>
         <v>2.7855731457791487E-3</v>
       </c>
     </row>
@@ -1278,7 +1405,7 @@
       <c r="C9" s="1">
         <v>3</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="3">
         <v>2.8412229817591202E-3</v>
       </c>
       <c r="E9" s="8"/>
@@ -1289,7 +1416,7 @@
       <c r="C10" s="1">
         <v>4</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="3">
         <v>2.8058455741671001E-3</v>
       </c>
       <c r="E10" s="8"/>
@@ -1300,7 +1427,7 @@
       <c r="C11" s="1">
         <v>5</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11" s="3">
         <v>2.8247020506802201E-3</v>
       </c>
       <c r="E11" s="8"/>
@@ -1311,7 +1438,7 @@
       <c r="C12" s="1">
         <v>6</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="3">
         <v>2.76881779349106E-3</v>
       </c>
       <c r="E12" s="8"/>
@@ -1333,57 +1460,53 @@
       <c r="C14" s="1">
         <v>8</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D14" s="3">
         <v>2.9603660335354798E-3</v>
       </c>
       <c r="E14" s="8"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="8"/>
-      <c r="B15" s="8" t="s">
-        <v>8</v>
-      </c>
+      <c r="B15" s="8"/>
       <c r="C15" s="1">
-        <v>1</v>
-      </c>
-      <c r="D15" s="6">
-        <v>2.0622498441260802E-3</v>
-      </c>
-      <c r="E15" s="9">
-        <f>AVERAGE(D15:D24)</f>
-        <v>2.2569335674385918E-3</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="8"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="1">
-        <v>2</v>
-      </c>
-      <c r="D16" s="3">
-        <v>2.3794685929811499E-3</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="D16" s="3"/>
       <c r="E16" s="8"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
+      <c r="B17" s="8" t="s">
+        <v>8</v>
+      </c>
       <c r="C17" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D17" s="3">
-        <v>2.2977682884525799E-3</v>
-      </c>
-      <c r="E17" s="8"/>
+        <v>2.0622498441260802E-3</v>
+      </c>
+      <c r="E17" s="9">
+        <f>AVERAGE(D17:D26)</f>
+        <v>2.3243687230132359E-3</v>
+      </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
       <c r="C18" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D18" s="3">
-        <v>2.4343621971597198E-3</v>
+        <v>2.3794685929811499E-3</v>
       </c>
       <c r="E18" s="8"/>
     </row>
@@ -1391,10 +1514,10 @@
       <c r="A19" s="8"/>
       <c r="B19" s="8"/>
       <c r="C19" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D19" s="3">
-        <v>2.1108189144734301E-3</v>
+        <v>2.2977682884525799E-3</v>
       </c>
       <c r="E19" s="8"/>
     </row>
@@ -1402,66 +1525,94 @@
       <c r="A20" s="8"/>
       <c r="B20" s="8"/>
       <c r="C20" s="1">
-        <v>6</v>
-      </c>
-      <c r="D20" s="3"/>
+        <v>4</v>
+      </c>
+      <c r="D20" s="3">
+        <v>2.4343621971597198E-3</v>
+      </c>
       <c r="E20" s="8"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="8"/>
       <c r="B21" s="8"/>
       <c r="C21" s="1">
-        <v>7</v>
-      </c>
-      <c r="D21" s="3"/>
+        <v>5</v>
+      </c>
+      <c r="D21" s="3">
+        <v>2.1108189144734301E-3</v>
+      </c>
       <c r="E21" s="8"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="8"/>
       <c r="B22" s="8"/>
       <c r="C22" s="1">
-        <v>8</v>
-      </c>
-      <c r="D22" s="3"/>
+        <v>6</v>
+      </c>
+      <c r="D22" s="3">
+        <v>2.3621231197317998E-3</v>
+      </c>
       <c r="E22" s="8"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="8"/>
       <c r="B23" s="8"/>
       <c r="C23" s="1">
-        <v>9</v>
-      </c>
-      <c r="D23" s="3"/>
+        <v>7</v>
+      </c>
+      <c r="D23" s="3">
+        <v>2.4698851227879198E-3</v>
+      </c>
       <c r="E23" s="8"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="8"/>
       <c r="B24" s="8"/>
       <c r="C24" s="1">
+        <v>8</v>
+      </c>
+      <c r="D24" s="3">
+        <v>2.47827370439321E-3</v>
+      </c>
+      <c r="E24" s="8"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="1">
+        <v>9</v>
+      </c>
+      <c r="D25" s="3"/>
+      <c r="E25" s="8"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="1">
         <v>10</v>
       </c>
-      <c r="D24" s="3"/>
-      <c r="E24" s="8"/>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="7" t="s">
+      <c r="D26" s="3"/>
+      <c r="E26" s="8"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A2:A24"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A2:A26"/>
     <mergeCell ref="B2:B6"/>
     <mergeCell ref="E2:E6"/>
-    <mergeCell ref="B7:B14"/>
-    <mergeCell ref="E7:E14"/>
-    <mergeCell ref="B15:B24"/>
-    <mergeCell ref="E15:E24"/>
+    <mergeCell ref="B7:B16"/>
+    <mergeCell ref="E7:E16"/>
+    <mergeCell ref="B17:B26"/>
+    <mergeCell ref="E17:E26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/_resultados/_resultados.xlsx
+++ b/_resultados/_resultados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ravar\Documents\GitHub\recsys-fair-federation-flower\_resultados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{370FEFCB-0184-4EA8-8792-E8C20DE92242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A23AD160-DF9B-4E76-8992-6A62FDBCD30E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Activity" sheetId="12" r:id="rId1"/>
@@ -293,6 +293,10 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -302,10 +306,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -631,10 +631,10 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="10" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="1">
@@ -643,57 +643,57 @@
       <c r="D2" s="3">
         <v>1.81177350386232E-3</v>
       </c>
-      <c r="E2" s="9">
+      <c r="E2" s="11">
         <f>AVERAGE(D2:D6)</f>
         <v>1.8257771737235358E-3</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
+      <c r="A3" s="10"/>
+      <c r="B3" s="10"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
       <c r="D3" s="3">
         <v>1.8148006812720001E-3</v>
       </c>
-      <c r="E3" s="8"/>
+      <c r="E3" s="10"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
       <c r="D4" s="5">
         <v>1.9192099019838601E-3</v>
       </c>
-      <c r="E4" s="8"/>
+      <c r="E4" s="10"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
+      <c r="A5" s="10"/>
+      <c r="B5" s="10"/>
       <c r="C5" s="1">
         <v>4</v>
       </c>
       <c r="D5" s="3">
         <v>1.7683693332491801E-3</v>
       </c>
-      <c r="E5" s="8"/>
+      <c r="E5" s="10"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
+      <c r="A6" s="10"/>
+      <c r="B6" s="10"/>
       <c r="C6" s="1">
         <v>5</v>
       </c>
       <c r="D6" s="3">
         <v>1.81473244825032E-3</v>
       </c>
-      <c r="E6" s="8"/>
+      <c r="E6" s="10"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="8"/>
+      <c r="A7" s="10"/>
       <c r="B7" s="12" t="s">
         <v>7</v>
       </c>
@@ -709,7 +709,7 @@
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="8"/>
+      <c r="A8" s="10"/>
       <c r="B8" s="13"/>
       <c r="C8" s="1">
         <v>2</v>
@@ -720,7 +720,7 @@
       <c r="E8" s="16"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="8"/>
+      <c r="A9" s="10"/>
       <c r="B9" s="13"/>
       <c r="C9" s="1">
         <v>3</v>
@@ -731,7 +731,7 @@
       <c r="E9" s="16"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="8"/>
+      <c r="A10" s="10"/>
       <c r="B10" s="13"/>
       <c r="C10" s="1">
         <v>4</v>
@@ -742,7 +742,7 @@
       <c r="E10" s="16"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="8"/>
+      <c r="A11" s="10"/>
       <c r="B11" s="13"/>
       <c r="C11" s="1">
         <v>5</v>
@@ -753,7 +753,7 @@
       <c r="E11" s="16"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="8"/>
+      <c r="A12" s="10"/>
       <c r="B12" s="13"/>
       <c r="C12" s="1">
         <v>6</v>
@@ -764,7 +764,7 @@
       <c r="E12" s="16"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="8"/>
+      <c r="A13" s="10"/>
       <c r="B13" s="13"/>
       <c r="C13" s="1">
         <v>7</v>
@@ -775,7 +775,7 @@
       <c r="E13" s="16"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="8"/>
+      <c r="A14" s="10"/>
       <c r="B14" s="13"/>
       <c r="C14" s="1">
         <v>8</v>
@@ -784,7 +784,7 @@
       <c r="E14" s="16"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="8"/>
+      <c r="A15" s="10"/>
       <c r="B15" s="13"/>
       <c r="C15" s="1">
         <v>9</v>
@@ -793,7 +793,7 @@
       <c r="E15" s="16"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="8"/>
+      <c r="A16" s="10"/>
       <c r="B16" s="14"/>
       <c r="C16" s="1">
         <v>10</v>
@@ -802,8 +802,8 @@
       <c r="E16" s="17"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8" t="s">
+      <c r="A17" s="10"/>
+      <c r="B17" s="10" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="1">
@@ -812,108 +812,108 @@
       <c r="D17" s="6">
         <v>7.2837430705559596E-4</v>
       </c>
-      <c r="E17" s="9">
+      <c r="E17" s="11">
         <f>AVERAGE(D17:D26)</f>
         <v>8.179226084032836E-4</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
+      <c r="A18" s="10"/>
+      <c r="B18" s="10"/>
       <c r="C18" s="1">
         <v>2</v>
       </c>
       <c r="D18" s="3">
         <v>8.4607791428294903E-4</v>
       </c>
-      <c r="E18" s="8"/>
+      <c r="E18" s="10"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
+      <c r="A19" s="10"/>
+      <c r="B19" s="10"/>
       <c r="C19" s="1">
         <v>3</v>
       </c>
       <c r="D19" s="3">
         <v>8.6882802551990898E-4</v>
       </c>
-      <c r="E19" s="8"/>
+      <c r="E19" s="10"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
+      <c r="A20" s="10"/>
+      <c r="B20" s="10"/>
       <c r="C20" s="1">
         <v>4</v>
       </c>
       <c r="D20" s="3">
         <v>8.6728801473186397E-4</v>
       </c>
-      <c r="E20" s="8"/>
+      <c r="E20" s="10"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
+      <c r="A21" s="10"/>
+      <c r="B21" s="10"/>
       <c r="C21" s="1">
         <v>5</v>
       </c>
       <c r="D21" s="3">
         <v>7.7904478042610005E-4</v>
       </c>
-      <c r="E21" s="8"/>
+      <c r="E21" s="10"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
+      <c r="A22" s="10"/>
+      <c r="B22" s="10"/>
       <c r="C22" s="1">
         <v>6</v>
       </c>
       <c r="D22" s="3"/>
-      <c r="E22" s="8"/>
+      <c r="E22" s="10"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8"/>
+      <c r="A23" s="10"/>
+      <c r="B23" s="10"/>
       <c r="C23" s="1">
         <v>7</v>
       </c>
       <c r="D23" s="3"/>
-      <c r="E23" s="8"/>
+      <c r="E23" s="10"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8"/>
+      <c r="A24" s="10"/>
+      <c r="B24" s="10"/>
       <c r="C24" s="1">
         <v>8</v>
       </c>
       <c r="D24" s="3"/>
-      <c r="E24" s="8"/>
+      <c r="E24" s="10"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
+      <c r="A25" s="10"/>
+      <c r="B25" s="10"/>
       <c r="C25" s="1">
         <v>9</v>
       </c>
       <c r="D25" s="3"/>
-      <c r="E25" s="8"/>
+      <c r="E25" s="10"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
+      <c r="A26" s="10"/>
+      <c r="B26" s="10"/>
       <c r="C26" s="1">
         <v>10</v>
       </c>
       <c r="D26" s="3"/>
-      <c r="E26" s="8"/>
+      <c r="E26" s="10"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="7" t="s">
+      <c r="A28" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -937,7 +937,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.77734375" style="11" customWidth="1"/>
+    <col min="4" max="4" width="22.77734375" style="8" customWidth="1"/>
     <col min="5" max="5" width="22.77734375" customWidth="1"/>
     <col min="7" max="7" width="8.88671875" style="4"/>
   </cols>
@@ -952,7 +952,7 @@
       <c r="C1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="7" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="2" t="s">
@@ -960,10 +960,10 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="10" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="1">
@@ -972,58 +972,58 @@
       <c r="D2" s="3">
         <v>8.8432581244842993E-3</v>
       </c>
-      <c r="E2" s="9">
+      <c r="E2" s="11">
         <f>AVERAGE(D2:D6)</f>
         <v>8.8390938647225532E-3</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
+      <c r="A3" s="10"/>
+      <c r="B3" s="10"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
       <c r="D3" s="3">
         <v>8.9353771851844298E-3</v>
       </c>
-      <c r="E3" s="8"/>
+      <c r="E3" s="10"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
       <c r="D4" s="3">
         <v>9.0998611554805892E-3</v>
       </c>
-      <c r="E4" s="8"/>
+      <c r="E4" s="10"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
+      <c r="A5" s="10"/>
+      <c r="B5" s="10"/>
       <c r="C5" s="1">
         <v>4</v>
       </c>
       <c r="D5" s="3">
         <v>8.7097429395581304E-3</v>
       </c>
-      <c r="E5" s="8"/>
+      <c r="E5" s="10"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
+      <c r="A6" s="10"/>
+      <c r="B6" s="10"/>
       <c r="C6" s="1">
         <v>5</v>
       </c>
       <c r="D6" s="3">
         <v>8.6072299189053209E-3</v>
       </c>
-      <c r="E6" s="8"/>
+      <c r="E6" s="10"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8" t="s">
+      <c r="A7" s="10"/>
+      <c r="B7" s="10" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="1">
@@ -1032,123 +1032,123 @@
       <c r="D7" s="3">
         <v>8.4438215453025E-3</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="11">
         <f>AVERAGE(D7:D18)</f>
         <v>8.5087860683188653E-3</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
+      <c r="A8" s="10"/>
+      <c r="B8" s="10"/>
       <c r="C8" s="1">
         <v>2</v>
       </c>
       <c r="D8" s="3">
         <v>8.5537611231829604E-3</v>
       </c>
-      <c r="E8" s="8"/>
+      <c r="E8" s="10"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
+      <c r="A9" s="10"/>
+      <c r="B9" s="10"/>
       <c r="C9" s="1">
         <v>3</v>
       </c>
       <c r="D9" s="3">
         <v>8.5229916662684403E-3</v>
       </c>
-      <c r="E9" s="8"/>
+      <c r="E9" s="10"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
+      <c r="A10" s="10"/>
+      <c r="B10" s="10"/>
       <c r="C10" s="1">
         <v>4</v>
       </c>
       <c r="D10" s="3">
         <v>8.6347088477538494E-3</v>
       </c>
-      <c r="E10" s="8"/>
+      <c r="E10" s="10"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
+      <c r="A11" s="10"/>
+      <c r="B11" s="10"/>
       <c r="C11" s="1">
         <v>5</v>
       </c>
       <c r="D11" s="3">
         <v>8.2299496186085501E-3</v>
       </c>
-      <c r="E11" s="8"/>
+      <c r="E11" s="10"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
+      <c r="A12" s="10"/>
+      <c r="B12" s="10"/>
       <c r="C12" s="1">
         <v>6</v>
       </c>
       <c r="D12" s="3">
         <v>8.6674836087969002E-3</v>
       </c>
-      <c r="E12" s="8"/>
+      <c r="E12" s="10"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
+      <c r="A13" s="10"/>
+      <c r="B13" s="10"/>
       <c r="C13" s="1">
         <v>7</v>
       </c>
       <c r="D13" s="3"/>
-      <c r="E13" s="8"/>
+      <c r="E13" s="10"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
+      <c r="A14" s="10"/>
+      <c r="B14" s="10"/>
       <c r="C14" s="1">
         <v>8</v>
       </c>
       <c r="D14" s="3"/>
-      <c r="E14" s="8"/>
+      <c r="E14" s="10"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
+      <c r="A15" s="10"/>
+      <c r="B15" s="10"/>
       <c r="C15" s="1">
         <v>9</v>
       </c>
       <c r="D15" s="3"/>
-      <c r="E15" s="8"/>
+      <c r="E15" s="10"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
+      <c r="A16" s="10"/>
+      <c r="B16" s="10"/>
       <c r="C16" s="1">
         <v>10</v>
       </c>
       <c r="D16" s="3"/>
-      <c r="E16" s="8"/>
+      <c r="E16" s="10"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
+      <c r="A17" s="10"/>
+      <c r="B17" s="10"/>
       <c r="C17" s="1">
         <v>11</v>
       </c>
       <c r="D17" s="3"/>
-      <c r="E17" s="8"/>
+      <c r="E17" s="10"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
+      <c r="A18" s="10"/>
+      <c r="B18" s="10"/>
       <c r="C18" s="1">
         <v>12</v>
       </c>
       <c r="D18" s="3"/>
-      <c r="E18" s="8"/>
+      <c r="E18" s="10"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8" t="s">
+      <c r="A19" s="10"/>
+      <c r="B19" s="10" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="1">
@@ -1157,114 +1157,114 @@
       <c r="D19" s="3">
         <v>6.2969138289247001E-3</v>
       </c>
-      <c r="E19" s="9">
+      <c r="E19" s="11">
         <f>AVERAGE(D19:D28)</f>
         <v>6.1674863148601993E-3</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
+      <c r="A20" s="10"/>
+      <c r="B20" s="10"/>
       <c r="C20" s="1">
         <v>2</v>
       </c>
       <c r="D20" s="3">
         <v>6.4076776396648598E-3</v>
       </c>
-      <c r="E20" s="8"/>
+      <c r="E20" s="10"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
+      <c r="A21" s="10"/>
+      <c r="B21" s="10"/>
       <c r="C21" s="1">
         <v>3</v>
       </c>
       <c r="D21" s="3">
         <v>6.2667263273711001E-3</v>
       </c>
-      <c r="E21" s="8"/>
+      <c r="E21" s="10"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
+      <c r="A22" s="10"/>
+      <c r="B22" s="10"/>
       <c r="C22" s="1">
         <v>4</v>
       </c>
       <c r="D22" s="3">
         <v>6.2939902848690703E-3</v>
       </c>
-      <c r="E22" s="8"/>
+      <c r="E22" s="10"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8"/>
+      <c r="A23" s="10"/>
+      <c r="B23" s="10"/>
       <c r="C23" s="1">
         <v>5</v>
       </c>
       <c r="D23" s="3">
         <v>6.1958847109314704E-3</v>
       </c>
-      <c r="E23" s="8"/>
+      <c r="E23" s="10"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8"/>
+      <c r="A24" s="10"/>
+      <c r="B24" s="10"/>
       <c r="C24" s="1">
         <v>6</v>
       </c>
       <c r="D24" s="3">
         <v>5.8309748107789102E-3</v>
       </c>
-      <c r="E24" s="8"/>
+      <c r="E24" s="10"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
+      <c r="A25" s="10"/>
+      <c r="B25" s="10"/>
       <c r="C25" s="1">
         <v>7</v>
       </c>
       <c r="D25" s="3">
         <v>5.5695092562729398E-3</v>
       </c>
-      <c r="E25" s="8"/>
+      <c r="E25" s="10"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
+      <c r="A26" s="10"/>
+      <c r="B26" s="10"/>
       <c r="C26" s="1">
         <v>8</v>
       </c>
       <c r="D26" s="3">
         <v>6.4782136600685398E-3</v>
       </c>
-      <c r="E26" s="8"/>
+      <c r="E26" s="10"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="8"/>
-      <c r="B27" s="8"/>
+      <c r="A27" s="10"/>
+      <c r="B27" s="10"/>
       <c r="C27" s="1">
         <v>9</v>
       </c>
       <c r="D27" s="3"/>
-      <c r="E27" s="8"/>
+      <c r="E27" s="10"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="8"/>
-      <c r="B28" s="8"/>
+      <c r="A28" s="10"/>
+      <c r="B28" s="10"/>
       <c r="C28" s="1">
         <v>10</v>
       </c>
       <c r="D28" s="3"/>
-      <c r="E28" s="8"/>
+      <c r="E28" s="10"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="7" t="s">
+      <c r="A30" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B30" s="7"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -1288,7 +1288,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.77734375" style="11" customWidth="1"/>
+    <col min="4" max="4" width="22.77734375" style="8" customWidth="1"/>
     <col min="5" max="5" width="22.77734375" customWidth="1"/>
     <col min="7" max="7" width="8.88671875" style="4"/>
   </cols>
@@ -1303,7 +1303,7 @@
       <c r="C1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="7" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="2" t="s">
@@ -1311,10 +1311,10 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="10" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="1">
@@ -1323,58 +1323,58 @@
       <c r="D2" s="3">
         <v>3.0401932235441099E-3</v>
       </c>
-      <c r="E2" s="9">
+      <c r="E2" s="11">
         <f>AVERAGE(D2:D6)</f>
         <v>3.05091106736371E-3</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
+      <c r="A3" s="10"/>
+      <c r="B3" s="10"/>
       <c r="C3" s="1">
         <v>2</v>
       </c>
       <c r="D3" s="3">
         <v>3.0331384444736401E-3</v>
       </c>
-      <c r="E3" s="8"/>
+      <c r="E3" s="10"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
       <c r="C4" s="1">
         <v>3</v>
       </c>
       <c r="D4" s="3">
         <v>3.1182764735492199E-3</v>
       </c>
-      <c r="E4" s="8"/>
+      <c r="E4" s="10"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
+      <c r="A5" s="10"/>
+      <c r="B5" s="10"/>
       <c r="C5" s="1">
         <v>4</v>
       </c>
       <c r="D5" s="3">
         <v>3.0575230874511799E-3</v>
       </c>
-      <c r="E5" s="8"/>
+      <c r="E5" s="10"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
+      <c r="A6" s="10"/>
+      <c r="B6" s="10"/>
       <c r="C6" s="1">
         <v>5</v>
       </c>
       <c r="D6" s="3">
         <v>3.0054241078004001E-3</v>
       </c>
-      <c r="E6" s="8"/>
+      <c r="E6" s="10"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8" t="s">
+      <c r="A7" s="10"/>
+      <c r="B7" s="10" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="1">
@@ -1383,109 +1383,109 @@
       <c r="D7" s="3">
         <v>2.67957260688739E-3</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="11">
         <f>AVERAGE(D7:D16)</f>
         <v>2.7855731457791487E-3</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
+      <c r="A8" s="10"/>
+      <c r="B8" s="10"/>
       <c r="C8" s="1">
         <v>2</v>
       </c>
       <c r="D8" s="3">
         <v>2.7552147060860401E-3</v>
       </c>
-      <c r="E8" s="8"/>
+      <c r="E8" s="10"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
+      <c r="A9" s="10"/>
+      <c r="B9" s="10"/>
       <c r="C9" s="1">
         <v>3</v>
       </c>
       <c r="D9" s="3">
         <v>2.8412229817591202E-3</v>
       </c>
-      <c r="E9" s="8"/>
+      <c r="E9" s="10"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
+      <c r="A10" s="10"/>
+      <c r="B10" s="10"/>
       <c r="C10" s="1">
         <v>4</v>
       </c>
       <c r="D10" s="3">
         <v>2.8058455741671001E-3</v>
       </c>
-      <c r="E10" s="8"/>
+      <c r="E10" s="10"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
+      <c r="A11" s="10"/>
+      <c r="B11" s="10"/>
       <c r="C11" s="1">
         <v>5</v>
       </c>
       <c r="D11" s="3">
         <v>2.8247020506802201E-3</v>
       </c>
-      <c r="E11" s="8"/>
+      <c r="E11" s="10"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
+      <c r="A12" s="10"/>
+      <c r="B12" s="10"/>
       <c r="C12" s="1">
         <v>6</v>
       </c>
       <c r="D12" s="3">
         <v>2.76881779349106E-3</v>
       </c>
-      <c r="E12" s="8"/>
+      <c r="E12" s="10"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
+      <c r="A13" s="10"/>
+      <c r="B13" s="10"/>
       <c r="C13" s="1">
         <v>7</v>
       </c>
       <c r="D13" s="3">
         <v>2.6488434196267801E-3</v>
       </c>
-      <c r="E13" s="8"/>
+      <c r="E13" s="10"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
+      <c r="A14" s="10"/>
+      <c r="B14" s="10"/>
       <c r="C14" s="1">
         <v>8</v>
       </c>
       <c r="D14" s="3">
         <v>2.9603660335354798E-3</v>
       </c>
-      <c r="E14" s="8"/>
+      <c r="E14" s="10"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
+      <c r="A15" s="10"/>
+      <c r="B15" s="10"/>
       <c r="C15" s="1">
         <v>9</v>
       </c>
       <c r="D15" s="3"/>
-      <c r="E15" s="8"/>
+      <c r="E15" s="10"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
+      <c r="A16" s="10"/>
+      <c r="B16" s="10"/>
       <c r="C16" s="1">
         <v>10</v>
       </c>
       <c r="D16" s="3"/>
-      <c r="E16" s="8"/>
+      <c r="E16" s="10"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8" t="s">
+      <c r="A17" s="10"/>
+      <c r="B17" s="10" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="1">
@@ -1494,114 +1494,116 @@
       <c r="D17" s="3">
         <v>2.0622498441260802E-3</v>
       </c>
-      <c r="E17" s="9">
+      <c r="E17" s="11">
         <f>AVERAGE(D17:D26)</f>
-        <v>2.3243687230132359E-3</v>
+        <v>2.3221626048794933E-3</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
+      <c r="A18" s="10"/>
+      <c r="B18" s="10"/>
       <c r="C18" s="1">
         <v>2</v>
       </c>
       <c r="D18" s="3">
         <v>2.3794685929811499E-3</v>
       </c>
-      <c r="E18" s="8"/>
+      <c r="E18" s="10"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
+      <c r="A19" s="10"/>
+      <c r="B19" s="10"/>
       <c r="C19" s="1">
         <v>3</v>
       </c>
       <c r="D19" s="3">
         <v>2.2977682884525799E-3</v>
       </c>
-      <c r="E19" s="8"/>
+      <c r="E19" s="10"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
+      <c r="A20" s="10"/>
+      <c r="B20" s="10"/>
       <c r="C20" s="1">
         <v>4</v>
       </c>
       <c r="D20" s="3">
         <v>2.4343621971597198E-3</v>
       </c>
-      <c r="E20" s="8"/>
+      <c r="E20" s="10"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
+      <c r="A21" s="10"/>
+      <c r="B21" s="10"/>
       <c r="C21" s="1">
         <v>5</v>
       </c>
       <c r="D21" s="3">
         <v>2.1108189144734301E-3</v>
       </c>
-      <c r="E21" s="8"/>
+      <c r="E21" s="10"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
+      <c r="A22" s="10"/>
+      <c r="B22" s="10"/>
       <c r="C22" s="1">
         <v>6</v>
       </c>
       <c r="D22" s="3">
         <v>2.3621231197317998E-3</v>
       </c>
-      <c r="E22" s="8"/>
+      <c r="E22" s="10"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8"/>
+      <c r="A23" s="10"/>
+      <c r="B23" s="10"/>
       <c r="C23" s="1">
         <v>7</v>
       </c>
       <c r="D23" s="3">
         <v>2.4698851227879198E-3</v>
       </c>
-      <c r="E23" s="8"/>
+      <c r="E23" s="10"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8"/>
+      <c r="A24" s="10"/>
+      <c r="B24" s="10"/>
       <c r="C24" s="1">
         <v>8</v>
       </c>
       <c r="D24" s="3">
         <v>2.47827370439321E-3</v>
       </c>
-      <c r="E24" s="8"/>
+      <c r="E24" s="10"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
+      <c r="A25" s="10"/>
+      <c r="B25" s="10"/>
       <c r="C25" s="1">
         <v>9</v>
       </c>
-      <c r="D25" s="3"/>
-      <c r="E25" s="8"/>
+      <c r="D25" s="3">
+        <v>2.3045136598095501E-3</v>
+      </c>
+      <c r="E25" s="10"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
+      <c r="A26" s="10"/>
+      <c r="B26" s="10"/>
       <c r="C26" s="1">
         <v>10</v>
       </c>
       <c r="D26" s="3"/>
-      <c r="E26" s="8"/>
+      <c r="E26" s="10"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="7" t="s">
+      <c r="A28" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/_resultados/_resultados.xlsx
+++ b/_resultados/_resultados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ravar\Documents\GitHub\recsys-fair-federation-flower\_resultados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A23AD160-DF9B-4E76-8992-6A62FDBCD30E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A54AED0-BAAB-4028-8078-7598DD3BB62A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Activity" sheetId="12" r:id="rId1"/>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="E17" s="11">
         <f>AVERAGE(D17:D26)</f>
-        <v>2.3221626048794933E-3</v>
+        <v>2.3188578817489917E-3</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -1593,7 +1593,9 @@
       <c r="C26" s="1">
         <v>10</v>
       </c>
-      <c r="D26" s="3"/>
+      <c r="D26" s="3">
+        <v>2.2891153735744799E-3</v>
+      </c>
       <c r="E26" s="10"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">

--- a/_resultados/_resultados.xlsx
+++ b/_resultados/_resultados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ravar\Documents\GitHub\recsys-fair-federation-flower\_resultados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A54AED0-BAAB-4028-8078-7598DD3BB62A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C122727-F3EB-4399-8CCA-437AACCF2F71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -933,7 +933,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E822B54-E6B9-4F6D-BD17-4242A3C7CFDB}">
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
@@ -1033,7 +1033,7 @@
         <v>8.4438215453025E-3</v>
       </c>
       <c r="E7" s="11">
-        <f>AVERAGE(D7:D18)</f>
+        <f>AVERAGE(D7:D16)</f>
         <v>8.5087860683188653E-3</v>
       </c>
     </row>
@@ -1130,46 +1130,50 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="10"/>
-      <c r="B17" s="10"/>
+      <c r="B17" s="10" t="s">
+        <v>8</v>
+      </c>
       <c r="C17" s="1">
-        <v>11</v>
-      </c>
-      <c r="D17" s="3"/>
-      <c r="E17" s="10"/>
+        <v>1</v>
+      </c>
+      <c r="D17" s="3">
+        <v>6.2969138289247001E-3</v>
+      </c>
+      <c r="E17" s="11">
+        <f>AVERAGE(D17:D26)</f>
+        <v>6.1136459708670248E-3</v>
+      </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="10"/>
       <c r="B18" s="10"/>
       <c r="C18" s="1">
-        <v>12</v>
-      </c>
-      <c r="D18" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="D18" s="3">
+        <v>6.4076776396648598E-3</v>
+      </c>
       <c r="E18" s="10"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="10"/>
-      <c r="B19" s="10" t="s">
-        <v>8</v>
-      </c>
+      <c r="B19" s="10"/>
       <c r="C19" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D19" s="3">
-        <v>6.2969138289247001E-3</v>
-      </c>
-      <c r="E19" s="11">
-        <f>AVERAGE(D19:D28)</f>
-        <v>6.1674863148601993E-3</v>
-      </c>
+        <v>6.2667263273711001E-3</v>
+      </c>
+      <c r="E19" s="10"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="10"/>
       <c r="B20" s="10"/>
       <c r="C20" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D20" s="3">
-        <v>6.4076776396648598E-3</v>
+        <v>6.2939902848690703E-3</v>
       </c>
       <c r="E20" s="10"/>
     </row>
@@ -1177,10 +1181,10 @@
       <c r="A21" s="10"/>
       <c r="B21" s="10"/>
       <c r="C21" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D21" s="3">
-        <v>6.2667263273711001E-3</v>
+        <v>6.1958847109314704E-3</v>
       </c>
       <c r="E21" s="10"/>
     </row>
@@ -1188,10 +1192,10 @@
       <c r="A22" s="10"/>
       <c r="B22" s="10"/>
       <c r="C22" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D22" s="3">
-        <v>6.2939902848690703E-3</v>
+        <v>5.8309748107789102E-3</v>
       </c>
       <c r="E22" s="10"/>
     </row>
@@ -1199,10 +1203,10 @@
       <c r="A23" s="10"/>
       <c r="B23" s="10"/>
       <c r="C23" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D23" s="3">
-        <v>6.1958847109314704E-3</v>
+        <v>5.5695092562729398E-3</v>
       </c>
       <c r="E23" s="10"/>
     </row>
@@ -1210,10 +1214,10 @@
       <c r="A24" s="10"/>
       <c r="B24" s="10"/>
       <c r="C24" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D24" s="3">
-        <v>5.8309748107789102E-3</v>
+        <v>6.4782136600685398E-3</v>
       </c>
       <c r="E24" s="10"/>
     </row>
@@ -1221,7 +1225,7 @@
       <c r="A25" s="10"/>
       <c r="B25" s="10"/>
       <c r="C25" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D25" s="3">
         <v>5.5695092562729398E-3</v>
@@ -1232,50 +1236,32 @@
       <c r="A26" s="10"/>
       <c r="B26" s="10"/>
       <c r="C26" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D26" s="3">
-        <v>6.4782136600685398E-3</v>
+        <v>6.2270599335157101E-3</v>
       </c>
       <c r="E26" s="10"/>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="10"/>
-      <c r="B27" s="10"/>
-      <c r="C27" s="1">
-        <v>9</v>
-      </c>
-      <c r="D27" s="3"/>
-      <c r="E27" s="10"/>
-    </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="10"/>
-      <c r="B28" s="10"/>
-      <c r="C28" s="1">
-        <v>10</v>
-      </c>
-      <c r="D28" s="3"/>
-      <c r="E28" s="10"/>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="9" t="s">
+      <c r="A28" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A30:E30"/>
-    <mergeCell ref="A2:A28"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A2:A26"/>
     <mergeCell ref="B2:B6"/>
     <mergeCell ref="E2:E6"/>
-    <mergeCell ref="B7:B18"/>
-    <mergeCell ref="E7:E18"/>
-    <mergeCell ref="B19:B28"/>
-    <mergeCell ref="E19:E28"/>
+    <mergeCell ref="B7:B16"/>
+    <mergeCell ref="E7:E16"/>
+    <mergeCell ref="B17:B26"/>
+    <mergeCell ref="E17:E26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
